--- a/ESERCIZIO_M2-1-1_dati - Copia.xlsx
+++ b/ESERCIZIO_M2-1-1_dati - Copia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3965ca6def52ccf6/Desktop/Epicode/Esercizi/1° Settimana_M1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3965ca6def52ccf6/Desktop/GitHub/Esercizi Condivisi/Esercizi-Data-Analyst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="741" documentId="8_{016B3A27-A793-41D9-80CF-710967D4E75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D1C50F8-D8B3-491E-B04E-017139786D5B}"/>
+  <xr:revisionPtr revIDLastSave="742" documentId="8_{016B3A27-A793-41D9-80CF-710967D4E75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{714D9907-478F-4AB2-A997-12FFD38F404E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assoluti_Iva" sheetId="1" r:id="rId1"/>
@@ -2561,12 +2561,6 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2595,11 +2589,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2723,31 +2748,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
         <right/>
         <top style="thin">
           <color indexed="64"/>
@@ -2814,22 +2814,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -2852,6 +2836,22 @@
         </right>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2942,13 +2942,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:E8" headerRowCount="0" headerRowDxfId="12" dataDxfId="11" totalsRowDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:E8" headerRowCount="0" headerRowDxfId="12" dataDxfId="11" totalsRowDxfId="9" tableBorderDxfId="10">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{CAA01F0E-EF37-4ED9-A2B6-239D729E0941}" name="Colonna1" headerRowDxfId="4" dataDxfId="3" totalsRowDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{8B6074E7-7AD3-4567-8E67-5A75EAC7205B}" name="Colonna2" headerRowDxfId="1" dataDxfId="0" totalsRowDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{CAA01F0E-EF37-4ED9-A2B6-239D729E0941}" name="Colonna1" headerRowDxfId="5" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{8B6074E7-7AD3-4567-8E67-5A75EAC7205B}" name="Colonna2" headerRowDxfId="2" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Giudizio-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3185,7 +3185,7 @@
       <c r="F1" s="62" t="s">
         <v>575</v>
       </c>
-      <c r="G1" s="78" t="s">
+      <c r="G1" s="76" t="s">
         <v>568</v>
       </c>
       <c r="I1" s="8"/>
@@ -3218,7 +3218,7 @@
         <v>281000</v>
       </c>
       <c r="D2" s="26">
-        <f>C2-(C2/(1+$G$2))</f>
+        <f t="shared" ref="D2:D65" si="0">C2-(C2/(1+$G$2))</f>
         <v>46833.333333333314</v>
       </c>
       <c r="E2" s="16" t="str">
@@ -3226,10 +3226,10 @@
         <v>MON.SVGA 0,28 14" AOC 4VLR 1024 x 768, MPR II, N.I.,  Energy Star Digital</v>
       </c>
       <c r="F2" s="10">
-        <f>C2/(1+$G$2)</f>
+        <f t="shared" ref="F2:F65" si="1">C2/(1+$G$2)</f>
         <v>234166.66666666669</v>
       </c>
-      <c r="G2" s="77">
+      <c r="G2" s="75">
         <v>0.2</v>
       </c>
       <c r="H2" s="27"/>
@@ -3262,15 +3262,15 @@
         <v>323000</v>
       </c>
       <c r="D3" s="26">
-        <f>C3-(C3/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>53833.333333333314</v>
       </c>
       <c r="E3" s="16" t="str">
-        <f t="shared" ref="E3:E66" si="0">A3 &amp; " " &amp; B3</f>
+        <f t="shared" ref="E3:E66" si="2">A3 &amp; " " &amp; B3</f>
         <v>MON.SVGA 0,28 15" AOC 5VLR 1280 x 1024, MPR II, N.I., Energy Star Digital</v>
       </c>
       <c r="F3" s="10">
-        <f>C3/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>269166.66666666669</v>
       </c>
       <c r="G3" s="19"/>
@@ -3305,15 +3305,15 @@
         <v>344000</v>
       </c>
       <c r="D4" s="26">
-        <f>C4-(C4/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>57333.333333333314</v>
       </c>
       <c r="E4" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON.SVGA 0,28 15" AOC 5NLR OSD 1280 x 1024, MPR II, N.I., Energy Star Digital, 69KHz</v>
       </c>
       <c r="F4" s="10">
-        <f>C4/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>286666.66666666669</v>
       </c>
       <c r="G4" s="19"/>
@@ -3348,15 +3348,15 @@
         <v>361000</v>
       </c>
       <c r="D5" s="26">
-        <f>C5-(C5/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>60166.666666666628</v>
       </c>
       <c r="E5" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON.SVGA 0,28 15" AOC 5GLR+ OSD 1280 x 1024, MPR II,TCO'92 N.I., Energy Star Digit 69KHz</v>
       </c>
       <c r="F5" s="10">
-        <f>C5/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>300833.33333333337</v>
       </c>
       <c r="G5" s="19"/>
@@ -3391,15 +3391,15 @@
         <v>521000</v>
       </c>
       <c r="D6" s="26">
-        <f>C6-(C6/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>86833.333333333314</v>
       </c>
       <c r="E6" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON. 15" 0.23 CM500ET HITACHI 1152x870, 75 Hz, MPR II,TCO'92, N.I.,Energy Star, P&amp;P</v>
       </c>
       <c r="F6" s="10">
-        <f>C6/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>434166.66666666669</v>
       </c>
       <c r="G6" s="19"/>
@@ -3434,15 +3434,15 @@
         <v>527000</v>
       </c>
       <c r="D7" s="26">
-        <f>C7-(C7/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>87833.333333333314</v>
       </c>
       <c r="E7" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON. 15" 0.28 A500 NEC 1280x1024, 60Hz, MPR II, Energy Star, P&amp;P</v>
       </c>
       <c r="F7" s="10">
-        <f>C7/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>439166.66666666669</v>
       </c>
       <c r="G7" s="19"/>
@@ -3477,15 +3477,15 @@
         <v>626000</v>
       </c>
       <c r="D8" s="26">
-        <f>C8-(C8/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>104333.33333333331</v>
       </c>
       <c r="E8" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON.SVGA 0,28 17" AOC 7VLR 1280 x 1024, MPR II, N.I., Energy Star Digital  70KHz</v>
       </c>
       <c r="F8" s="10">
-        <f>C8/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>521666.66666666669</v>
       </c>
       <c r="G8" s="19"/>
@@ -3520,15 +3520,15 @@
         <v>656000</v>
       </c>
       <c r="D9" s="26">
-        <f>C9-(C9/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>109333.33333333326</v>
       </c>
       <c r="E9" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON. 15" 0.25 E500 NEC, Croma Clear 1280x1024, 65Hz,TCO'95, MPR II, Energy Star, P&amp;P</v>
       </c>
       <c r="F9" s="10">
-        <f>C9/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>546666.66666666674</v>
       </c>
       <c r="G9" s="19"/>
@@ -3563,15 +3563,15 @@
         <v>666000</v>
       </c>
       <c r="D10" s="26">
-        <f>C10-(C10/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>111000</v>
       </c>
       <c r="E10" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON.SVGA 0,26 17" AOC 7GLR OSD 1280 x 1024,TCO '92, Energy Star Digital, 85KHz</v>
       </c>
       <c r="F10" s="10">
-        <f>C10/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>555000</v>
       </c>
       <c r="G10" s="19"/>
@@ -3606,15 +3606,15 @@
         <v>882000</v>
       </c>
       <c r="D11" s="26">
-        <f>C11-(C11/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>147000</v>
       </c>
       <c r="E11" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON. 17" 0.28 A700 NEC 1280x1024, 65Hz, MPR II, Energy Star, P&amp;P</v>
       </c>
       <c r="F11" s="10">
-        <f>C11/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>735000</v>
       </c>
       <c r="G11" s="19"/>
@@ -3649,15 +3649,15 @@
         <v>1108000</v>
       </c>
       <c r="D12" s="26">
-        <f>C12-(C12/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>184666.66666666663</v>
       </c>
       <c r="E12" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">MON. 17" 0.21 CM630ET HITACHI 1280x1024,80 Hz,TCO '95 N.I.,Energy Star, P&amp;P </v>
       </c>
       <c r="F12" s="10">
-        <f>C12/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>923333.33333333337</v>
       </c>
       <c r="G12" s="19"/>
@@ -3692,15 +3692,15 @@
         <v>1316000</v>
       </c>
       <c r="D13" s="26">
-        <f>C13-(C13/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>219333.33333333326</v>
       </c>
       <c r="E13" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON. 17" 0.25 P750 NEC, Croma Clear 1600x1280, 75Hz, TCO'92, MPR II, Energy Star, P&amp;P</v>
       </c>
       <c r="F13" s="10">
-        <f>C13/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>1096666.6666666667</v>
       </c>
       <c r="G13" s="19"/>
@@ -3735,15 +3735,15 @@
         <v>1594000</v>
       </c>
       <c r="D14" s="26">
-        <f>C14-(C14/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>265666.66666666651</v>
       </c>
       <c r="E14" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">MON. 19" 0.22 CM751ET HITACHI 1600x1200,75 Hz,TCO '95 N.I.,Energy Star, P&amp;P </v>
       </c>
       <c r="F14" s="10">
-        <f>C14/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>1328333.3333333335</v>
       </c>
       <c r="G14" s="19"/>
@@ -3778,15 +3778,15 @@
         <v>2719000</v>
       </c>
       <c r="D15" s="26">
-        <f>C15-(C15/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>453166.66666666651</v>
       </c>
       <c r="E15" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">MON. 21" 0.21 CM802ETM HITACHI 1600x1280,75 Hz,TCO '95 N.I.,Energy Star, P&amp;P </v>
       </c>
       <c r="F15" s="10">
-        <f>C15/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>2265833.3333333335</v>
       </c>
       <c r="G15" s="19"/>
@@ -3819,15 +3819,15 @@
         <v>0</v>
       </c>
       <c r="D16" s="26">
-        <f>C16-(C16/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">MONITOR  LCD </v>
       </c>
       <c r="F16" s="10">
-        <f>C16/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G16" s="19"/>
@@ -3862,15 +3862,15 @@
         <v>4092000</v>
       </c>
       <c r="D17" s="26">
-        <f>C17-(C17/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>682000</v>
       </c>
       <c r="E17" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON. 14" LCD 0.28 LCD400V NEC 1024x768 75Hz, TFT, Energy Star, P&amp;P</v>
       </c>
       <c r="F17" s="10">
-        <f>C17/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>3410000</v>
       </c>
       <c r="G17" s="19"/>
@@ -3905,15 +3905,15 @@
         <v>13859000</v>
       </c>
       <c r="D18" s="26">
-        <f>C18-(C18/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>2309833.3333333321</v>
       </c>
       <c r="E18" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MON. 20" LCD 0.31 LCD2000sf NEC 1280X1024 75Hz, TFT, Energy Star, P&amp;P</v>
       </c>
       <c r="F18" s="10">
-        <f>C18/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>11549166.666666668</v>
       </c>
       <c r="G18" s="19"/>
@@ -3946,15 +3946,15 @@
         <v>0</v>
       </c>
       <c r="D19" s="26">
-        <f>C19-(C19/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E19" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">SCHEDE MADRI </v>
       </c>
       <c r="F19" s="10">
-        <f>C19/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G19" s="19"/>
@@ -3989,15 +3989,15 @@
         <v>167000</v>
       </c>
       <c r="D20" s="26">
-        <f>C20-(C20/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>27833.333333333314</v>
       </c>
       <c r="E20" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS SP97-V SVGA SHARE MEMORY PCI/ISA/Media Bus. SIS 5598 Share Memory, 4XPCI, 3XISA</v>
       </c>
       <c r="F20" s="10">
-        <f>C20/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>139166.66666666669</v>
       </c>
       <c r="G20" s="19"/>
@@ -4032,15 +4032,15 @@
         <v>202000</v>
       </c>
       <c r="D21" s="26">
-        <f>C21-(C21/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>33666.666666666657</v>
       </c>
       <c r="E21" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS TXP4 PCI/ISA/Media Bus.TX/ 2 x 168 Pin DIMM, 4 x 72 Pin</v>
       </c>
       <c r="F21" s="10">
-        <f>C21/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>168333.33333333334</v>
       </c>
       <c r="G21" s="19"/>
@@ -4075,15 +4075,15 @@
         <v>203000</v>
       </c>
       <c r="D22" s="26">
-        <f>C22-(C22/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>33833.333333333314</v>
       </c>
       <c r="E22" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS SP98AGP-X ATX PCI/ISA/Media Bus. SIS 5591 Share Memory, 3XPCI, 3XISA</v>
       </c>
       <c r="F22" s="10">
-        <f>C22/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>169166.66666666669</v>
       </c>
       <c r="G22" s="19"/>
@@ -4118,15 +4118,15 @@
         <v>234000</v>
       </c>
       <c r="D23" s="26">
-        <f>C23-(C23/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>39000</v>
       </c>
       <c r="E23" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS TX-97 - E  PCI/ISA/Media Bus.TX/ 2 x 168 Pin DIMM, 4 x 72 Pin</v>
       </c>
       <c r="F23" s="10">
-        <f>C23/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>195000</v>
       </c>
       <c r="G23" s="19"/>
@@ -4161,15 +4161,15 @@
         <v>252000</v>
       </c>
       <c r="D24" s="26">
-        <f>C24-(C24/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>42000</v>
       </c>
       <c r="E24" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS TX-97  PCI/ISA/Media Bus.TX/ 3 x 168 Pin DIMM</v>
       </c>
       <c r="F24" s="10">
-        <f>C24/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>210000</v>
       </c>
       <c r="G24" s="19"/>
@@ -4204,15 +4204,15 @@
         <v>259000</v>
       </c>
       <c r="D25" s="26">
-        <f>C25-(C25/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>43166.666666666657</v>
       </c>
       <c r="E25" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS TX-97 - XE ATX NO AUDIO PCI/ISA/Media Bus.TX/ 2 x 168 Pin DIMM, 4 x 72 Pin</v>
       </c>
       <c r="F25" s="10">
-        <f>C25/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>215833.33333333334</v>
       </c>
       <c r="G25" s="19"/>
@@ -4247,15 +4247,15 @@
         <v>269000</v>
       </c>
       <c r="D26" s="26">
-        <f>C26-(C26/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>44833.333333333314</v>
       </c>
       <c r="E26" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS P2L97-B PCI/ISA/Intel 440LX/233-333 Mhz AT BABY</v>
       </c>
       <c r="F26" s="10">
-        <f>C26/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>224166.66666666669</v>
       </c>
       <c r="G26" s="19"/>
@@ -4290,15 +4290,15 @@
         <v>271000</v>
       </c>
       <c r="D27" s="26">
-        <f>C27-(C27/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>45166.666666666657</v>
       </c>
       <c r="E27" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS  P55T2P4 430HX 512K P5 PCI/ISA/Media Bus.Triton II/ZIF7/75-200 MHz</v>
       </c>
       <c r="F27" s="10">
-        <f>C27/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>225833.33333333334</v>
       </c>
       <c r="G27" s="19"/>
@@ -4333,15 +4333,15 @@
         <v>292000</v>
       </c>
       <c r="D28" s="26">
-        <f>C28-(C28/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>48666.666666666657</v>
       </c>
       <c r="E28" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS P2L97 ATX PCI/ISA/Intel 440LX/233-333 Mhz</v>
       </c>
       <c r="F28" s="10">
-        <f>C28/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>243333.33333333334</v>
       </c>
       <c r="G28" s="19"/>
@@ -4376,15 +4376,15 @@
         <v>293000</v>
       </c>
       <c r="D29" s="26">
-        <f>C29-(C29/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>48833.333333333314</v>
       </c>
       <c r="E29" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS XP55T2P4 512K ATX P5 PCI/ISA/Media Bus.Triton II/ZIF7/ 75-200 MHz</v>
       </c>
       <c r="F29" s="10">
-        <f>C29/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>244166.66666666669</v>
       </c>
       <c r="G29" s="19"/>
@@ -4419,15 +4419,15 @@
         <v>307000</v>
       </c>
       <c r="D30" s="26">
-        <f>C30-(C30/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>51166.666666666657</v>
       </c>
       <c r="E30" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS TX-97 -XE ATX -CREATIVE VIBRA16 PCI/ISA/Media Bus.TX/ 2 x 168 Pin DIMM, 4 x 72 Pin</v>
       </c>
       <c r="F30" s="10">
-        <f>C30/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>255833.33333333334</v>
       </c>
       <c r="G30" s="19"/>
@@ -4462,15 +4462,15 @@
         <v>440000</v>
       </c>
       <c r="D31" s="26">
-        <f>C31-(C31/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>73333.333333333314</v>
       </c>
       <c r="E31" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS P2L97-A ATX+VGA AGP 4MB PCI/ISA/Intel 440LX/233-333 Mhz ATI 3D Rage Pro AGP</v>
       </c>
       <c r="F31" s="10">
-        <f>C31/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>366666.66666666669</v>
       </c>
       <c r="G31" s="19"/>
@@ -4505,15 +4505,15 @@
         <v>487000</v>
       </c>
       <c r="D32" s="26">
-        <f>C32-(C32/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>81166.666666666628</v>
       </c>
       <c r="E32" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS P2L97-S ADAPTEC ATX PCI/ISA/Intel 440LX/233-333 Mhz/Adaptec 7880</v>
       </c>
       <c r="F32" s="10">
-        <f>C32/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>405833.33333333337</v>
       </c>
       <c r="G32" s="19"/>
@@ -4548,15 +4548,15 @@
         <v>566000</v>
       </c>
       <c r="D33" s="26">
-        <f>C33-(C33/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>94333.333333333314</v>
       </c>
       <c r="E33" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS P65UP5+P55T2D 512K DUAL P5 PCI/ISA/Media Bus/Intel 430HX/75-200 Mhz</v>
       </c>
       <c r="F33" s="10">
-        <f>C33/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>471666.66666666669</v>
       </c>
       <c r="G33" s="19"/>
@@ -4591,15 +4591,15 @@
         <v>802000</v>
       </c>
       <c r="D34" s="26">
-        <f>C34-(C34/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>133666.66666666663</v>
       </c>
       <c r="E34" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS P2L97-DS DUAL P II PCI/ISA/Intel 440LX/233-333 Mhz/Adaptec 7880</v>
       </c>
       <c r="F34" s="10">
-        <f>C34/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>668333.33333333337</v>
       </c>
       <c r="G34" s="19"/>
@@ -4634,15 +4634,15 @@
         <v>1579000</v>
       </c>
       <c r="D35" s="26">
-        <f>C35-(C35/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>263166.66666666651</v>
       </c>
       <c r="E35" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>M/B ASUS P65UP8+PKND DUAL PII Intel 440FX CPU INTEL RISC i960, SCSI I20 RAID, EXP 1GB</v>
       </c>
       <c r="F35" s="10">
-        <f>C35/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>1315833.3333333335</v>
       </c>
       <c r="G35" s="19"/>
@@ -4675,15 +4675,15 @@
         <v>0</v>
       </c>
       <c r="D36" s="26">
-        <f>C36-(C36/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E36" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">SCHEDE VIDEO </v>
       </c>
       <c r="F36" s="10">
-        <f>C36/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G36" s="19"/>
@@ -4718,15 +4718,15 @@
         <v>70000</v>
       </c>
       <c r="D37" s="26">
-        <f>C37-(C37/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>11666.666666666664</v>
       </c>
       <c r="E37" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>SVGA S3 3D PRO VIRGE 2MB S3 PRO VIRGE DX 2MB Edo exp. 4MB 3D Acc.</v>
       </c>
       <c r="F37" s="10">
-        <f>C37/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>58333.333333333336</v>
       </c>
       <c r="G37" s="19"/>
@@ -4761,15 +4761,15 @@
         <v>104000</v>
       </c>
       <c r="D38" s="26">
-        <f>C38-(C38/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>17333.333333333328</v>
       </c>
       <c r="E38" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>CREATIVE ECLIPSE 4MB ACC. 2D/3D 4MB LAGUNA 3D max 1600x1200</v>
       </c>
       <c r="F38" s="10">
-        <f>C38/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>86666.666666666672</v>
       </c>
       <c r="G38" s="19"/>
@@ -4804,15 +4804,15 @@
         <v>127000</v>
       </c>
       <c r="D39" s="26">
-        <f>C39-(C39/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>21166.666666666657</v>
       </c>
       <c r="E39" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ADD-ON MATROX m3D 4MB MATROX - NEC Power VR PCX2</v>
       </c>
       <c r="F39" s="10">
-        <f>C39/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>105833.33333333334</v>
       </c>
       <c r="G39" s="19"/>
@@ -4847,15 +4847,15 @@
         <v>162000</v>
       </c>
       <c r="D40" s="26">
-        <f>C40-(C40/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>27000</v>
       </c>
       <c r="E40" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ASUS 3DP-V264GT2 4MB TV-OUT ATI Rage II+ , 2D/3D, DVD Acc.,TV OUT</v>
       </c>
       <c r="F40" s="10">
-        <f>C40/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>135000</v>
       </c>
       <c r="G40" s="19"/>
@@ -4890,15 +4890,15 @@
         <v>179000</v>
       </c>
       <c r="D41" s="26">
-        <f>C41-(C41/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>29833.333333333314</v>
       </c>
       <c r="E41" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>SVGA MYSTIQUE 220 "BULK" 4MB MATROX,MGA 1064SG SGRAM</v>
       </c>
       <c r="F41" s="10">
-        <f>C41/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>149166.66666666669</v>
       </c>
       <c r="G41" s="19"/>
@@ -4933,15 +4933,15 @@
         <v>186000</v>
       </c>
       <c r="D42" s="26">
-        <f>C42-(C42/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>31000</v>
       </c>
       <c r="E42" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ASUS 3DP-V385GX2 4MB TV-OUT  S3 VIRGE/GX2,2D/3D DVD Acc. VIDEO-IN&amp;TV OUT</v>
       </c>
       <c r="F42" s="10">
-        <f>C42/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>155000</v>
       </c>
       <c r="G42" s="19"/>
@@ -4976,15 +4976,15 @@
         <v>186000</v>
       </c>
       <c r="D43" s="26">
-        <f>C43-(C43/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>31000</v>
       </c>
       <c r="E43" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ASUS V385GX2 AGP 4MB TV-OUT S3 VIRGE/GX2,2D/3D DVD Acc. VIDEO-IN&amp;TV OUT</v>
       </c>
       <c r="F43" s="10">
-        <f>C43/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>155000</v>
       </c>
       <c r="G43" s="19"/>
@@ -5019,15 +5019,15 @@
         <v>203000</v>
       </c>
       <c r="D44" s="26">
-        <f>C44-(C44/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>33833.333333333314</v>
       </c>
       <c r="E44" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>CREATIVE GRAPHIC EXXTREME 4MB ACC. 2D/3D 4MB SGRAM T.I.9735AC</v>
       </c>
       <c r="F44" s="10">
-        <f>C44/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>169166.66666666669</v>
       </c>
       <c r="G44" s="19"/>
@@ -5062,15 +5062,15 @@
         <v>212000</v>
       </c>
       <c r="D45" s="26">
-        <f>C45-(C45/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>35333.333333333314</v>
       </c>
       <c r="E45" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>SVGA MYSTIQUE 220  4MB MATROX,MGA 1064SG SGRAM</v>
       </c>
       <c r="F45" s="10">
-        <f>C45/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>176666.66666666669</v>
       </c>
       <c r="G45" s="19"/>
@@ -5105,15 +5105,15 @@
         <v>222000</v>
       </c>
       <c r="D46" s="26">
-        <f>C46-(C46/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>37000</v>
       </c>
       <c r="E46" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>SVGA ACC. 3D/FX VOODO RUSH 4MB ACC.2D/3D 3D/FX Voodo Rush+AT25 Game+Giochi</v>
       </c>
       <c r="F46" s="10">
-        <f>C46/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>185000</v>
       </c>
       <c r="G46" s="19"/>
@@ -5148,15 +5148,15 @@
         <v>245000</v>
       </c>
       <c r="D47" s="26">
-        <f>C47-(C47/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>40833.333333333314</v>
       </c>
       <c r="E47" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>SVGA ACC. 3D/FX VOODO RUSH 6MB ACC.2D/3D 3D/FX Voodoo Rush+AT25 Game+Giochi</v>
       </c>
       <c r="F47" s="10">
-        <f>C47/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>204166.66666666669</v>
       </c>
       <c r="G47" s="19"/>
@@ -5191,15 +5191,15 @@
         <v>251000</v>
       </c>
       <c r="D48" s="26">
-        <f>C48-(C48/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>41833.333333333314</v>
       </c>
       <c r="E48" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>RAINBOW R. TV MATROX</v>
       </c>
       <c r="F48" s="10">
-        <f>C48/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>209166.66666666669</v>
       </c>
       <c r="G48" s="19"/>
@@ -5234,15 +5234,15 @@
         <v>257000</v>
       </c>
       <c r="D49" s="26">
-        <f>C49-(C49/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>42833.333333333314</v>
       </c>
       <c r="E49" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ASUS 3D EXPLORER AGP 4MB TV-OUT ASUS, 2D/3D, 4MB SGRAM SGS T. RIVA128</v>
       </c>
       <c r="F49" s="10">
-        <f>C49/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>214166.66666666669</v>
       </c>
       <c r="G49" s="19"/>
@@ -5277,15 +5277,15 @@
         <v>269000</v>
       </c>
       <c r="D50" s="26">
-        <f>C50-(C50/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>44833.333333333314</v>
       </c>
       <c r="E50" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ASUS 3D EXPLORER PCI 4MB TV-OUT ASUS, 2D/3D, 4MB SGRAM SGS T. RIVA128</v>
       </c>
       <c r="F50" s="10">
-        <f>C50/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>224166.66666666669</v>
       </c>
       <c r="G50" s="19"/>
@@ -5320,15 +5320,15 @@
         <v>314000</v>
       </c>
       <c r="D51" s="26">
-        <f>C51-(C51/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>52333.333333333314</v>
       </c>
       <c r="E51" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">SVGA MILLENNIUM II 4MB "BULK" MATROX,MGA MILLENNIUM II WRAM </v>
       </c>
       <c r="F51" s="10">
-        <f>C51/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>261666.66666666669</v>
       </c>
       <c r="G51" s="19"/>
@@ -5363,15 +5363,15 @@
         <v>325000</v>
       </c>
       <c r="D52" s="26">
-        <f>C52-(C52/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>54166.666666666628</v>
       </c>
       <c r="E52" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>SVGA MILLENNIUM II 4MB AGP MATROX,MGA MILLENNIUM II WRAM  AGP</v>
       </c>
       <c r="F52" s="10">
-        <f>C52/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>270833.33333333337</v>
       </c>
       <c r="G52" s="19"/>
@@ -5406,15 +5406,15 @@
         <v>347000</v>
       </c>
       <c r="D53" s="26">
-        <f>C53-(C53/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>57833.333333333314</v>
       </c>
       <c r="E53" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>RAINBOW R. STUDIO per MATROX MYSTIQUE</v>
       </c>
       <c r="F53" s="10">
-        <f>C53/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>289166.66666666669</v>
       </c>
       <c r="G53" s="19"/>
@@ -5449,15 +5449,15 @@
         <v>369000</v>
       </c>
       <c r="D54" s="26">
-        <f>C54-(C54/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>61500</v>
       </c>
       <c r="E54" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">SVGA MILLENNIUM II 4MB MATROX,MGA MILLENNIUM II WRAM </v>
       </c>
       <c r="F54" s="10">
-        <f>C54/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>307500</v>
       </c>
       <c r="G54" s="19"/>
@@ -5492,15 +5492,15 @@
         <v>402000</v>
       </c>
       <c r="D55" s="26">
-        <f>C55-(C55/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>67000</v>
       </c>
       <c r="E55" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>CREATIVE VOODO-2 8MB Add-on ACC.3D Voodo 3Dfx + Pixelfx PQFP 256pin+Texelfx PQFP208pin</v>
       </c>
       <c r="F55" s="10">
-        <f>C55/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>335000</v>
       </c>
       <c r="G55" s="19"/>
@@ -5535,15 +5535,15 @@
         <v>471000</v>
       </c>
       <c r="D56" s="26">
-        <f>C56-(C56/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>78500</v>
       </c>
       <c r="E56" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">SVGA MILLENNIUM II 8MB "BULK" MATROX,MGA MILLENNIUM II WRAM </v>
       </c>
       <c r="F56" s="10">
-        <f>C56/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>392500</v>
       </c>
       <c r="G56" s="19"/>
@@ -5578,15 +5578,15 @@
         <v>476000</v>
       </c>
       <c r="D57" s="26">
-        <f>C57-(C57/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>79333.333333333314</v>
       </c>
       <c r="E57" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>SVGA MILLENNIUM II 8MB AGP MATROX,MGA MILLENNIUM II WRAM  AGP</v>
       </c>
       <c r="F57" s="10">
-        <f>C57/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>396666.66666666669</v>
       </c>
       <c r="G57" s="19"/>
@@ -5621,15 +5621,15 @@
         <v>492000</v>
       </c>
       <c r="D58" s="26">
-        <f>C58-(C58/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>82000</v>
       </c>
       <c r="E58" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>CREATIVE VOODO-2 12MB Add-on ACC.3D Voodo 3Dfx + Pixelfx PQFP 256pin+Texelfx PQFP208pin</v>
       </c>
       <c r="F58" s="10">
-        <f>C58/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>410000</v>
       </c>
       <c r="G58" s="19"/>
@@ -5664,15 +5664,15 @@
         <v>531000</v>
       </c>
       <c r="D59" s="26">
-        <f>C59-(C59/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>88500</v>
       </c>
       <c r="E59" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>VIDEO &amp; GRAPHIC KIT MATROX MISTIQUE 4MB+ RAINBOW RUNNER</v>
       </c>
       <c r="F59" s="10">
-        <f>C59/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>442500</v>
       </c>
       <c r="G59" s="19"/>
@@ -5707,15 +5707,15 @@
         <v>552000</v>
       </c>
       <c r="D60" s="26">
-        <f>C60-(C60/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>92000</v>
       </c>
       <c r="E60" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">SVGA MILLENNIUM II 8MB MATROX,MGA MILLENNIUM II WRAM </v>
       </c>
       <c r="F60" s="10">
-        <f>C60/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>460000</v>
       </c>
       <c r="G60" s="19"/>
@@ -5750,15 +5750,15 @@
         <v>1487000</v>
       </c>
       <c r="D61" s="26">
-        <f>C61-(C61/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>247833.33333333326</v>
       </c>
       <c r="E61" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ASUS 3DP- V500TX 16MB Work.Prof.3d 3D LABS GLINT500TX,8MB VRAM Frame Buffer,8MB DRAM</v>
       </c>
       <c r="F61" s="10">
-        <f>C61/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>1239166.6666666667</v>
       </c>
       <c r="G61" s="19"/>
@@ -5791,15 +5791,15 @@
         <v>0</v>
       </c>
       <c r="D62" s="26">
-        <f>C62-(C62/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E62" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">SCHEDE I/O </v>
       </c>
       <c r="F62" s="10">
-        <f>C62/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G62" s="19"/>
@@ -5834,15 +5834,15 @@
         <v>101000</v>
       </c>
       <c r="D63" s="26">
-        <f>C63-(C63/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>16833.333333333328</v>
       </c>
       <c r="E63" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Contr. PCI SCSI Fast SCSI-2</v>
       </c>
       <c r="F63" s="10">
-        <f>C63/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>84166.666666666672</v>
       </c>
       <c r="G63" s="19"/>
@@ -5877,15 +5877,15 @@
         <v>38000</v>
       </c>
       <c r="D64" s="26">
-        <f>C64-(C64/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>6333.3333333333321</v>
       </c>
       <c r="E64" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Contr. PCI EIDE Tekram 690B, 4 canali EIDE</v>
       </c>
       <c r="F64" s="10">
-        <f>C64/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>31666.666666666668</v>
       </c>
       <c r="G64" s="19"/>
@@ -5920,15 +5920,15 @@
         <v>137000</v>
       </c>
       <c r="D65" s="26">
-        <f>C65-(C65/(1+$G$2))</f>
+        <f t="shared" si="0"/>
         <v>22833.333333333328</v>
       </c>
       <c r="E65" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Contr. PCI SC200 SCSI-2 ASUS NCR-53C810 Ultra Fast, SCSI-2</v>
       </c>
       <c r="F65" s="10">
-        <f>C65/(1+$G$2)</f>
+        <f t="shared" si="1"/>
         <v>114166.66666666667</v>
       </c>
       <c r="G65" s="19"/>
@@ -5963,15 +5963,15 @@
         <v>222000</v>
       </c>
       <c r="D66" s="26">
-        <f>C66-(C66/(1+$G$2))</f>
+        <f t="shared" ref="D66:D129" si="3">C66-(C66/(1+$G$2))</f>
         <v>37000</v>
       </c>
       <c r="E66" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Contr. PCI SC875 Wide SCSI, SCSI-2 ASUS NCR-53C875 Ultra Fast, Wide SCSI e SCSI-2</v>
       </c>
       <c r="F66" s="10">
-        <f>C66/(1+$G$2)</f>
+        <f t="shared" ref="F66:F129" si="4">C66/(1+$G$2)</f>
         <v>185000</v>
       </c>
       <c r="G66" s="19"/>
@@ -6006,15 +6006,15 @@
         <v>501000</v>
       </c>
       <c r="D67" s="26">
-        <f>C67-(C67/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>83500</v>
       </c>
       <c r="E67" s="16" t="str">
-        <f t="shared" ref="E67:E130" si="1">A67 &amp; " " &amp; B67</f>
+        <f t="shared" ref="E67:E130" si="5">A67 &amp; " " &amp; B67</f>
         <v>Contr. PCI AHA 2940AU SCSI-2 Adaptec 2940 Ultra Fast, SCSI-2, sw EZ SCSI 4.0</v>
       </c>
       <c r="F67" s="10">
-        <f>C67/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>417500</v>
       </c>
       <c r="G67" s="19"/>
@@ -6049,15 +6049,15 @@
         <v>428000</v>
       </c>
       <c r="D68" s="26">
-        <f>C68-(C68/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>71333.333333333314</v>
       </c>
       <c r="E68" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Contr. PCI AHA 2940UW Wide SCSI OEM Adaptec 2940 Ultra Fast, Wide SCSI e SCSI-2</v>
       </c>
       <c r="F68" s="10">
-        <f>C68/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>356666.66666666669</v>
       </c>
       <c r="G68" s="19"/>
@@ -6092,15 +6092,15 @@
         <v>561000</v>
       </c>
       <c r="D69" s="26">
-        <f>C69-(C69/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>93500</v>
       </c>
       <c r="E69" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Contr. PCI AHA 2940UW Wide SCSI Adaptec 2940 Ultra Fast, Wide SCSI e SCSI-2, sw EZ SCSI</v>
       </c>
       <c r="F69" s="10">
-        <f>C69/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>467500</v>
       </c>
       <c r="G69" s="19"/>
@@ -6135,15 +6135,15 @@
         <v>1578000</v>
       </c>
       <c r="D70" s="26">
-        <f>C70-(C70/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>263000</v>
       </c>
       <c r="E70" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Contr.PCI DA2100 Dual Wide SCSI ASUS Infotrend-500127 dual Ultra Fast, Wide SCSI, RAID</v>
       </c>
       <c r="F70" s="10">
-        <f>C70/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>1315000</v>
       </c>
       <c r="G70" s="19"/>
@@ -6178,15 +6178,15 @@
         <v>34000</v>
       </c>
       <c r="D71" s="26">
-        <f>C71-(C71/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>5666.6666666666642</v>
       </c>
       <c r="E71" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>Scheda 2 porte seriali, 1 porta parallela 16550 Fast UART</v>
       </c>
       <c r="F71" s="10">
-        <f>C71/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>28333.333333333336</v>
       </c>
       <c r="G71" s="19"/>
@@ -6221,15 +6221,15 @@
         <v>20000</v>
       </c>
       <c r="D72" s="26">
-        <f>C72-(C72/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>3333.3333333333321</v>
       </c>
       <c r="E72" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">Scheda singola seriale  </v>
       </c>
       <c r="F72" s="10">
-        <f>C72/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>16666.666666666668</v>
       </c>
       <c r="G72" s="19"/>
@@ -6264,15 +6264,15 @@
         <v>23000</v>
       </c>
       <c r="D73" s="26">
-        <f>C73-(C73/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>3833.3333333333321</v>
       </c>
       <c r="E73" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">Scheda doppia seriale  </v>
       </c>
       <c r="F73" s="10">
-        <f>C73/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>19166.666666666668</v>
       </c>
       <c r="G73" s="19"/>
@@ -6305,15 +6305,15 @@
         <v>98000</v>
       </c>
       <c r="D74" s="26">
-        <f>C74-(C74/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>16333.333333333328</v>
       </c>
       <c r="E74" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">Scheda 4 porte seriali </v>
       </c>
       <c r="F74" s="10">
-        <f>C74/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>81666.666666666672</v>
       </c>
       <c r="G74" s="19"/>
@@ -6346,15 +6346,15 @@
         <v>251000</v>
       </c>
       <c r="D75" s="26">
-        <f>C75-(C75/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>41833.333333333314</v>
       </c>
       <c r="E75" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">Scheda 8 porte seriali </v>
       </c>
       <c r="F75" s="10">
-        <f>C75/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>209166.66666666669</v>
       </c>
       <c r="G75" s="19"/>
@@ -6387,15 +6387,15 @@
         <v>15000</v>
       </c>
       <c r="D76" s="26">
-        <f>C76-(C76/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>2500</v>
       </c>
       <c r="E76" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">Scheda singola parallela </v>
       </c>
       <c r="F76" s="10">
-        <f>C76/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>12500</v>
       </c>
       <c r="G76" s="19"/>
@@ -6428,15 +6428,15 @@
         <v>14000</v>
       </c>
       <c r="D77" s="26">
-        <f>C77-(C77/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>2333.3333333333321</v>
       </c>
       <c r="E77" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">Scheda 2 porte joystick </v>
       </c>
       <c r="F77" s="10">
-        <f>C77/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>11666.666666666668</v>
       </c>
       <c r="G77" s="19"/>
@@ -6469,15 +6469,15 @@
         <v>0</v>
       </c>
       <c r="D78" s="26">
-        <f>C78-(C78/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E78" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">HARD DISK </v>
       </c>
       <c r="F78" s="10">
-        <f>C78/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G78" s="19"/>
@@ -6512,15 +6512,15 @@
         <v>399000</v>
       </c>
       <c r="D79" s="26">
-        <f>C79-(C79/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>66500</v>
       </c>
       <c r="E79" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>HARD DISK 2.5"  2,1GB U.Dma 2,5" 12mm HITACHI - DK226A-21</v>
       </c>
       <c r="F79" s="10">
-        <f>C79/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>332500</v>
       </c>
       <c r="G79" s="19"/>
@@ -6555,15 +6555,15 @@
         <v>259000</v>
       </c>
       <c r="D80" s="26">
-        <f>C80-(C80/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>43166.666666666657</v>
       </c>
       <c r="E80" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">HD 2,1 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F80" s="10">
-        <f>C80/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>215833.33333333334</v>
       </c>
       <c r="G80" s="19"/>
@@ -6598,15 +6598,15 @@
         <v>324000</v>
       </c>
       <c r="D81" s="26">
-        <f>C81-(C81/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>54000</v>
       </c>
       <c r="E81" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">HD 3,2 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F81" s="10">
-        <f>C81/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>270000</v>
       </c>
       <c r="G81" s="19"/>
@@ -6641,15 +6641,15 @@
         <v>378000</v>
       </c>
       <c r="D82" s="26">
-        <f>C82-(C82/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>63000</v>
       </c>
       <c r="E82" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">HD 4,3 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F82" s="10">
-        <f>C82/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>315000</v>
       </c>
       <c r="G82" s="19"/>
@@ -6684,15 +6684,15 @@
         <v>469000</v>
       </c>
       <c r="D83" s="26">
-        <f>C83-(C83/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>78166.666666666628</v>
       </c>
       <c r="E83" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">HD 5,2 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F83" s="10">
-        <f>C83/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>390833.33333333337</v>
       </c>
       <c r="G83" s="19"/>
@@ -6727,15 +6727,15 @@
         <v>556000</v>
       </c>
       <c r="D84" s="26">
-        <f>C84-(C84/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>92666.666666666628</v>
       </c>
       <c r="E84" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">HD 6,4 GB Ultra DMA 5400rpm 3,5" ULTRA DMA FUJITSU </v>
       </c>
       <c r="F84" s="10">
-        <f>C84/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>463333.33333333337</v>
       </c>
       <c r="G84" s="19"/>
@@ -6770,15 +6770,15 @@
         <v>476000</v>
       </c>
       <c r="D85" s="26">
-        <f>C85-(C85/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>79333.333333333314</v>
       </c>
       <c r="E85" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>HD 2 GB SCSI III 5400 rpm 3,5" SCSI QUANTUM FIREBALL ST</v>
       </c>
       <c r="F85" s="10">
-        <f>C85/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>396666.66666666669</v>
       </c>
       <c r="G85" s="19"/>
@@ -6813,15 +6813,15 @@
         <v>477000</v>
       </c>
       <c r="D86" s="26">
-        <f>C86-(C86/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>79500</v>
       </c>
       <c r="E86" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>HD 3,2 GB SCSI III 5400rpm 3,5" SCSI QUANTUM FIREBALL ST</v>
       </c>
       <c r="F86" s="10">
-        <f>C86/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>397500</v>
       </c>
       <c r="G86" s="19"/>
@@ -6856,15 +6856,15 @@
         <v>556000</v>
       </c>
       <c r="D87" s="26">
-        <f>C87-(C87/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>92666.666666666628</v>
       </c>
       <c r="E87" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>HD 4,3 GB SCSI 5400 rpm 3,5" SCSI QUANTUM FIREBALL ST</v>
       </c>
       <c r="F87" s="10">
-        <f>C87/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>463333.33333333337</v>
       </c>
       <c r="G87" s="19"/>
@@ -6899,15 +6899,15 @@
         <v>695000</v>
       </c>
       <c r="D88" s="26">
-        <f>C88-(C88/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>115833.33333333326</v>
       </c>
       <c r="E88" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>HD 4,5 GB SCSI ULTRA WIDE 7200rpm 3,5" SCSI III, QUANTUM VIKING</v>
       </c>
       <c r="F88" s="10">
-        <f>C88/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>579166.66666666674</v>
       </c>
       <c r="G88" s="19"/>
@@ -6942,15 +6942,15 @@
         <v>1279000</v>
       </c>
       <c r="D89" s="26">
-        <f>C89-(C89/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>213166.66666666651</v>
       </c>
       <c r="E89" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>HD 4,5 GB SCSI ULTRA WIDE 10.000rpm 3,5" SCSI U.W. SEAGATE CHEETAH</v>
       </c>
       <c r="F89" s="10">
-        <f>C89/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>1065833.3333333335</v>
       </c>
       <c r="G89" s="19"/>
@@ -6985,15 +6985,15 @@
         <v>35000</v>
       </c>
       <c r="D90" s="26">
-        <f>C90-(C90/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>5833.3333333333321</v>
       </c>
       <c r="E90" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>FDD 1,44MB PANASONIC</v>
       </c>
       <c r="F90" s="10">
-        <f>C90/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>29166.666666666668</v>
       </c>
       <c r="G90" s="19"/>
@@ -7028,15 +7028,15 @@
         <v>175000</v>
       </c>
       <c r="D91" s="26">
-        <f>C91-(C91/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>29166.666666666657</v>
       </c>
       <c r="E91" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>FLOPPY DRIVE 120MB PANASONIC LS-120</v>
       </c>
       <c r="F91" s="10">
-        <f>C91/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>145833.33333333334</v>
       </c>
       <c r="G91" s="19"/>
@@ -7071,15 +7071,15 @@
         <v>272000</v>
       </c>
       <c r="D92" s="26">
-        <f>C92-(C92/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>45333.333333333314</v>
       </c>
       <c r="E92" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>ZIP DRIVE 100MB PARALL. IOMEGA</v>
       </c>
       <c r="F92" s="10">
-        <f>C92/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>226666.66666666669</v>
       </c>
       <c r="G92" s="19"/>
@@ -7114,15 +7114,15 @@
         <v>198000</v>
       </c>
       <c r="D93" s="26">
-        <f>C93-(C93/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>33000</v>
       </c>
       <c r="E93" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>ZIP ATAPI 100MB INTERNO IOMEGA</v>
       </c>
       <c r="F93" s="10">
-        <f>C93/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>165000</v>
       </c>
       <c r="G93" s="19"/>
@@ -7157,15 +7157,15 @@
         <v>290000</v>
       </c>
       <c r="D94" s="26">
-        <f>C94-(C94/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>48333.333333333314</v>
       </c>
       <c r="E94" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>ZIP DRIVE 100MB SCSI IOMEGA</v>
       </c>
       <c r="F94" s="10">
-        <f>C94/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>241666.66666666669</v>
       </c>
       <c r="G94" s="19"/>
@@ -7200,15 +7200,15 @@
         <v>589000</v>
       </c>
       <c r="D95" s="26">
-        <f>C95-(C95/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>98166.666666666628</v>
       </c>
       <c r="E95" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>JAZ DRIVE 1GB INT. IOMEGA</v>
       </c>
       <c r="F95" s="10">
-        <f>C95/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>490833.33333333337</v>
       </c>
       <c r="G95" s="19"/>
@@ -7243,15 +7243,15 @@
         <v>743000</v>
       </c>
       <c r="D96" s="26">
-        <f>C96-(C96/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>123833.33333333326</v>
       </c>
       <c r="E96" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>JAZ DRIVE 1GB EXT. IOMEGA</v>
       </c>
       <c r="F96" s="10">
-        <f>C96/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>619166.66666666674</v>
       </c>
       <c r="G96" s="19"/>
@@ -7286,15 +7286,15 @@
         <v>271000</v>
       </c>
       <c r="D97" s="26">
-        <f>C97-(C97/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>45166.666666666657</v>
       </c>
       <c r="E97" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">KIT 10  CARTUCCE ZIP DRIVE  </v>
       </c>
       <c r="F97" s="10">
-        <f>C97/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>225833.33333333334</v>
       </c>
       <c r="G97" s="19"/>
@@ -7329,15 +7329,15 @@
         <v>632000</v>
       </c>
       <c r="D98" s="26">
-        <f>C98-(C98/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>105333.33333333326</v>
       </c>
       <c r="E98" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">KIT 3 CARTUCCE JAZ DRIVE  </v>
       </c>
       <c r="F98" s="10">
-        <f>C98/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>526666.66666666674</v>
       </c>
       <c r="G98" s="19"/>
@@ -7372,15 +7372,15 @@
         <v>90000</v>
       </c>
       <c r="D99" s="26">
-        <f>C99-(C99/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>15000</v>
       </c>
       <c r="E99" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>KIT 3 CARTUCCE 120MB 3M per LS-120</v>
       </c>
       <c r="F99" s="10">
-        <f>C99/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>75000</v>
       </c>
       <c r="G99" s="19"/>
@@ -7415,15 +7415,15 @@
         <v>4000</v>
       </c>
       <c r="D100" s="26">
-        <f>C100-(C100/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>666.66666666666652</v>
       </c>
       <c r="E100" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>FRAME HDD  Kit montaggio Hard Disk 3,5"</v>
       </c>
       <c r="F100" s="10">
-        <f>C100/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>3333.3333333333335</v>
       </c>
       <c r="G100" s="19"/>
@@ -7458,15 +7458,15 @@
         <v>5000</v>
       </c>
       <c r="D101" s="26">
-        <f>C101-(C101/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>833.33333333333303</v>
       </c>
       <c r="E101" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>FRAME FDD  Kit montaggio Floppy Disk Drive 3,5"</v>
       </c>
       <c r="F101" s="10">
-        <f>C101/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>4166.666666666667</v>
       </c>
       <c r="G101" s="19"/>
@@ -7501,15 +7501,15 @@
         <v>41000</v>
       </c>
       <c r="D102" s="26">
-        <f>C102-(C102/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>6833.3333333333285</v>
       </c>
       <c r="E102" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>FRAME REMOVIBILE 3.5" Kit FRAME REMOVIBILE per HDD 3,5"</v>
       </c>
       <c r="F102" s="10">
-        <f>C102/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>34166.666666666672</v>
       </c>
       <c r="G102" s="19"/>
@@ -7542,15 +7542,15 @@
         <v>0</v>
       </c>
       <c r="D103" s="26">
-        <f>C103-(C103/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E103" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">MAGNETO-OTTICI </v>
       </c>
       <c r="F103" s="10">
-        <f>C103/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G103" s="19"/>
@@ -7585,15 +7585,15 @@
         <v>737000</v>
       </c>
       <c r="D104" s="26">
-        <f>C104-(C104/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>122833.33333333326</v>
       </c>
       <c r="E104" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>M.O. + CD 4X,  PD 2000 INT. 650 MB PLASMON PD2000I</v>
       </c>
       <c r="F104" s="10">
-        <f>C104/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>614166.66666666674</v>
       </c>
       <c r="G104" s="19"/>
@@ -7628,15 +7628,15 @@
         <v>910000</v>
       </c>
       <c r="D105" s="26">
-        <f>C105-(C105/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>151666.66666666663</v>
       </c>
       <c r="E105" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>M.O. + CD 4X,  PD 2000 EXT. 650 MB PLASMON PD2000E</v>
       </c>
       <c r="F105" s="10">
-        <f>C105/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>758333.33333333337</v>
       </c>
       <c r="G105" s="19"/>
@@ -7669,15 +7669,15 @@
         <v>241000</v>
       </c>
       <c r="D106" s="26">
-        <f>C106-(C106/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>40166.666666666657</v>
       </c>
       <c r="E106" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">KIT 5 CARTUCCE 650 MB </v>
       </c>
       <c r="F106" s="10">
-        <f>C106/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>200833.33333333334</v>
       </c>
       <c r="G106" s="19"/>
@@ -7710,15 +7710,15 @@
         <v>0</v>
       </c>
       <c r="D107" s="26">
-        <f>C107-(C107/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E107" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">CD ROM </v>
       </c>
       <c r="F107" s="10">
-        <f>C107/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G107" s="19"/>
@@ -7753,15 +7753,15 @@
         <v>112000</v>
       </c>
       <c r="D108" s="26">
-        <f>C108-(C108/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>18666.666666666657</v>
       </c>
       <c r="E108" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CD ROM 24X HITACHI CDR 8330 24 velocita',EIDE</v>
       </c>
       <c r="F108" s="10">
-        <f>C108/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>93333.333333333343</v>
       </c>
       <c r="G108" s="19"/>
@@ -7796,15 +7796,15 @@
         <v>113000</v>
       </c>
       <c r="D109" s="26">
-        <f>C109-(C109/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>18833.333333333328</v>
       </c>
       <c r="E109" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CD ROM 24X CREATIVE 24 velocita',EIDE</v>
       </c>
       <c r="F109" s="10">
-        <f>C109/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>94166.666666666672</v>
       </c>
       <c r="G109" s="19"/>
@@ -7839,15 +7839,15 @@
         <v>121000</v>
       </c>
       <c r="D110" s="26">
-        <f>C110-(C110/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>20166.666666666657</v>
       </c>
       <c r="E110" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CD ROM 24X PIONEER 502-S Bulk 24 velocita',EIDE,SLOT-IN</v>
       </c>
       <c r="F110" s="10">
-        <f>C110/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>100833.33333333334</v>
       </c>
       <c r="G110" s="19"/>
@@ -7882,15 +7882,15 @@
         <v>160000</v>
       </c>
       <c r="D111" s="26">
-        <f>C111-(C111/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>26666.666666666657</v>
       </c>
       <c r="E111" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CD ROM 34X ASUS 34 velocita',EIDE</v>
       </c>
       <c r="F111" s="10">
-        <f>C111/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>133333.33333333334</v>
       </c>
       <c r="G111" s="19"/>
@@ -7925,15 +7925,15 @@
         <v>195000</v>
       </c>
       <c r="D112" s="26">
-        <f>C112-(C112/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>32500</v>
       </c>
       <c r="E112" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CD ROM 24X SCSI NEC 24 velocita',SCSI</v>
       </c>
       <c r="F112" s="10">
-        <f>C112/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>162500</v>
       </c>
       <c r="G112" s="19"/>
@@ -7968,15 +7968,15 @@
         <v>215000</v>
       </c>
       <c r="D113" s="26">
-        <f>C113-(C113/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>35833.333333333314</v>
       </c>
       <c r="E113" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CD ROM 32X SCSI WAITEC 32 velocita',SCSI</v>
       </c>
       <c r="F113" s="10">
-        <f>C113/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>179166.66666666669</v>
       </c>
       <c r="G113" s="19"/>
@@ -8011,15 +8011,15 @@
         <v>321000</v>
       </c>
       <c r="D114" s="26">
-        <f>C114-(C114/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>53500</v>
       </c>
       <c r="E114" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CD ROM PLEXTOR PX-32TSI 32 velocita',SCSI</v>
       </c>
       <c r="F114" s="10">
-        <f>C114/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>267500</v>
       </c>
       <c r="G114" s="19"/>
@@ -8054,15 +8054,15 @@
         <v>614000</v>
       </c>
       <c r="D115" s="26">
-        <f>C115-(C115/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>102333.33333333331</v>
       </c>
       <c r="E115" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>DVD CREATIVE KIT ENCORE DXR2 CREATIVE</v>
       </c>
       <c r="F115" s="10">
-        <f>C115/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>511666.66666666669</v>
       </c>
       <c r="G115" s="19"/>
@@ -8095,15 +8095,15 @@
         <v>0</v>
       </c>
       <c r="D116" s="26">
-        <f>C116-(C116/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E116" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">MASTERIZZATORI </v>
       </c>
       <c r="F116" s="10">
-        <f>C116/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G116" s="19"/>
@@ -8138,15 +8138,15 @@
         <v>30000</v>
       </c>
       <c r="D117" s="26">
-        <f>C117-(C117/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>5000</v>
       </c>
       <c r="E117" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CONFEZIONE 10 CDR 74' Kit 10 pz.</v>
       </c>
       <c r="F117" s="10">
-        <f>C117/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>25000</v>
       </c>
       <c r="G117" s="19"/>
@@ -8181,15 +8181,15 @@
         <v>34000</v>
       </c>
       <c r="D118" s="26">
-        <f>C118-(C118/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>5666.6666666666642</v>
       </c>
       <c r="E118" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CD RISCRIVIBILE 74' VERBATIM</v>
       </c>
       <c r="F118" s="10">
-        <f>C118/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>28333.333333333336</v>
       </c>
       <c r="G118" s="19"/>
@@ -8224,15 +8224,15 @@
         <v>35000</v>
       </c>
       <c r="D119" s="26">
-        <f>C119-(C119/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>5833.3333333333321</v>
       </c>
       <c r="E119" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CONFEZIONE 10 CDR 74' KODAK Kit 10 pz.</v>
       </c>
       <c r="F119" s="10">
-        <f>C119/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>29166.666666666668</v>
       </c>
       <c r="G119" s="19"/>
@@ -8267,15 +8267,15 @@
         <v>77000</v>
       </c>
       <c r="D120" s="26">
-        <f>C120-(C120/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>12833.333333333328</v>
       </c>
       <c r="E120" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>SOFTWARE LABELLER CD KIT Software per creazione etichette CD</v>
       </c>
       <c r="F120" s="10">
-        <f>C120/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>64166.666666666672</v>
       </c>
       <c r="G120" s="19"/>
@@ -8310,15 +8310,15 @@
         <v>723000</v>
       </c>
       <c r="D121" s="26">
-        <f>C121-(C121/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>120500</v>
       </c>
       <c r="E121" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>WAITEC WT48/1 - GEAR - int. 4 WRITE 8 READ</v>
       </c>
       <c r="F121" s="10">
-        <f>C121/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>602500</v>
       </c>
       <c r="G121" s="19"/>
@@ -8353,15 +8353,15 @@
         <v>742000</v>
       </c>
       <c r="D122" s="26">
-        <f>C122-(C122/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>123666.66666666663</v>
       </c>
       <c r="E122" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>WAITEC 2036EI/1 - SOFTWARE  CD RISCRIVIBILE 2REW,2WRI,6READ, EIDE</v>
       </c>
       <c r="F122" s="10">
-        <f>C122/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>618333.33333333337</v>
       </c>
       <c r="G122" s="19"/>
@@ -8396,15 +8396,15 @@
         <v>778000</v>
       </c>
       <c r="D123" s="26">
-        <f>C123-(C123/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>129666.66666666663</v>
       </c>
       <c r="E123" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>RICOH MP6200ADP + SOFT.+5 CDR CD RISCRIVIBILE 2REW,2WRI,6R E-IDE</v>
       </c>
       <c r="F123" s="10">
-        <f>C123/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>648333.33333333337</v>
       </c>
       <c r="G123" s="19"/>
@@ -8439,15 +8439,15 @@
         <v>878000</v>
       </c>
       <c r="D124" s="26">
-        <f>C124-(C124/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>146333.33333333326</v>
       </c>
       <c r="E124" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>RICOH MP6200SR - SOFTWARE SCSI CD RISCRIVIBILE 2REW,2WRI,6READ, SCSI</v>
       </c>
       <c r="F124" s="10">
-        <f>C124/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>731666.66666666674</v>
       </c>
       <c r="G124" s="19"/>
@@ -8482,15 +8482,15 @@
         <v>883000</v>
       </c>
       <c r="D125" s="26">
-        <f>C125-(C125/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>147166.66666666663</v>
       </c>
       <c r="E125" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>WAITEC 2026/1 - SOFTWARE SCSI CD RISCRIVIBILE 2REW,2WRI,6READ, SCSI</v>
       </c>
       <c r="F125" s="10">
-        <f>C125/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>735833.33333333337</v>
       </c>
       <c r="G125" s="19"/>
@@ -8525,15 +8525,15 @@
         <v>913000</v>
       </c>
       <c r="D126" s="26">
-        <f>C126-(C126/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>152166.66666666663</v>
       </c>
       <c r="E126" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CDR 480i PLASMON EASY CD int. 4 WRITE 8 READ</v>
       </c>
       <c r="F126" s="10">
-        <f>C126/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>760833.33333333337</v>
       </c>
       <c r="G126" s="19"/>
@@ -8568,15 +8568,15 @@
         <v>1125000</v>
       </c>
       <c r="D127" s="26">
-        <f>C127-(C127/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>187500</v>
       </c>
       <c r="E127" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>CDR 480e PLASMON EASY CD ext. 4 WRITE 8 READ</v>
       </c>
       <c r="F127" s="10">
-        <f>C127/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>937500</v>
       </c>
       <c r="G127" s="19"/>
@@ -8609,15 +8609,15 @@
         <v>0</v>
       </c>
       <c r="D128" s="26">
-        <f>C128-(C128/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E128" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">MEMORIE </v>
       </c>
       <c r="F128" s="10">
-        <f>C128/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G128" s="19"/>
@@ -8650,15 +8650,15 @@
         <v>33000</v>
       </c>
       <c r="D129" s="26">
-        <f>C129-(C129/(1+$G$2))</f>
+        <f t="shared" si="3"/>
         <v>5500</v>
       </c>
       <c r="E129" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">SIMM 8MB 72 PIN (EDO) </v>
       </c>
       <c r="F129" s="10">
-        <f>C129/(1+$G$2)</f>
+        <f t="shared" si="4"/>
         <v>27500</v>
       </c>
       <c r="G129" s="19"/>
@@ -8691,15 +8691,15 @@
         <v>52000</v>
       </c>
       <c r="D130" s="26">
-        <f>C130-(C130/(1+$G$2))</f>
+        <f t="shared" ref="D130:D193" si="6">C130-(C130/(1+$G$2))</f>
         <v>8666.6666666666642</v>
       </c>
       <c r="E130" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve">SIMM 16MB 72 PIN (EDO) </v>
       </c>
       <c r="F130" s="10">
-        <f>C130/(1+$G$2)</f>
+        <f t="shared" ref="F130:F193" si="7">C130/(1+$G$2)</f>
         <v>43333.333333333336</v>
       </c>
       <c r="G130" s="19"/>
@@ -8732,15 +8732,15 @@
         <v>97000</v>
       </c>
       <c r="D131" s="26">
-        <f>C131-(C131/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>16166.666666666657</v>
       </c>
       <c r="E131" s="16" t="str">
-        <f t="shared" ref="E131:E194" si="2">A131 &amp; " " &amp; B131</f>
+        <f t="shared" ref="E131:E194" si="8">A131 &amp; " " &amp; B131</f>
         <v xml:space="preserve">SIMM 32MB 72 PIN (EDO) </v>
       </c>
       <c r="F131" s="10">
-        <f>C131/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>80833.333333333343</v>
       </c>
       <c r="G131" s="19"/>
@@ -8775,15 +8775,15 @@
         <v>0</v>
       </c>
       <c r="D132" s="26">
-        <f>C132-(C132/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E132" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">MODEM FAX - VIDEOCAMERA  </v>
       </c>
       <c r="F132" s="10">
-        <f>C132/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G132" s="19"/>
@@ -8818,15 +8818,15 @@
         <v>131000</v>
       </c>
       <c r="D133" s="26">
-        <f>C133-(C133/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>21833.333333333328</v>
       </c>
       <c r="E133" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F MOTOROLA 3400PRO 28800 EXT MOTOROLA</v>
       </c>
       <c r="F133" s="10">
-        <f>C133/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>109166.66666666667</v>
       </c>
       <c r="G133" s="19"/>
@@ -8861,15 +8861,15 @@
         <v>169000</v>
       </c>
       <c r="D134" s="26">
-        <f>C134-(C134/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>28166.666666666657</v>
       </c>
       <c r="E134" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F LEONARDO PC 33600 INT OEM DIGICOM</v>
       </c>
       <c r="F134" s="10">
-        <f>C134/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>140833.33333333334</v>
       </c>
       <c r="G134" s="19"/>
@@ -8904,15 +8904,15 @@
         <v>190000</v>
       </c>
       <c r="D135" s="26">
-        <f>C135-(C135/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>31666.666666666657</v>
       </c>
       <c r="E135" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F LEONARDO PC 33600 EXT DIGICOM</v>
       </c>
       <c r="F135" s="10">
-        <f>C135/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>158333.33333333334</v>
       </c>
       <c r="G135" s="19"/>
@@ -8947,15 +8947,15 @@
         <v>191000</v>
       </c>
       <c r="D136" s="26">
-        <f>C136-(C136/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>31833.333333333314</v>
       </c>
       <c r="E136" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F MOTOROLA 56K  EXT BULK MOTOROLA</v>
       </c>
       <c r="F136" s="10">
-        <f>C136/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>159166.66666666669</v>
       </c>
       <c r="G136" s="19"/>
@@ -8990,15 +8990,15 @@
         <v>197000</v>
       </c>
       <c r="D137" s="26">
-        <f>C137-(C137/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>32833.333333333314</v>
       </c>
       <c r="E137" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F LEONARDO PC 33600 INT DIGICOM</v>
       </c>
       <c r="F137" s="10">
-        <f>C137/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>164166.66666666669</v>
       </c>
       <c r="G137" s="19"/>
@@ -9033,15 +9033,15 @@
         <v>201000</v>
       </c>
       <c r="D138" s="26">
-        <f>C138-(C138/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>33500</v>
       </c>
       <c r="E138" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F TIZIANO 33600 EXT DIGICOM</v>
       </c>
       <c r="F138" s="10">
-        <f>C138/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>167500</v>
       </c>
       <c r="G138" s="19"/>
@@ -9076,15 +9076,15 @@
         <v>220000</v>
       </c>
       <c r="D139" s="26">
-        <f>C139-(C139/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>36666.666666666657</v>
       </c>
       <c r="E139" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F SPORTSTER FLASH 33600 EXT ITA  US ROBOTICS</v>
       </c>
       <c r="F139" s="10">
-        <f>C139/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>183333.33333333334</v>
       </c>
       <c r="G139" s="19"/>
@@ -9119,15 +9119,15 @@
         <v>250000</v>
       </c>
       <c r="D140" s="26">
-        <f>C140-(C140/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>41666.666666666657</v>
       </c>
       <c r="E140" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F MOTOROLA 56K  EXT MOTOROLA</v>
       </c>
       <c r="F140" s="10">
-        <f>C140/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>208333.33333333334</v>
       </c>
       <c r="G140" s="19"/>
@@ -9162,15 +9162,15 @@
         <v>257000</v>
       </c>
       <c r="D141" s="26">
-        <f>C141-(C141/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>42833.333333333314</v>
       </c>
       <c r="E141" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F LEONARDO  56K  EXT DIGICOM</v>
       </c>
       <c r="F141" s="10">
-        <f>C141/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>214166.66666666669</v>
       </c>
       <c r="G141" s="19"/>
@@ -9205,15 +9205,15 @@
         <v>278000</v>
       </c>
       <c r="D142" s="26">
-        <f>C142-(C142/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>46333.333333333314</v>
       </c>
       <c r="E142" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F TIZIANO 56K EXT DIGICOM</v>
       </c>
       <c r="F142" s="10">
-        <f>C142/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>231666.66666666669</v>
       </c>
       <c r="G142" s="19"/>
@@ -9248,15 +9248,15 @@
         <v>280000</v>
       </c>
       <c r="D143" s="26">
-        <f>C143-(C143/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>46666.666666666657</v>
       </c>
       <c r="E143" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F SPORTSTER MESSAGE PLUS US ROBOTICS</v>
       </c>
       <c r="F143" s="10">
-        <f>C143/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>233333.33333333334</v>
       </c>
       <c r="G143" s="19"/>
@@ -9291,15 +9291,15 @@
         <v>300000</v>
       </c>
       <c r="D144" s="26">
-        <f>C144-(C144/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>50000</v>
       </c>
       <c r="E144" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F LEONARDO PCMCIA 33600 DIGICOM</v>
       </c>
       <c r="F144" s="10">
-        <f>C144/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>250000</v>
       </c>
       <c r="G144" s="19"/>
@@ -9334,15 +9334,15 @@
         <v>305000</v>
       </c>
       <c r="D145" s="26">
-        <f>C145-(C145/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>50833.333333333314</v>
       </c>
       <c r="E145" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>KIT VIDEOCONFERENZA "GALILEO" DIGICOM / H.324</v>
       </c>
       <c r="F145" s="10">
-        <f>C145/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>254166.66666666669</v>
       </c>
       <c r="G145" s="19"/>
@@ -9377,15 +9377,15 @@
         <v>335000</v>
       </c>
       <c r="D146" s="26">
-        <f>C146-(C146/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>55833.333333333314</v>
       </c>
       <c r="E146" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>MODEM ISDN TINTORETTO EXT. DIGICOM</v>
       </c>
       <c r="F146" s="10">
-        <f>C146/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>279166.66666666669</v>
       </c>
       <c r="G146" s="19"/>
@@ -9420,15 +9420,15 @@
         <v>360000</v>
       </c>
       <c r="D147" s="26">
-        <f>C147-(C147/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>60000</v>
       </c>
       <c r="E147" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F LEONARDO PCMCIA 56K DIGICOM</v>
       </c>
       <c r="F147" s="10">
-        <f>C147/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>300000</v>
       </c>
       <c r="G147" s="19"/>
@@ -9463,15 +9463,15 @@
         <v>429000</v>
       </c>
       <c r="D148" s="26">
-        <f>C148-(C148/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>71500</v>
       </c>
       <c r="E148" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>MODEM MOTOROLA ISDN  EXT.64/128K MOTOROLA</v>
       </c>
       <c r="F148" s="10">
-        <f>C148/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>357500</v>
       </c>
       <c r="G148" s="19"/>
@@ -9506,15 +9506,15 @@
         <v>701000</v>
       </c>
       <c r="D149" s="26">
-        <f>C149-(C149/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>116833.33333333326</v>
       </c>
       <c r="E149" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>M/F ISDN DONATELLO EXT. DIGICOM</v>
       </c>
       <c r="F149" s="10">
-        <f>C149/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>584166.66666666674</v>
       </c>
       <c r="G149" s="19"/>
@@ -9547,15 +9547,15 @@
         <v>0</v>
       </c>
       <c r="D150" s="26">
-        <f>C150-(C150/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E150" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">MULTIMEDIA </v>
       </c>
       <c r="F150" s="10">
-        <f>C150/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G150" s="19"/>
@@ -9590,15 +9590,15 @@
         <v>90000</v>
       </c>
       <c r="D151" s="26">
-        <f>C151-(C151/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>15000</v>
       </c>
       <c r="E151" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SOUND AXP201/U PCI 64 Asus - ESS Maestro-1 Audio accellerator</v>
       </c>
       <c r="F151" s="10">
-        <f>C151/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>75000</v>
       </c>
       <c r="G151" s="19"/>
@@ -9633,15 +9633,15 @@
         <v>69000</v>
       </c>
       <c r="D152" s="26">
-        <f>C152-(C152/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>11500</v>
       </c>
       <c r="E152" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SOUND BLASTER 16 PnP  O.E.M. Creative</v>
       </c>
       <c r="F152" s="10">
-        <f>C152/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>57500</v>
       </c>
       <c r="G152" s="19"/>
@@ -9676,15 +9676,15 @@
         <v>89000</v>
       </c>
       <c r="D153" s="26">
-        <f>C153-(C153/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>14833.333333333328</v>
       </c>
       <c r="E153" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SOUND BLASTER 16 PnP NO IDE Creative</v>
       </c>
       <c r="F153" s="10">
-        <f>C153/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>74166.666666666672</v>
       </c>
       <c r="G153" s="19"/>
@@ -9719,15 +9719,15 @@
         <v>138000</v>
       </c>
       <c r="D154" s="26">
-        <f>C154-(C154/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>23000</v>
       </c>
       <c r="E154" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SOUND BLASTER AWE64 STD OEM Creative</v>
       </c>
       <c r="F154" s="10">
-        <f>C154/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>115000</v>
       </c>
       <c r="G154" s="19"/>
@@ -9762,15 +9762,15 @@
         <v>196000</v>
       </c>
       <c r="D155" s="26">
-        <f>C155-(C155/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>32666.666666666657</v>
       </c>
       <c r="E155" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SOUND BLASTER AWE64 STANDARD Creative</v>
       </c>
       <c r="F155" s="10">
-        <f>C155/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>163333.33333333334</v>
       </c>
       <c r="G155" s="19"/>
@@ -9805,15 +9805,15 @@
         <v>329000</v>
       </c>
       <c r="D156" s="26">
-        <f>C156-(C156/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>54833.333333333314</v>
       </c>
       <c r="E156" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SOUND BLASTER AWE64 GOLD PNP  Creative</v>
       </c>
       <c r="F156" s="10">
-        <f>C156/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>274166.66666666669</v>
       </c>
       <c r="G156" s="19"/>
@@ -9848,15 +9848,15 @@
         <v>295000</v>
       </c>
       <c r="D157" s="26">
-        <f>C157-(C157/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>49166.666666666657</v>
       </c>
       <c r="E157" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>KIT "DISCOVERY AWE64" 24X PNP Creative</v>
       </c>
       <c r="F157" s="10">
-        <f>C157/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>245833.33333333334</v>
       </c>
       <c r="G157" s="19"/>
@@ -9891,15 +9891,15 @@
         <v>19000</v>
       </c>
       <c r="D158" s="26">
-        <f>C158-(C158/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>3166.6666666666661</v>
       </c>
       <c r="E158" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SPEAKERS MLI-699 MLI-60</v>
       </c>
       <c r="F158" s="10">
-        <f>C158/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>15833.333333333334</v>
       </c>
       <c r="G158" s="19"/>
@@ -9934,15 +9934,15 @@
         <v>26000</v>
       </c>
       <c r="D159" s="26">
-        <f>C159-(C159/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>4333.3333333333321</v>
       </c>
       <c r="E159" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SPEAKER 25 W FS-60</v>
       </c>
       <c r="F159" s="10">
-        <f>C159/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>21666.666666666668</v>
       </c>
       <c r="G159" s="19"/>
@@ -9977,15 +9977,15 @@
         <v>28000</v>
       </c>
       <c r="D160" s="26">
-        <f>C160-(C160/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>4666.6666666666642</v>
       </c>
       <c r="E160" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>SPEAKER PROFESSIONAL 70 W FS-70</v>
       </c>
       <c r="F160" s="10">
-        <f>C160/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>23333.333333333336</v>
       </c>
       <c r="G160" s="19"/>
@@ -10020,15 +10020,15 @@
         <v>56000</v>
       </c>
       <c r="D161" s="26">
-        <f>C161-(C161/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>9333.3333333333285</v>
       </c>
       <c r="E161" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>ULTRA SPEAKER 130W FS-100</v>
       </c>
       <c r="F161" s="10">
-        <f>C161/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>46666.666666666672</v>
       </c>
       <c r="G161" s="19"/>
@@ -10061,15 +10061,15 @@
         <v>0</v>
       </c>
       <c r="D162" s="26">
-        <f>C162-(C162/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E162" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">MICROPROCESSORI </v>
       </c>
       <c r="F162" s="10">
-        <f>C162/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G162" s="19"/>
@@ -10102,15 +10102,15 @@
         <v>216000</v>
       </c>
       <c r="D163" s="26">
-        <f>C163-(C163/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>36000</v>
       </c>
       <c r="E163" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM 166 INTEL MMX </v>
       </c>
       <c r="F163" s="10">
-        <f>C163/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>180000</v>
       </c>
       <c r="G163" s="19"/>
@@ -10143,15 +10143,15 @@
         <v>250000</v>
       </c>
       <c r="D164" s="26">
-        <f>C164-(C164/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>41666.666666666657</v>
       </c>
       <c r="E164" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM 200 INTEL MMX </v>
       </c>
       <c r="F164" s="10">
-        <f>C164/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>208333.33333333334</v>
       </c>
       <c r="G164" s="19"/>
@@ -10184,15 +10184,15 @@
         <v>382000</v>
       </c>
       <c r="D165" s="26">
-        <f>C165-(C165/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>63666.666666666628</v>
       </c>
       <c r="E165" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM 233 INTEL MMX </v>
       </c>
       <c r="F165" s="10">
-        <f>C165/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>318333.33333333337</v>
       </c>
       <c r="G165" s="19"/>
@@ -10225,15 +10225,15 @@
         <v>524000</v>
       </c>
       <c r="D166" s="26">
-        <f>C166-(C166/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>87333.333333333314</v>
       </c>
       <c r="E166" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM II 233 INTEL 512k </v>
       </c>
       <c r="F166" s="10">
-        <f>C166/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>436666.66666666669</v>
       </c>
       <c r="G166" s="19"/>
@@ -10266,15 +10266,15 @@
         <v>757000</v>
       </c>
       <c r="D167" s="26">
-        <f>C167-(C167/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>126166.66666666663</v>
       </c>
       <c r="E167" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM II 266 INTEL 512k </v>
       </c>
       <c r="F167" s="10">
-        <f>C167/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>630833.33333333337</v>
       </c>
       <c r="G167" s="19"/>
@@ -10307,15 +10307,15 @@
         <v>1045000</v>
       </c>
       <c r="D168" s="26">
-        <f>C168-(C168/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>174166.66666666663</v>
       </c>
       <c r="E168" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM II 300 INTEL 512K </v>
       </c>
       <c r="F168" s="10">
-        <f>C168/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>870833.33333333337</v>
       </c>
       <c r="G168" s="19"/>
@@ -10348,15 +10348,15 @@
         <v>1568000</v>
       </c>
       <c r="D169" s="26">
-        <f>C169-(C169/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>261333.33333333326</v>
       </c>
       <c r="E169" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM II 333 INTEL 512K </v>
       </c>
       <c r="F169" s="10">
-        <f>C169/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>1306666.6666666667</v>
       </c>
       <c r="G169" s="19"/>
@@ -10389,15 +10389,15 @@
         <v>117000</v>
       </c>
       <c r="D170" s="26">
-        <f>C170-(C170/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>19500</v>
       </c>
       <c r="E170" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">SGS P 166+ </v>
       </c>
       <c r="F170" s="10">
-        <f>C170/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>97500</v>
       </c>
       <c r="G170" s="19"/>
@@ -10430,15 +10430,15 @@
         <v>158000</v>
       </c>
       <c r="D171" s="26">
-        <f>C171-(C171/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>26333.333333333314</v>
       </c>
       <c r="E171" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">IBM 200 MX </v>
       </c>
       <c r="F171" s="10">
-        <f>C171/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>131666.66666666669</v>
       </c>
       <c r="G171" s="19"/>
@@ -10471,15 +10471,15 @@
         <v>260000</v>
       </c>
       <c r="D172" s="26">
-        <f>C172-(C172/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>43333.333333333314</v>
       </c>
       <c r="E172" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">IBM 233 MX </v>
       </c>
       <c r="F172" s="10">
-        <f>C172/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>216666.66666666669</v>
       </c>
       <c r="G172" s="19"/>
@@ -10512,15 +10512,15 @@
         <v>193000</v>
       </c>
       <c r="D173" s="26">
-        <f>C173-(C173/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>32166.666666666657</v>
       </c>
       <c r="E173" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">AMD K6-166 </v>
       </c>
       <c r="F173" s="10">
-        <f>C173/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>160833.33333333334</v>
       </c>
       <c r="G173" s="19"/>
@@ -10553,15 +10553,15 @@
         <v>270000</v>
       </c>
       <c r="D174" s="26">
-        <f>C174-(C174/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>45000</v>
       </c>
       <c r="E174" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">AMD K6-200 </v>
       </c>
       <c r="F174" s="10">
-        <f>C174/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>225000</v>
       </c>
       <c r="G174" s="19"/>
@@ -10594,15 +10594,15 @@
         <v>314000</v>
       </c>
       <c r="D175" s="26">
-        <f>C175-(C175/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>52333.333333333314</v>
       </c>
       <c r="E175" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">AMD K6-233 </v>
       </c>
       <c r="F175" s="10">
-        <f>C175/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>261666.66666666669</v>
       </c>
       <c r="G175" s="19"/>
@@ -10635,15 +10635,15 @@
         <v>894000</v>
       </c>
       <c r="D176" s="26">
-        <f>C176-(C176/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>149000</v>
       </c>
       <c r="E176" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM PRO 180 MZH </v>
       </c>
       <c r="F176" s="10">
-        <f>C176/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>745000</v>
       </c>
       <c r="G176" s="19"/>
@@ -10676,15 +10676,15 @@
         <v>1040000</v>
       </c>
       <c r="D177" s="26">
-        <f>C177-(C177/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>173333.33333333326</v>
       </c>
       <c r="E177" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">PENTIUM PRO 200 MZH </v>
       </c>
       <c r="F177" s="10">
-        <f>C177/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>866666.66666666674</v>
       </c>
       <c r="G177" s="19"/>
@@ -10717,15 +10717,15 @@
         <v>8000</v>
       </c>
       <c r="D178" s="26">
-        <f>C178-(C178/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>1333.333333333333</v>
       </c>
       <c r="E178" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">VENTOLINA PENTIUM 75-166 </v>
       </c>
       <c r="F178" s="10">
-        <f>C178/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>6666.666666666667</v>
       </c>
       <c r="G178" s="19"/>
@@ -10758,15 +10758,15 @@
         <v>10000</v>
       </c>
       <c r="D179" s="26">
-        <f>C179-(C179/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>1666.6666666666661</v>
       </c>
       <c r="E179" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">VENTOLINA PENTIUM 200 </v>
       </c>
       <c r="F179" s="10">
-        <f>C179/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>8333.3333333333339</v>
       </c>
       <c r="G179" s="19"/>
@@ -10799,15 +10799,15 @@
         <v>24000</v>
       </c>
       <c r="D180" s="26">
-        <f>C180-(C180/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>4000</v>
       </c>
       <c r="E180" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">VENTOLA PER PENTIUM PRO </v>
       </c>
       <c r="F180" s="10">
-        <f>C180/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>20000</v>
       </c>
       <c r="G180" s="19"/>
@@ -10842,15 +10842,15 @@
         <v>11000</v>
       </c>
       <c r="D181" s="26">
-        <f>C181-(C181/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>1833.3333333333321</v>
       </c>
       <c r="E181" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">VENTOLINA PER IBM/CYRIX 686  </v>
       </c>
       <c r="F181" s="10">
-        <f>C181/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>9166.6666666666679</v>
       </c>
       <c r="G181" s="19"/>
@@ -10885,15 +10885,15 @@
         <v>10000</v>
       </c>
       <c r="D182" s="26">
-        <f>C182-(C182/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>1666.6666666666661</v>
       </c>
       <c r="E182" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">VENTOLA 3 PIN per TX97  </v>
       </c>
       <c r="F182" s="10">
-        <f>C182/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>8333.3333333333339</v>
       </c>
       <c r="G182" s="19"/>
@@ -10928,15 +10928,15 @@
         <v>26000</v>
       </c>
       <c r="D183" s="26">
-        <f>C183-(C183/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>4333.3333333333321</v>
       </c>
       <c r="E183" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">VENTOLA PENTIUM II  </v>
       </c>
       <c r="F183" s="10">
-        <f>C183/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>21666.666666666668</v>
       </c>
       <c r="G183" s="19"/>
@@ -10969,15 +10969,15 @@
         <v>0</v>
       </c>
       <c r="D184" s="26">
-        <f>C184-(C184/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E184" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">TASTIERE </v>
       </c>
       <c r="F184" s="10">
-        <f>C184/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G184" s="19"/>
@@ -11012,15 +11012,15 @@
         <v>22000</v>
       </c>
       <c r="D185" s="26">
-        <f>C185-(C185/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>3666.6666666666642</v>
       </c>
       <c r="E185" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>TAST. ITA 105 TASTI WIN 95 UNIKEY</v>
       </c>
       <c r="F185" s="10">
-        <f>C185/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>18333.333333333336</v>
       </c>
       <c r="G185" s="19"/>
@@ -11055,15 +11055,15 @@
         <v>63000</v>
       </c>
       <c r="D186" s="26">
-        <f>C186-(C186/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>10500</v>
       </c>
       <c r="E186" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>TAST. ITA   79t BTC</v>
       </c>
       <c r="F186" s="10">
-        <f>C186/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>52500</v>
       </c>
       <c r="G186" s="19"/>
@@ -11098,15 +11098,15 @@
         <v>63000</v>
       </c>
       <c r="D187" s="26">
-        <f>C187-(C187/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>10500</v>
       </c>
       <c r="E187" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>TAST. USA 79t BTC</v>
       </c>
       <c r="F187" s="10">
-        <f>C187/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>52500</v>
       </c>
       <c r="G187" s="19"/>
@@ -11141,15 +11141,15 @@
         <v>26000</v>
       </c>
       <c r="D188" s="26">
-        <f>C188-(C188/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>4333.3333333333321</v>
       </c>
       <c r="E188" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>TAST. USA 105 TASTI WIN95 BTC</v>
       </c>
       <c r="F188" s="10">
-        <f>C188/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>21666.666666666668</v>
       </c>
       <c r="G188" s="19"/>
@@ -11184,15 +11184,15 @@
         <v>25000</v>
       </c>
       <c r="D189" s="26">
-        <f>C189-(C189/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>4166.6666666666642</v>
       </c>
       <c r="E189" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>TAST. ITA  105 TASTI NMB, WIN95 NMB</v>
       </c>
       <c r="F189" s="10">
-        <f>C189/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>20833.333333333336</v>
       </c>
       <c r="G189" s="19"/>
@@ -11227,15 +11227,15 @@
         <v>25000</v>
       </c>
       <c r="D190" s="26">
-        <f>C190-(C190/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>4166.6666666666642</v>
       </c>
       <c r="E190" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>TAST. ITA  105 TASTI NMB, PS/2 WIN95 NMB</v>
       </c>
       <c r="F190" s="10">
-        <f>C190/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>20833.333333333336</v>
       </c>
       <c r="G190" s="19"/>
@@ -11270,15 +11270,15 @@
         <v>46000</v>
       </c>
       <c r="D191" s="26">
-        <f>C191-(C191/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>7666.6666666666642</v>
       </c>
       <c r="E191" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>TAST. ITA 105 TASTI "CYPRESS"  WIN95 NMB</v>
       </c>
       <c r="F191" s="10">
-        <f>C191/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>38333.333333333336</v>
       </c>
       <c r="G191" s="19"/>
@@ -11311,15 +11311,15 @@
         <v>0</v>
       </c>
       <c r="D192" s="26">
-        <f>C192-(C192/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E192" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">SCANNER E ACCESSORI </v>
       </c>
       <c r="F192" s="10">
-        <f>C192/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G192" s="19"/>
@@ -11354,15 +11354,15 @@
         <v>37000</v>
       </c>
       <c r="D193" s="26">
-        <f>C193-(C193/(1+$G$2))</f>
+        <f t="shared" si="6"/>
         <v>6166.6666666666642</v>
       </c>
       <c r="E193" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>MOUSE  PILOT SERIALE LOGITECH</v>
       </c>
       <c r="F193" s="10">
-        <f>C193/(1+$G$2)</f>
+        <f t="shared" si="7"/>
         <v>30833.333333333336</v>
       </c>
       <c r="G193" s="19"/>
@@ -11397,15 +11397,15 @@
         <v>37000</v>
       </c>
       <c r="D194" s="26">
-        <f>C194-(C194/(1+$G$2))</f>
+        <f t="shared" ref="D194:D257" si="9">C194-(C194/(1+$G$2))</f>
         <v>6166.6666666666642</v>
       </c>
       <c r="E194" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>MOUSE  PILOT P/S2 LOGITECH</v>
       </c>
       <c r="F194" s="10">
-        <f>C194/(1+$G$2)</f>
+        <f t="shared" ref="F194:F257" si="10">C194/(1+$G$2)</f>
         <v>30833.333333333336</v>
       </c>
       <c r="G194" s="19"/>
@@ -11440,15 +11440,15 @@
         <v>11000</v>
       </c>
       <c r="D195" s="26">
-        <f>C195-(C195/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>1833.3333333333321</v>
       </c>
       <c r="E195" s="16" t="str">
-        <f t="shared" ref="E195:E258" si="3">A195 &amp; " " &amp; B195</f>
+        <f t="shared" ref="E195:E258" si="11">A195 &amp; " " &amp; B195</f>
         <v>MOUSE SERIALE 3 TASTI PRIMAX</v>
       </c>
       <c r="F195" s="10">
-        <f>C195/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>9166.6666666666679</v>
       </c>
       <c r="G195" s="19"/>
@@ -11483,15 +11483,15 @@
         <v>46000</v>
       </c>
       <c r="D196" s="26">
-        <f>C196-(C196/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>7666.6666666666642</v>
       </c>
       <c r="E196" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>MOUSE TRACKBALL  PRIMAX</v>
       </c>
       <c r="F196" s="10">
-        <f>C196/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>38333.333333333336</v>
       </c>
       <c r="G196" s="19"/>
@@ -11526,15 +11526,15 @@
         <v>19000</v>
       </c>
       <c r="D197" s="26">
-        <f>C197-(C197/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>3166.6666666666661</v>
       </c>
       <c r="E197" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>MOUSE "RAINBOW" SERIALE PRIMAX</v>
       </c>
       <c r="F197" s="10">
-        <f>C197/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>15833.333333333334</v>
       </c>
       <c r="G197" s="19"/>
@@ -11569,15 +11569,15 @@
         <v>13000</v>
       </c>
       <c r="D198" s="26">
-        <f>C198-(C198/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>2166.6666666666661</v>
       </c>
       <c r="E198" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>MOUSE  ECHO PS/2 PRIMAX</v>
       </c>
       <c r="F198" s="10">
-        <f>C198/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>10833.333333333334</v>
       </c>
       <c r="G198" s="19"/>
@@ -11612,15 +11612,15 @@
         <v>26000</v>
       </c>
       <c r="D199" s="26">
-        <f>C199-(C199/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>4333.3333333333321</v>
       </c>
       <c r="E199" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>VENUS MOUSE SERIALE PRIMAX</v>
       </c>
       <c r="F199" s="10">
-        <f>C199/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>21666.666666666668</v>
       </c>
       <c r="G199" s="19"/>
@@ -11655,15 +11655,15 @@
         <v>26000</v>
       </c>
       <c r="D200" s="26">
-        <f>C200-(C200/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>4333.3333333333321</v>
       </c>
       <c r="E200" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>VENUS MOUSE PS/2 PRIMAX</v>
       </c>
       <c r="F200" s="10">
-        <f>C200/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>21666.666666666668</v>
       </c>
       <c r="G200" s="19"/>
@@ -11698,15 +11698,15 @@
         <v>20000</v>
       </c>
       <c r="D201" s="26">
-        <f>C201-(C201/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>3333.3333333333321</v>
       </c>
       <c r="E201" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>JOYSTICK DIGITALE PRIMAX</v>
       </c>
       <c r="F201" s="10">
-        <f>C201/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>16666.666666666668</v>
       </c>
       <c r="G201" s="19"/>
@@ -11741,15 +11741,15 @@
         <v>49000</v>
       </c>
       <c r="D202" s="26">
-        <f>C202-(C202/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>8166.6666666666642</v>
       </c>
       <c r="E202" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>JOYSTICK ULTRASTRIKER PRIMAX</v>
       </c>
       <c r="F202" s="10">
-        <f>C202/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>40833.333333333336</v>
       </c>
       <c r="G202" s="19"/>
@@ -11784,15 +11784,15 @@
         <v>33000</v>
       </c>
       <c r="D203" s="26">
-        <f>C203-(C203/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>5500</v>
       </c>
       <c r="E203" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>NAVIGATOR MOUSE PRIMAX</v>
       </c>
       <c r="F203" s="10">
-        <f>C203/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>27500</v>
       </c>
       <c r="G203" s="19"/>
@@ -11827,15 +11827,15 @@
         <v>68000</v>
       </c>
       <c r="D204" s="26">
-        <f>C204-(C204/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>11333.333333333328</v>
       </c>
       <c r="E204" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>JOYSTICK EXCALIBUR PRIMAX</v>
       </c>
       <c r="F204" s="10">
-        <f>C204/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>56666.666666666672</v>
       </c>
       <c r="G204" s="19"/>
@@ -11870,15 +11870,15 @@
         <v>33000</v>
       </c>
       <c r="D205" s="26">
-        <f>C205-(C205/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>5500</v>
       </c>
       <c r="E205" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>GAMEPAD CONQUEROR PRIMAX</v>
       </c>
       <c r="F205" s="10">
-        <f>C205/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>27500</v>
       </c>
       <c r="G205" s="19"/>
@@ -11913,15 +11913,15 @@
         <v>147000</v>
       </c>
       <c r="D206" s="26">
-        <f>C206-(C206/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>24500</v>
       </c>
       <c r="E206" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>COLOR HAND SCANNER PRIMAX</v>
       </c>
       <c r="F206" s="10">
-        <f>C206/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>122500</v>
       </c>
       <c r="G206" s="19"/>
@@ -11956,15 +11956,15 @@
         <v>151000</v>
       </c>
       <c r="D207" s="26">
-        <f>C207-(C207/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>25166.666666666657</v>
       </c>
       <c r="E207" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>SCANNER COLORADO 4800 SW + OCR  PRIMAX</v>
       </c>
       <c r="F207" s="10">
-        <f>C207/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>125833.33333333334</v>
       </c>
       <c r="G207" s="19"/>
@@ -11999,15 +11999,15 @@
         <v>197000</v>
       </c>
       <c r="D208" s="26">
-        <f>C208-(C208/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>32833.333333333314</v>
       </c>
       <c r="E208" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>SCANNER COLORADO D600 SW + OCR  PRIMAX</v>
       </c>
       <c r="F208" s="10">
-        <f>C208/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>164166.66666666669</v>
       </c>
       <c r="G208" s="19"/>
@@ -12042,15 +12042,15 @@
         <v>310000</v>
       </c>
       <c r="D209" s="26">
-        <f>C209-(C209/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>51666.666666666657</v>
       </c>
       <c r="E209" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>SCANNER  DIRECT 9600 SW + OCR PRIMAX</v>
       </c>
       <c r="F209" s="10">
-        <f>C209/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>258333.33333333334</v>
       </c>
       <c r="G209" s="19"/>
@@ -12085,15 +12085,15 @@
         <v>271000</v>
       </c>
       <c r="D210" s="26">
-        <f>C210-(C210/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>45166.666666666657</v>
       </c>
       <c r="E210" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>SCANNER  JEWEL 4800 SCSI PRIMAX</v>
       </c>
       <c r="F210" s="10">
-        <f>C210/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>225833.33333333334</v>
       </c>
       <c r="G210" s="19"/>
@@ -12128,15 +12128,15 @@
         <v>458000</v>
       </c>
       <c r="D211" s="26">
-        <f>C211-(C211/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>76333.333333333314</v>
       </c>
       <c r="E211" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>SCANNER PROFI  9600 SCSI PRIMAX</v>
       </c>
       <c r="F211" s="10">
-        <f>C211/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>381666.66666666669</v>
       </c>
       <c r="G211" s="19"/>
@@ -12171,15 +12171,15 @@
         <v>412000</v>
       </c>
       <c r="D212" s="26">
-        <f>C212-(C212/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>68666.666666666628</v>
       </c>
       <c r="E212" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>SCANNER PHODOX U. S. 300 PRIMAX</v>
       </c>
       <c r="F212" s="10">
-        <f>C212/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>343333.33333333337</v>
       </c>
       <c r="G212" s="19"/>
@@ -12214,15 +12214,15 @@
         <v>807000</v>
       </c>
       <c r="D213" s="26">
-        <f>C213-(C213/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>134500</v>
       </c>
       <c r="E213" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>FILMSCAN-200PC EPSON</v>
       </c>
       <c r="F213" s="10">
-        <f>C213/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>672500</v>
       </c>
       <c r="G213" s="19"/>
@@ -12255,15 +12255,15 @@
         <v>4000</v>
       </c>
       <c r="D214" s="26">
-        <f>C214-(C214/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>666.66666666666652</v>
       </c>
       <c r="E214" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">TAPPETINO PER MOUSE </v>
       </c>
       <c r="F214" s="10">
-        <f>C214/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>3333.3333333333335</v>
       </c>
       <c r="G214" s="19"/>
@@ -12296,15 +12296,15 @@
         <v>81000</v>
       </c>
       <c r="D215" s="26">
-        <f>C215-(C215/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>13500</v>
       </c>
       <c r="E215" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">ALIMENTATORE 200 W CE </v>
       </c>
       <c r="F215" s="10">
-        <f>C215/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>67500</v>
       </c>
       <c r="G215" s="19"/>
@@ -12337,15 +12337,15 @@
         <v>125000</v>
       </c>
       <c r="D216" s="26">
-        <f>C216-(C216/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>20833.333333333328</v>
       </c>
       <c r="E216" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">ALIMENTATORE 250 W CE ATX </v>
       </c>
       <c r="F216" s="10">
-        <f>C216/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>104166.66666666667</v>
       </c>
       <c r="G216" s="19"/>
@@ -12378,15 +12378,15 @@
         <v>98000</v>
       </c>
       <c r="D217" s="26">
-        <f>C217-(C217/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>16333.333333333328</v>
       </c>
       <c r="E217" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">ALIMENTATORE 230 W CE ATX </v>
       </c>
       <c r="F217" s="10">
-        <f>C217/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>81666.666666666672</v>
       </c>
       <c r="G217" s="19"/>
@@ -12419,15 +12419,15 @@
         <v>140000</v>
       </c>
       <c r="D218" s="26">
-        <f>C218-(C218/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>23333.333333333328</v>
       </c>
       <c r="E218" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">ALIMENTATORE 300 W CE ATX </v>
       </c>
       <c r="F218" s="10">
-        <f>C218/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>116666.66666666667</v>
       </c>
       <c r="G218" s="19"/>
@@ -12462,15 +12462,15 @@
         <v>5000</v>
       </c>
       <c r="D219" s="26">
-        <f>C219-(C219/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>833.33333333333303</v>
       </c>
       <c r="E219" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>CAVO PARALLELO STAMP. MT 1,8 Unidirez.</v>
       </c>
       <c r="F219" s="10">
-        <f>C219/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>4166.666666666667</v>
       </c>
       <c r="G219" s="19"/>
@@ -12505,15 +12505,15 @@
         <v>6000</v>
       </c>
       <c r="D220" s="26">
-        <f>C220-(C220/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>1000</v>
       </c>
       <c r="E220" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>CAVO PARALLELO STAMP. MT 1,8 Bidirez.</v>
       </c>
       <c r="F220" s="10">
-        <f>C220/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>5000</v>
       </c>
       <c r="G220" s="19"/>
@@ -12546,15 +12546,15 @@
         <v>9000</v>
       </c>
       <c r="D221" s="26">
-        <f>C221-(C221/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>1500</v>
       </c>
       <c r="E221" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">CAVO PARALLELO STAMP. MT 3 </v>
       </c>
       <c r="F221" s="10">
-        <f>C221/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>7500</v>
       </c>
       <c r="G221" s="19"/>
@@ -12589,15 +12589,15 @@
         <v>8000</v>
       </c>
       <c r="D222" s="26">
-        <f>C222-(C222/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>1333.333333333333</v>
       </c>
       <c r="E222" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>CONNETTORE MOUSE PS/2 per M/B ASUS P55T2P4</v>
       </c>
       <c r="F222" s="10">
-        <f>C222/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>6666.666666666667</v>
       </c>
       <c r="G222" s="19"/>
@@ -12630,15 +12630,15 @@
         <v>11000</v>
       </c>
       <c r="D223" s="26">
-        <f>C223-(C223/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>1833.3333333333321</v>
       </c>
       <c r="E223" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">CONNETTORE TASTIERA PS/2 </v>
       </c>
       <c r="F223" s="10">
-        <f>C223/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>9166.6666666666679</v>
       </c>
       <c r="G223" s="19"/>
@@ -12673,15 +12673,15 @@
         <v>21000</v>
       </c>
       <c r="D224" s="26">
-        <f>C224-(C224/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>3500</v>
       </c>
       <c r="E224" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>CONNETTORE USB/MIR per M/B ASUS TX97</v>
       </c>
       <c r="F224" s="10">
-        <f>C224/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>17500</v>
       </c>
       <c r="G224" s="19"/>
@@ -12716,15 +12716,15 @@
         <v>14000</v>
       </c>
       <c r="D225" s="26">
-        <f>C225-(C225/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>2333.3333333333321</v>
       </c>
       <c r="E225" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>DATA-SWITCH 2/1 MANUALE PRIMAX</v>
       </c>
       <c r="F225" s="10">
-        <f>C225/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>11666.666666666668</v>
       </c>
       <c r="G225" s="19"/>
@@ -12759,15 +12759,15 @@
         <v>23000</v>
       </c>
       <c r="D226" s="26">
-        <f>C226-(C226/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>3833.3333333333321</v>
       </c>
       <c r="E226" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>DATA-SWITCH 2/2 MANUALE PRIMAX</v>
       </c>
       <c r="F226" s="10">
-        <f>C226/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>19166.666666666668</v>
       </c>
       <c r="G226" s="19"/>
@@ -12802,15 +12802,15 @@
         <v>51000</v>
       </c>
       <c r="D227" s="26">
-        <f>C227-(C227/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>8500</v>
       </c>
       <c r="E227" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>DATA-SWITCH 2/1 BIDIREZ. PRIMAX</v>
       </c>
       <c r="F227" s="10">
-        <f>C227/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>42500</v>
       </c>
       <c r="G227" s="19"/>
@@ -12843,15 +12843,15 @@
         <v>0</v>
       </c>
       <c r="D228" s="26">
-        <f>C228-(C228/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E228" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">SOFTWARE </v>
       </c>
       <c r="F228" s="10">
-        <f>C228/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G228" s="19"/>
@@ -12886,15 +12886,15 @@
         <v>198000</v>
       </c>
       <c r="D229" s="26">
-        <f>C229-(C229/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>33000</v>
       </c>
       <c r="E229" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>COMBO DOS6.22+WIN3.11+DSK.MAN. MICROSOFT  OEM</v>
       </c>
       <c r="F229" s="10">
-        <f>C229/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>165000</v>
       </c>
       <c r="G229" s="19"/>
@@ -12929,15 +12929,15 @@
         <v>167000</v>
       </c>
       <c r="D230" s="26">
-        <f>C230-(C230/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>27833.333333333314</v>
       </c>
       <c r="E230" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>WINDOWS 95, MANUALI + CD MICROSOFT  OEM</v>
       </c>
       <c r="F230" s="10">
-        <f>C230/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>139166.66666666669</v>
       </c>
       <c r="G230" s="19"/>
@@ -12972,15 +12972,15 @@
         <v>95000</v>
       </c>
       <c r="D231" s="26">
-        <f>C231-(C231/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>15833.333333333328</v>
       </c>
       <c r="E231" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>LICENZA STUDENTE SISTEMI  MICROSOFT  STUDENTE</v>
       </c>
       <c r="F231" s="10">
-        <f>C231/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>79166.666666666672</v>
       </c>
       <c r="G231" s="19"/>
@@ -13015,15 +13015,15 @@
         <v>141000</v>
       </c>
       <c r="D232" s="26">
-        <f>C232-(C232/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>23500</v>
       </c>
       <c r="E232" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>LICENZA STUDENTE APPLICAZIONI MICROSOFT  STUDENTE</v>
       </c>
       <c r="F232" s="10">
-        <f>C232/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>117500</v>
       </c>
       <c r="G232" s="19"/>
@@ -13058,15 +13058,15 @@
         <v>351000</v>
       </c>
       <c r="D233" s="26">
-        <f>C233-(C233/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>58500</v>
       </c>
       <c r="E233" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>WIN NT WORKSTATION 4.0 MICROSOFT  OEM</v>
       </c>
       <c r="F233" s="10">
-        <f>C233/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>292500</v>
       </c>
       <c r="G233" s="19"/>
@@ -13101,15 +13101,15 @@
         <v>414000</v>
       </c>
       <c r="D234" s="26">
-        <f>C234-(C234/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>69000</v>
       </c>
       <c r="E234" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>OFFICE SMALL BUSINESS WORD97,EXCEL97,OUTLOOK97,PUBLISHER97</v>
       </c>
       <c r="F234" s="10">
-        <f>C234/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>345000</v>
       </c>
       <c r="G234" s="19"/>
@@ -13144,15 +13144,15 @@
         <v>61000</v>
       </c>
       <c r="D235" s="26">
-        <f>C235-(C235/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>10166.666666666664</v>
       </c>
       <c r="E235" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>WORKS 4.5 ITA, MANUALI + CD MICROSOFT  OEM</v>
       </c>
       <c r="F235" s="10">
-        <f>C235/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>50833.333333333336</v>
       </c>
       <c r="G235" s="19"/>
@@ -13187,15 +13187,15 @@
         <v>893000</v>
       </c>
       <c r="D236" s="26">
-        <f>C236-(C236/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>148833.33333333326</v>
       </c>
       <c r="E236" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>FIVE PACK WIN 95 MICROSOFT  OEM</v>
       </c>
       <c r="F236" s="10">
-        <f>C236/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>744166.66666666674</v>
       </c>
       <c r="G236" s="19"/>
@@ -13230,15 +13230,15 @@
         <v>985000</v>
       </c>
       <c r="D237" s="26">
-        <f>C237-(C237/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>164166.66666666663</v>
       </c>
       <c r="E237" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>FIVE PACK COMBO WIN3.11-DOS MICROSOFT  OEM</v>
       </c>
       <c r="F237" s="10">
-        <f>C237/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>820833.33333333337</v>
       </c>
       <c r="G237" s="19"/>
@@ -13273,15 +13273,15 @@
         <v>296000</v>
       </c>
       <c r="D238" s="26">
-        <f>C238-(C238/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>49333.333333333314</v>
       </c>
       <c r="E238" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>FIVE PACK WORKS 4.5 MICROSOFT  OEM</v>
       </c>
       <c r="F238" s="10">
-        <f>C238/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>246666.66666666669</v>
       </c>
       <c r="G238" s="19"/>
@@ -13316,15 +13316,15 @@
         <v>685000</v>
       </c>
       <c r="D239" s="26">
-        <f>C239-(C239/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>114166.66666666663</v>
       </c>
       <c r="E239" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>3-PACK  HOME ESSENTIALS 98 MICROSOFT  OEM</v>
       </c>
       <c r="F239" s="10">
-        <f>C239/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>570833.33333333337</v>
       </c>
       <c r="G239" s="19"/>
@@ -13359,15 +13359,15 @@
         <v>1138000</v>
       </c>
       <c r="D240" s="26">
-        <f>C240-(C240/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>189666.66666666663</v>
       </c>
       <c r="E240" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>3-PACK WIN NT WORKSTATION 4.0 MICROSOFT  OEM</v>
       </c>
       <c r="F240" s="10">
-        <f>C240/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>948333.33333333337</v>
       </c>
       <c r="G240" s="19"/>
@@ -13402,15 +13402,15 @@
         <v>1334000</v>
       </c>
       <c r="D241" s="26">
-        <f>C241-(C241/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>222333.33333333326</v>
       </c>
       <c r="E241" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>3-PACK OFFICE SMALL BUSINESS MICROSOFT  OEM</v>
       </c>
       <c r="F241" s="10">
-        <f>C241/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>1111666.6666666667</v>
       </c>
       <c r="G241" s="19"/>
@@ -13445,15 +13445,15 @@
         <v>30000</v>
       </c>
       <c r="D242" s="26">
-        <f>C242-(C242/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>5000</v>
       </c>
       <c r="E242" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">CD VIDEOGUIDA  WIN'95  </v>
       </c>
       <c r="F242" s="10">
-        <f>C242/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>25000</v>
       </c>
       <c r="G242" s="19"/>
@@ -13488,15 +13488,15 @@
         <v>30000</v>
       </c>
       <c r="D243" s="26">
-        <f>C243-(C243/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>5000</v>
       </c>
       <c r="E243" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v xml:space="preserve">CD VIDEGUIDA INTERNET  </v>
       </c>
       <c r="F243" s="10">
-        <f>C243/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>25000</v>
       </c>
       <c r="G243" s="19"/>
@@ -13531,15 +13531,15 @@
         <v>406000</v>
       </c>
       <c r="D244" s="26">
-        <f>C244-(C244/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>67666.666666666628</v>
       </c>
       <c r="E244" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>WINDOWS 95  MICROSOFT</v>
       </c>
       <c r="F244" s="10">
-        <f>C244/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>338333.33333333337</v>
       </c>
       <c r="G244" s="19"/>
@@ -13574,15 +13574,15 @@
         <v>197000</v>
       </c>
       <c r="D245" s="26">
-        <f>C245-(C245/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>32833.333333333314</v>
       </c>
       <c r="E245" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>WINDOWS 95 Lic. Agg. MICROSOFT</v>
       </c>
       <c r="F245" s="10">
-        <f>C245/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>164166.66666666669</v>
       </c>
       <c r="G245" s="19"/>
@@ -13617,15 +13617,15 @@
         <v>645000</v>
       </c>
       <c r="D246" s="26">
-        <f>C246-(C246/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>107500</v>
       </c>
       <c r="E246" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>EXCEL 7.0 MICROSOFT</v>
       </c>
       <c r="F246" s="10">
-        <f>C246/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>537500</v>
       </c>
       <c r="G246" s="19"/>
@@ -13660,15 +13660,15 @@
         <v>645000</v>
       </c>
       <c r="D247" s="26">
-        <f>C247-(C247/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>107500</v>
       </c>
       <c r="E247" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>EXCEL 97 MICROSOFT</v>
       </c>
       <c r="F247" s="10">
-        <f>C247/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>537500</v>
       </c>
       <c r="G247" s="19"/>
@@ -13703,15 +13703,15 @@
         <v>259000</v>
       </c>
       <c r="D248" s="26">
-        <f>C248-(C248/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>43166.666666666657</v>
       </c>
       <c r="E248" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>EXCEL 97 Agg. MICROSOFT</v>
       </c>
       <c r="F248" s="10">
-        <f>C248/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>215833.33333333334</v>
       </c>
       <c r="G248" s="19"/>
@@ -13746,15 +13746,15 @@
         <v>646000</v>
       </c>
       <c r="D249" s="26">
-        <f>C249-(C249/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>107666.66666666663</v>
       </c>
       <c r="E249" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>WORD 97 MICROSOFT</v>
       </c>
       <c r="F249" s="10">
-        <f>C249/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>538333.33333333337</v>
       </c>
       <c r="G249" s="19"/>
@@ -13789,15 +13789,15 @@
         <v>259000</v>
       </c>
       <c r="D250" s="26">
-        <f>C250-(C250/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>43166.666666666657</v>
       </c>
       <c r="E250" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>WORD 97 Agg. MICROSOFT</v>
       </c>
       <c r="F250" s="10">
-        <f>C250/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>215833.33333333334</v>
       </c>
       <c r="G250" s="19"/>
@@ -13832,15 +13832,15 @@
         <v>645000</v>
       </c>
       <c r="D251" s="26">
-        <f>C251-(C251/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>107500</v>
       </c>
       <c r="E251" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>ACCESS 97 MICROSOFT</v>
       </c>
       <c r="F251" s="10">
-        <f>C251/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>537500</v>
       </c>
       <c r="G251" s="19"/>
@@ -13875,15 +13875,15 @@
         <v>879000</v>
       </c>
       <c r="D252" s="26">
-        <f>C252-(C252/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>146500</v>
       </c>
       <c r="E252" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>OFFICE 97 SMALL BUSINESS MICROSOFT</v>
       </c>
       <c r="F252" s="10">
-        <f>C252/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>732500</v>
       </c>
       <c r="G252" s="19"/>
@@ -13918,15 +13918,15 @@
         <v>259000</v>
       </c>
       <c r="D253" s="26">
-        <f>C253-(C253/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>43166.666666666657</v>
       </c>
       <c r="E253" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>HOME ESSENTIALS 98 MICROSOFT</v>
       </c>
       <c r="F253" s="10">
-        <f>C253/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>215833.33333333334</v>
       </c>
       <c r="G253" s="19"/>
@@ -13961,15 +13961,15 @@
         <v>274000</v>
       </c>
       <c r="D254" s="26">
-        <f>C254-(C254/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>45666.666666666657</v>
       </c>
       <c r="E254" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>FRONTPAGE 98 MICROSOFT</v>
       </c>
       <c r="F254" s="10">
-        <f>C254/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>228333.33333333334</v>
       </c>
       <c r="G254" s="19"/>
@@ -14004,15 +14004,15 @@
         <v>975000</v>
       </c>
       <c r="D255" s="26">
-        <f>C255-(C255/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>162500</v>
       </c>
       <c r="E255" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>OFFICE '97 MICROSOFT</v>
       </c>
       <c r="F255" s="10">
-        <f>C255/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>812500</v>
       </c>
       <c r="G255" s="19"/>
@@ -14047,15 +14047,15 @@
         <v>480000</v>
       </c>
       <c r="D256" s="26">
-        <f>C256-(C256/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>80000</v>
       </c>
       <c r="E256" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>OFFICE '97 Agg. MICROSOFT</v>
       </c>
       <c r="F256" s="10">
-        <f>C256/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>400000</v>
       </c>
       <c r="G256" s="19"/>
@@ -14090,15 +14090,15 @@
         <v>1187000</v>
       </c>
       <c r="D257" s="26">
-        <f>C257-(C257/(1+$G$2))</f>
+        <f t="shared" si="9"/>
         <v>197833.33333333326</v>
       </c>
       <c r="E257" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>OFFICE '97 Professional MICROSOFT</v>
       </c>
       <c r="F257" s="10">
-        <f>C257/(1+$G$2)</f>
+        <f t="shared" si="10"/>
         <v>989166.66666666674</v>
       </c>
       <c r="G257" s="19"/>
@@ -14133,15 +14133,15 @@
         <v>832000</v>
       </c>
       <c r="D258" s="26">
-        <f>C258-(C258/(1+$G$2))</f>
+        <f t="shared" ref="D258:D321" si="12">C258-(C258/(1+$G$2))</f>
         <v>138666.66666666663</v>
       </c>
       <c r="E258" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>OFFICE '97 Professional Agg. MICROSOFT</v>
       </c>
       <c r="F258" s="10">
-        <f>C258/(1+$G$2)</f>
+        <f t="shared" ref="F258:F321" si="13">C258/(1+$G$2)</f>
         <v>693333.33333333337</v>
       </c>
       <c r="G258" s="19"/>
@@ -14176,15 +14176,15 @@
         <v>227000</v>
       </c>
       <c r="D259" s="26">
-        <f>C259-(C259/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>37833.333333333314</v>
       </c>
       <c r="E259" s="16" t="str">
-        <f t="shared" ref="E259:E322" si="4">A259 &amp; " " &amp; B259</f>
+        <f t="shared" ref="E259:E322" si="14">A259 &amp; " " &amp; B259</f>
         <v>VISUAL BASIC 4.0 STD MICROSOFT</v>
       </c>
       <c r="F259" s="10">
-        <f>C259/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>189166.66666666669</v>
       </c>
       <c r="G259" s="19"/>
@@ -14219,15 +14219,15 @@
         <v>98000</v>
       </c>
       <c r="D260" s="26">
-        <f>C260-(C260/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>16333.333333333328</v>
       </c>
       <c r="E260" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>VISUAL BASIC 4.0 Agg. MICROSOFT</v>
       </c>
       <c r="F260" s="10">
-        <f>C260/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>81666.666666666672</v>
       </c>
       <c r="G260" s="19"/>
@@ -14262,15 +14262,15 @@
         <v>1190000</v>
       </c>
       <c r="D261" s="26">
-        <f>C261-(C261/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>198333.33333333326</v>
       </c>
       <c r="E261" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>VISUAL BASIC 4.0 PROFESSIONAL MICROSOFT</v>
       </c>
       <c r="F261" s="10">
-        <f>C261/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>991666.66666666674</v>
       </c>
       <c r="G261" s="19"/>
@@ -14305,15 +14305,15 @@
         <v>300000</v>
       </c>
       <c r="D262" s="26">
-        <f>C262-(C262/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>50000</v>
       </c>
       <c r="E262" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>VISUAL BASIC 4.0 PROF. Agg. MICROSOFT</v>
       </c>
       <c r="F262" s="10">
-        <f>C262/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>250000</v>
       </c>
       <c r="G262" s="19"/>
@@ -14348,15 +14348,15 @@
         <v>2407000</v>
       </c>
       <c r="D263" s="26">
-        <f>C263-(C263/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>401166.66666666651</v>
       </c>
       <c r="E263" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>VISUAL BASIC 4.0 ENTERPRICE MICROSOFT</v>
       </c>
       <c r="F263" s="10">
-        <f>C263/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>2005833.3333333335</v>
       </c>
       <c r="G263" s="19"/>
@@ -14391,15 +14391,15 @@
         <v>1021000</v>
       </c>
       <c r="D264" s="26">
-        <f>C264-(C264/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>170166.66666666663</v>
       </c>
       <c r="E264" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>VISUAL BASIC 4.0 ENTERPRICE Agg. MICROSOFT</v>
       </c>
       <c r="F264" s="10">
-        <f>C264/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>850833.33333333337</v>
       </c>
       <c r="G264" s="19"/>
@@ -14434,15 +14434,15 @@
         <v>646000</v>
       </c>
       <c r="D265" s="26">
-        <f>C265-(C265/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>107666.66666666663</v>
       </c>
       <c r="E265" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>POWERPOINT 97 MICROSOFT</v>
       </c>
       <c r="F265" s="10">
-        <f>C265/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>538333.33333333337</v>
       </c>
       <c r="G265" s="19"/>
@@ -14477,15 +14477,15 @@
         <v>259000</v>
       </c>
       <c r="D266" s="26">
-        <f>C266-(C266/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>43166.666666666657</v>
       </c>
       <c r="E266" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>POWERPOINT 97 Agg. MICROSOFT</v>
       </c>
       <c r="F266" s="10">
-        <f>C266/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>215833.33333333334</v>
       </c>
       <c r="G266" s="19"/>
@@ -14520,15 +14520,15 @@
         <v>193000</v>
       </c>
       <c r="D267" s="26">
-        <f>C267-(C267/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>32166.666666666657</v>
       </c>
       <c r="E267" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>PUBLISHER 3.0 MICROSOFT</v>
       </c>
       <c r="F267" s="10">
-        <f>C267/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>160833.33333333334</v>
       </c>
       <c r="G267" s="19"/>
@@ -14563,15 +14563,15 @@
         <v>96000</v>
       </c>
       <c r="D268" s="26">
-        <f>C268-(C268/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>16000</v>
       </c>
       <c r="E268" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>PUBLISHER 3.0 Agg. MICROSOFT</v>
       </c>
       <c r="F268" s="10">
-        <f>C268/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>80000</v>
       </c>
       <c r="G268" s="19"/>
@@ -14606,15 +14606,15 @@
         <v>594000</v>
       </c>
       <c r="D269" s="26">
-        <f>C269-(C269/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>99000</v>
       </c>
       <c r="E269" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>WINDOWS NT 4.0 WORKSTATION MICROSOFT</v>
       </c>
       <c r="F269" s="10">
-        <f>C269/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>495000</v>
       </c>
       <c r="G269" s="19"/>
@@ -14649,15 +14649,15 @@
         <v>282000</v>
       </c>
       <c r="D270" s="26">
-        <f>C270-(C270/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>47000</v>
       </c>
       <c r="E270" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>WINDOWS NT 4.0 Agg. WORKSTATION MICROSOFT</v>
       </c>
       <c r="F270" s="10">
-        <f>C270/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>235000</v>
       </c>
       <c r="G270" s="19"/>
@@ -14692,15 +14692,15 @@
         <v>1814000</v>
       </c>
       <c r="D271" s="26">
-        <f>C271-(C271/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>302333.33333333326</v>
       </c>
       <c r="E271" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>WINDOWS NT 4.0 SERVER 5 client MICROSOFT</v>
       </c>
       <c r="F271" s="10">
-        <f>C271/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>1511666.6666666667</v>
       </c>
       <c r="G271" s="19"/>
@@ -14735,15 +14735,15 @@
         <v>193000</v>
       </c>
       <c r="D272" s="26">
-        <f>C272-(C272/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>32166.666666666657</v>
       </c>
       <c r="E272" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>WINDOWS 3.1 MICROSOFT</v>
       </c>
       <c r="F272" s="10">
-        <f>C272/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>160833.33333333334</v>
       </c>
       <c r="G272" s="19"/>
@@ -14778,15 +14778,15 @@
         <v>654000</v>
       </c>
       <c r="D273" s="26">
-        <f>C273-(C273/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>109000</v>
       </c>
       <c r="E273" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>POWERPOINT 4.0 MICROSOFT</v>
       </c>
       <c r="F273" s="10">
-        <f>C273/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>545000</v>
       </c>
       <c r="G273" s="19"/>
@@ -14821,15 +14821,15 @@
         <v>729000</v>
       </c>
       <c r="D274" s="26">
-        <f>C274-(C274/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>121500</v>
       </c>
       <c r="E274" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>EXCEL 5.0 MICROSOFT</v>
       </c>
       <c r="F274" s="10">
-        <f>C274/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>607500</v>
       </c>
       <c r="G274" s="19"/>
@@ -14864,15 +14864,15 @@
         <v>632000</v>
       </c>
       <c r="D275" s="26">
-        <f>C275-(C275/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>105333.33333333326</v>
       </c>
       <c r="E275" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>ACCESS 2.0 MICROSOFT</v>
       </c>
       <c r="F275" s="10">
-        <f>C275/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>526666.66666666674</v>
       </c>
       <c r="G275" s="19"/>
@@ -14907,15 +14907,15 @@
         <v>240000</v>
       </c>
       <c r="D276" s="26">
-        <f>C276-(C276/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>40000</v>
       </c>
       <c r="E276" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>ACCESS 2.0 Competitivo MICROSOFT</v>
       </c>
       <c r="F276" s="10">
-        <f>C276/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>200000</v>
       </c>
       <c r="G276" s="19"/>
@@ -14950,15 +14950,15 @@
         <v>955000</v>
       </c>
       <c r="D277" s="26">
-        <f>C277-(C277/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>159166.66666666663</v>
       </c>
       <c r="E277" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">OFFICE 4.2 MICROSOFT </v>
       </c>
       <c r="F277" s="10">
-        <f>C277/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>795833.33333333337</v>
       </c>
       <c r="G277" s="19"/>
@@ -14993,15 +14993,15 @@
         <v>1126000</v>
       </c>
       <c r="D278" s="26">
-        <f>C278-(C278/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>187666.66666666663</v>
       </c>
       <c r="E278" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">OFFICE 4.3 PROFESSIONAL MICROSOFT </v>
       </c>
       <c r="F278" s="10">
-        <f>C278/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>938333.33333333337</v>
       </c>
       <c r="G278" s="19"/>
@@ -15034,15 +15034,15 @@
         <v>0</v>
       </c>
       <c r="D279" s="26">
-        <f>C279-(C279/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E279" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">STAMPANTI </v>
       </c>
       <c r="F279" s="10">
-        <f>C279/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G279" s="19"/>
@@ -15077,15 +15077,15 @@
         <v>297000</v>
       </c>
       <c r="D280" s="26">
-        <f>C280-(C280/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>49500</v>
       </c>
       <c r="E280" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON LX300 9 aghi, 80 col. 220 cps. opz. colore</v>
       </c>
       <c r="F280" s="10">
-        <f>C280/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>247500</v>
       </c>
       <c r="G280" s="19"/>
@@ -15120,15 +15120,15 @@
         <v>646000</v>
       </c>
       <c r="D281" s="26">
-        <f>C281-(C281/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>107666.66666666663</v>
       </c>
       <c r="E281" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON LX1050+ 9 aghi, 136 col. 200 cps</v>
       </c>
       <c r="F281" s="10">
-        <f>C281/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>538333.33333333337</v>
       </c>
       <c r="G281" s="19"/>
@@ -15163,15 +15163,15 @@
         <v>714000</v>
       </c>
       <c r="D282" s="26">
-        <f>C282-(C282/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>119000</v>
       </c>
       <c r="E282" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON FX870 9 aghi, 80 col. 380 cps</v>
       </c>
       <c r="F282" s="10">
-        <f>C282/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>595000</v>
       </c>
       <c r="G282" s="19"/>
@@ -15206,15 +15206,15 @@
         <v>807000</v>
       </c>
       <c r="D283" s="26">
-        <f>C283-(C283/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>134500</v>
       </c>
       <c r="E283" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON FX1170 9 aghi, 136 col.380 cps</v>
       </c>
       <c r="F283" s="10">
-        <f>C283/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>672500</v>
       </c>
       <c r="G283" s="19"/>
@@ -15249,15 +15249,15 @@
         <v>591000</v>
       </c>
       <c r="D284" s="26">
-        <f>C284-(C284/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>98500</v>
       </c>
       <c r="E284" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON LQ570+ 24 aghi, 80 col. 225 cps</v>
       </c>
       <c r="F284" s="10">
-        <f>C284/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>492500</v>
       </c>
       <c r="G284" s="19"/>
@@ -15292,15 +15292,15 @@
         <v>918000</v>
       </c>
       <c r="D285" s="26">
-        <f>C285-(C285/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>153000</v>
       </c>
       <c r="E285" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON LQ2070+ 24 aghi, 136 col. 225 cps</v>
       </c>
       <c r="F285" s="10">
-        <f>C285/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>765000</v>
       </c>
       <c r="G285" s="19"/>
@@ -15335,15 +15335,15 @@
         <v>1265000</v>
       </c>
       <c r="D286" s="26">
-        <f>C286-(C286/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>210833.33333333326</v>
       </c>
       <c r="E286" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON LQ 2170 24 aghi, 136 col. 440 cps</v>
       </c>
       <c r="F286" s="10">
-        <f>C286/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>1054166.6666666667</v>
       </c>
       <c r="G286" s="19"/>
@@ -15378,15 +15378,15 @@
         <v>256000</v>
       </c>
       <c r="D287" s="26">
-        <f>C287-(C287/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>42666.666666666657</v>
       </c>
       <c r="E287" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON STYLUS 300COLOR Ink Jet A4,1ppm col.</v>
       </c>
       <c r="F287" s="10">
-        <f>C287/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>213333.33333333334</v>
       </c>
       <c r="G287" s="19"/>
@@ -15421,15 +15421,15 @@
         <v>371000</v>
       </c>
       <c r="D288" s="26">
-        <f>C288-(C288/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>61833.333333333314</v>
       </c>
       <c r="E288" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON STYLUS 400COLOR Ink Jet A4,3ppm col.</v>
       </c>
       <c r="F288" s="10">
-        <f>C288/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>309166.66666666669</v>
       </c>
       <c r="G288" s="19"/>
@@ -15464,15 +15464,15 @@
         <v>457000</v>
       </c>
       <c r="D289" s="26">
-        <f>C289-(C289/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>76166.666666666628</v>
       </c>
       <c r="E289" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON STYLUS 600COLOR Ink Jet A4,4ppm col.</v>
       </c>
       <c r="F289" s="10">
-        <f>C289/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>380833.33333333337</v>
       </c>
       <c r="G289" s="19"/>
@@ -15507,15 +15507,15 @@
         <v>642000</v>
       </c>
       <c r="D290" s="26">
-        <f>C290-(C290/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>107000</v>
       </c>
       <c r="E290" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON STYLUS 800COLOR Ink Jet A4,7ppm col.</v>
       </c>
       <c r="F290" s="10">
-        <f>C290/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>535000</v>
       </c>
       <c r="G290" s="19"/>
@@ -15550,15 +15550,15 @@
         <v>1571000</v>
       </c>
       <c r="D291" s="26">
-        <f>C291-(C291/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>261833.33333333326</v>
       </c>
       <c r="E291" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON STYLUS 1520COLOR Ink Jet A2,800cps draft</v>
       </c>
       <c r="F291" s="10">
-        <f>C291/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>1309166.6666666667</v>
       </c>
       <c r="G291" s="19"/>
@@ -15593,15 +15593,15 @@
         <v>756000</v>
       </c>
       <c r="D292" s="26">
-        <f>C292-(C292/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>126000</v>
       </c>
       <c r="E292" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON STYLUS 1000 Ink Jet A3,250cps draft</v>
       </c>
       <c r="F292" s="10">
-        <f>C292/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>630000</v>
       </c>
       <c r="G292" s="19"/>
@@ -15636,15 +15636,15 @@
         <v>1571000</v>
       </c>
       <c r="D293" s="26">
-        <f>C293-(C293/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>261833.33333333326</v>
       </c>
       <c r="E293" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP.EPSON STYLUS PRO XL+ Ink Jet A4/A3</v>
       </c>
       <c r="F293" s="10">
-        <f>C293/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>1309166.6666666667</v>
       </c>
       <c r="G293" s="19"/>
@@ -15679,15 +15679,15 @@
         <v>2716000</v>
       </c>
       <c r="D294" s="26">
-        <f>C294-(C294/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>452666.66666666651</v>
       </c>
       <c r="E294" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">STAMP.EPSON STYLUS  3000 Ink Jet A2 800cpc 1440*720 dpi </v>
       </c>
       <c r="F294" s="10">
-        <f>C294/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>2263333.3333333335</v>
       </c>
       <c r="G294" s="19"/>
@@ -15722,15 +15722,15 @@
         <v>640000</v>
       </c>
       <c r="D295" s="26">
-        <f>C295-(C295/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>106666.66666666663</v>
       </c>
       <c r="E295" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">STAMP.EPSON STYLUS PHOTO Ink Jet A4 6 colori 2ppm </v>
       </c>
       <c r="F295" s="10">
-        <f>C295/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>533333.33333333337</v>
       </c>
       <c r="G295" s="19"/>
@@ -15765,15 +15765,15 @@
         <v>255000</v>
       </c>
       <c r="D296" s="26">
-        <f>C296-(C296/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>42500</v>
       </c>
       <c r="E296" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. CANON BJ-250 COLOR Ink Jet A4, 1ppm col</v>
       </c>
       <c r="F296" s="10">
-        <f>C296/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>212500</v>
       </c>
       <c r="G296" s="19"/>
@@ -15808,15 +15808,15 @@
         <v>413000</v>
       </c>
       <c r="D297" s="26">
-        <f>C297-(C297/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>68833.333333333314</v>
       </c>
       <c r="E297" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. CANON BJC-80 COLOR Ink jet A4, 2ppm col.</v>
       </c>
       <c r="F297" s="10">
-        <f>C297/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>344166.66666666669</v>
       </c>
       <c r="G297" s="19"/>
@@ -15851,15 +15851,15 @@
         <v>361000</v>
       </c>
       <c r="D298" s="26">
-        <f>C298-(C298/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>60166.666666666628</v>
       </c>
       <c r="E298" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. CANON BJC-4300 COLOR Ink Jet A4, 1ppm col.</v>
       </c>
       <c r="F298" s="10">
-        <f>C298/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>300833.33333333337</v>
       </c>
       <c r="G298" s="19"/>
@@ -15894,15 +15894,15 @@
         <v>544000</v>
       </c>
       <c r="D299" s="26">
-        <f>C299-(C299/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>90666.666666666628</v>
       </c>
       <c r="E299" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. CANON BJC-4550 COLOR Ink Jet A4/A3, 1 ppm</v>
       </c>
       <c r="F299" s="10">
-        <f>C299/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>453333.33333333337</v>
       </c>
       <c r="G299" s="19"/>
@@ -15937,15 +15937,15 @@
         <v>678000</v>
       </c>
       <c r="D300" s="26">
-        <f>C300-(C300/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>113000</v>
       </c>
       <c r="E300" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. CANON BJC-4650 COLOR Ink Jet A4/A3, 4,5 ppm</v>
       </c>
       <c r="F300" s="10">
-        <f>C300/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>565000</v>
       </c>
       <c r="G300" s="19"/>
@@ -15980,15 +15980,15 @@
         <v>1054000</v>
       </c>
       <c r="D301" s="26">
-        <f>C301-(C301/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>175666.66666666663</v>
       </c>
       <c r="E301" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. CANON BJC-5500 COLOR Ink Jet A3/A2 694cps</v>
       </c>
       <c r="F301" s="10">
-        <f>C301/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>878333.33333333337</v>
       </c>
       <c r="G301" s="19"/>
@@ -16023,15 +16023,15 @@
         <v>482000</v>
       </c>
       <c r="D302" s="26">
-        <f>C302-(C302/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>80333.333333333314</v>
       </c>
       <c r="E302" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. CANON BJC-620 COLOR Ink Jet A4, 300cps</v>
       </c>
       <c r="F302" s="10">
-        <f>C302/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>401666.66666666669</v>
       </c>
       <c r="G302" s="19"/>
@@ -16066,15 +16066,15 @@
         <v>722000</v>
       </c>
       <c r="D303" s="26">
-        <f>C303-(C303/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>120333.33333333326</v>
       </c>
       <c r="E303" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. CANON BJC-7000 COLOR Ink Jet A4,4,5ppm, 1200x600dpi</v>
       </c>
       <c r="F303" s="10">
-        <f>C303/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>601666.66666666674</v>
       </c>
       <c r="G303" s="19"/>
@@ -16109,15 +16109,15 @@
         <v>269000</v>
       </c>
       <c r="D304" s="26">
-        <f>C304-(C304/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>44833.333333333314</v>
       </c>
       <c r="E304" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 400L Ink Jet A4, 3 ppm col.</v>
       </c>
       <c r="F304" s="10">
-        <f>C304/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>224166.66666666669</v>
       </c>
       <c r="G304" s="19"/>
@@ -16152,15 +16152,15 @@
         <v>371000</v>
       </c>
       <c r="D305" s="26">
-        <f>C305-(C305/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>61833.333333333314</v>
       </c>
       <c r="E305" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 670 Ink Jet A4, 3 ppm col.</v>
       </c>
       <c r="F305" s="10">
-        <f>C305/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>309166.66666666669</v>
       </c>
       <c r="G305" s="19"/>
@@ -16195,15 +16195,15 @@
         <v>462000</v>
       </c>
       <c r="D306" s="26">
-        <f>C306-(C306/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>77000</v>
       </c>
       <c r="E306" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 690+ Ink Jet A4,  5 ppm col.</v>
       </c>
       <c r="F306" s="10">
-        <f>C306/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>385000</v>
       </c>
       <c r="G306" s="19"/>
@@ -16238,15 +16238,15 @@
         <v>541000</v>
       </c>
       <c r="D307" s="26">
-        <f>C307-(C307/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>90166.666666666628</v>
       </c>
       <c r="E307" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 720C Ink Jet A4,  7 ppm col.</v>
       </c>
       <c r="F307" s="10">
-        <f>C307/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>450833.33333333337</v>
       </c>
       <c r="G307" s="19"/>
@@ -16281,15 +16281,15 @@
         <v>648000</v>
       </c>
       <c r="D308" s="26">
-        <f>C308-(C308/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>108000</v>
       </c>
       <c r="E308" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 870 CXI Ink Jet A4,  8 ppm col.</v>
       </c>
       <c r="F308" s="10">
-        <f>C308/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>540000</v>
       </c>
       <c r="G308" s="19"/>
@@ -16324,15 +16324,15 @@
         <v>644000</v>
       </c>
       <c r="D309" s="26">
-        <f>C309-(C309/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>107333.33333333326</v>
       </c>
       <c r="E309" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 890C Ink Jet A4,  9 ppm col.</v>
       </c>
       <c r="F309" s="10">
-        <f>C309/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>536666.66666666674</v>
       </c>
       <c r="G309" s="19"/>
@@ -16367,15 +16367,15 @@
         <v>902000</v>
       </c>
       <c r="D310" s="26">
-        <f>C310-(C310/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>150333.33333333326</v>
       </c>
       <c r="E310" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 1100C Ink Jet A3/A4,  6 ppm col., 2Mb</v>
       </c>
       <c r="F310" s="10">
-        <f>C310/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>751666.66666666674</v>
       </c>
       <c r="G310" s="19"/>
@@ -16410,15 +16410,15 @@
         <v>722000</v>
       </c>
       <c r="D311" s="26">
-        <f>C311-(C311/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>120333.33333333326</v>
       </c>
       <c r="E311" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 6L Laser, A4 600dpi, 6ppm</v>
       </c>
       <c r="F311" s="10">
-        <f>C311/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>601666.66666666674</v>
       </c>
       <c r="G311" s="29">
@@ -16455,15 +16455,15 @@
         <v>1457000</v>
       </c>
       <c r="D312" s="26">
-        <f>C312-(C312/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>242833.33333333326</v>
       </c>
       <c r="E312" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 6P Laser, A4 600dpi, 6ppm</v>
       </c>
       <c r="F312" s="10">
-        <f>C312/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>1214166.6666666667</v>
       </c>
       <c r="G312" s="19"/>
@@ -16498,15 +16498,15 @@
         <v>1786000</v>
       </c>
       <c r="D313" s="26">
-        <f>C313-(C313/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>297666.66666666651</v>
       </c>
       <c r="E313" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>STAMP. HP 6MP Laser, A4 600dpi, 8ppm, 3Mb</v>
       </c>
       <c r="F313" s="10">
-        <f>C313/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>1488333.3333333335</v>
       </c>
       <c r="G313" s="19"/>
@@ -16539,15 +16539,15 @@
         <v>0</v>
       </c>
       <c r="D314" s="26">
-        <f>C314-(C314/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E314" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">CABINATI  </v>
       </c>
       <c r="F314" s="10">
-        <f>C314/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G314" s="19"/>
@@ -16582,15 +16582,15 @@
         <v>85000</v>
       </c>
       <c r="D315" s="26">
-        <f>C315-(C315/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>14166.666666666657</v>
       </c>
       <c r="E315" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>CASE DESKTOP   CE CK 131-6 P/S 200W</v>
       </c>
       <c r="F315" s="10">
-        <f>C315/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>70833.333333333343</v>
       </c>
       <c r="G315" s="19"/>
@@ -16625,15 +16625,15 @@
         <v>84000</v>
       </c>
       <c r="D316" s="26">
-        <f>C316-(C316/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>14000</v>
       </c>
       <c r="E316" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>CASE MINITOWER CE CK 136-1 P/S 200W</v>
       </c>
       <c r="F316" s="10">
-        <f>C316/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>70000</v>
       </c>
       <c r="G316" s="19"/>
@@ -16668,15 +16668,15 @@
         <v>115000</v>
       </c>
       <c r="D317" s="26">
-        <f>C317-(C317/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>19166.666666666657</v>
       </c>
       <c r="E317" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">CASE MIDITOWER CE CK 135-1 P/S 230W </v>
       </c>
       <c r="F317" s="10">
-        <f>C317/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>95833.333333333343</v>
       </c>
       <c r="G317" s="19"/>
@@ -16711,15 +16711,15 @@
         <v>152000</v>
       </c>
       <c r="D318" s="26">
-        <f>C318-(C318/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>25333.333333333328</v>
       </c>
       <c r="E318" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">CASE BIG TOWER CE   CK139-1 P/S 230W </v>
       </c>
       <c r="F318" s="10">
-        <f>C318/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>126666.66666666667</v>
       </c>
       <c r="G318" s="19"/>
@@ -16754,15 +16754,15 @@
         <v>82000</v>
       </c>
       <c r="D319" s="26">
-        <f>C319-(C319/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>13666.666666666657</v>
       </c>
       <c r="E319" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>CASE DESKTOP CE CK 131-8 P/S 200W</v>
       </c>
       <c r="F319" s="10">
-        <f>C319/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>68333.333333333343</v>
       </c>
       <c r="G319" s="19"/>
@@ -16797,15 +16797,15 @@
         <v>84000</v>
       </c>
       <c r="D320" s="26">
-        <f>C320-(C320/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>14000</v>
       </c>
       <c r="E320" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>CASE SUB-MIDITOWER CE  CK 132-3 P/S 200W</v>
       </c>
       <c r="F320" s="10">
-        <f>C320/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>70000</v>
       </c>
       <c r="G320" s="19"/>
@@ -16840,15 +16840,15 @@
         <v>115000</v>
       </c>
       <c r="D321" s="26">
-        <f>C321-(C321/(1+$G$2))</f>
+        <f t="shared" si="12"/>
         <v>19166.666666666657</v>
       </c>
       <c r="E321" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>CASE  MIDITOWER CE  CK 135-2 P/S 230W</v>
       </c>
       <c r="F321" s="10">
-        <f>C321/(1+$G$2)</f>
+        <f t="shared" si="13"/>
         <v>95833.333333333343</v>
       </c>
       <c r="G321" s="19"/>
@@ -16883,15 +16883,15 @@
         <v>153000</v>
       </c>
       <c r="D322" s="26">
-        <f>C322-(C322/(1+$G$2))</f>
+        <f t="shared" ref="D322:D385" si="15">C322-(C322/(1+$G$2))</f>
         <v>25500</v>
       </c>
       <c r="E322" s="16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>CASE TOWER CE CK 139-2 P/S 230W</v>
       </c>
       <c r="F322" s="10">
-        <f>C322/(1+$G$2)</f>
+        <f t="shared" ref="F322:F337" si="16">C322/(1+$G$2)</f>
         <v>127500</v>
       </c>
       <c r="G322" s="19"/>
@@ -16926,15 +16926,15 @@
         <v>80000</v>
       </c>
       <c r="D323" s="26">
-        <f>C323-(C323/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>13333.333333333328</v>
       </c>
       <c r="E323" s="16" t="str">
-        <f t="shared" ref="E323:E337" si="5">A323 &amp; " " &amp; B323</f>
+        <f t="shared" ref="E323:E337" si="17">A323 &amp; " " &amp; B323</f>
         <v>CASE MIDITOWER BC VIP 432 P/S 230W</v>
       </c>
       <c r="F323" s="10">
-        <f>C323/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>66666.666666666672</v>
       </c>
       <c r="G323" s="19"/>
@@ -16969,15 +16969,15 @@
         <v>102000</v>
       </c>
       <c r="D324" s="26">
-        <f>C324-(C324/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>17000</v>
       </c>
       <c r="E324" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>CASE TOWER BC VIP 730 P/S 230W</v>
       </c>
       <c r="F324" s="10">
-        <f>C324/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>85000</v>
       </c>
       <c r="G324" s="19"/>
@@ -17008,15 +17008,15 @@
       <c r="B325" s="12"/>
       <c r="C325" s="11"/>
       <c r="D325" s="26">
-        <f>C325-(C325/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E325" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">GRUPPI DI CONTINUITA' </v>
       </c>
       <c r="F325" s="10">
-        <f>C325/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G325" s="19"/>
@@ -17051,15 +17051,15 @@
         <v>198000</v>
       </c>
       <c r="D326" s="26">
-        <f>C326-(C326/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>33000</v>
       </c>
       <c r="E326" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.REVOLUTION E300  STAND- BY</v>
       </c>
       <c r="F326" s="10">
-        <f>C326/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>165000</v>
       </c>
       <c r="G326" s="19"/>
@@ -17094,15 +17094,15 @@
         <v>233000</v>
       </c>
       <c r="D327" s="26">
-        <f>C327-(C327/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>38833.333333333314</v>
       </c>
       <c r="E327" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.REVOLUTION F450 STAND- BY</v>
       </c>
       <c r="F327" s="10">
-        <f>C327/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>194166.66666666669</v>
       </c>
       <c r="G327" s="19"/>
@@ -17137,15 +17137,15 @@
         <v>279000</v>
       </c>
       <c r="D328" s="26">
-        <f>C328-(C328/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>46500</v>
       </c>
       <c r="E328" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.REVOLUTION L600 STAND- BY</v>
       </c>
       <c r="F328" s="10">
-        <f>C328/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>232500</v>
       </c>
       <c r="G328" s="19"/>
@@ -17180,15 +17180,15 @@
         <v>298000</v>
       </c>
       <c r="D329" s="26">
-        <f>C329-(C329/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>49666.666666666657</v>
       </c>
       <c r="E329" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWER PRO 600 LINE INTERACTIVE</v>
       </c>
       <c r="F329" s="10">
-        <f>C329/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>248333.33333333334</v>
       </c>
       <c r="G329" s="19"/>
@@ -17223,15 +17223,15 @@
         <v>478000</v>
       </c>
       <c r="D330" s="26">
-        <f>C330-(C330/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>79666.666666666628</v>
       </c>
       <c r="E330" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWER PRO 750 LINE INTERACTIVE</v>
       </c>
       <c r="F330" s="10">
-        <f>C330/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>398333.33333333337</v>
       </c>
       <c r="G330" s="19"/>
@@ -17266,15 +17266,15 @@
         <v>626000</v>
       </c>
       <c r="D331" s="26">
-        <f>C331-(C331/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>104333.33333333331</v>
       </c>
       <c r="E331" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWER PRO 900 LINE INTERACTIVE</v>
       </c>
       <c r="F331" s="10">
-        <f>C331/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>521666.66666666669</v>
       </c>
       <c r="G331" s="19"/>
@@ -17309,15 +17309,15 @@
         <v>757000</v>
       </c>
       <c r="D332" s="26">
-        <f>C332-(C332/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>126166.66666666663</v>
       </c>
       <c r="E332" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWER PRO 1000 LINE INTERACTIVE</v>
       </c>
       <c r="F332" s="10">
-        <f>C332/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>630833.33333333337</v>
       </c>
       <c r="G332" s="19"/>
@@ -17352,15 +17352,15 @@
         <v>1128000</v>
       </c>
       <c r="D333" s="26">
-        <f>C333-(C333/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>188000</v>
       </c>
       <c r="E333" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWER PRO 1600 LINE INTERACTIVE</v>
       </c>
       <c r="F333" s="10">
-        <f>C333/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>940000</v>
       </c>
       <c r="G333" s="19"/>
@@ -17395,15 +17395,15 @@
         <v>1527000</v>
       </c>
       <c r="D334" s="26">
-        <f>C334-(C334/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>254500</v>
       </c>
       <c r="E334" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWER PRO 2400 LINE INTERACTIVE</v>
       </c>
       <c r="F334" s="10">
-        <f>C334/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>1272500</v>
       </c>
       <c r="G334" s="19"/>
@@ -17438,15 +17438,15 @@
         <v>4134000</v>
       </c>
       <c r="D335" s="26">
-        <f>C335-(C335/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>689000</v>
       </c>
       <c r="E335" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWERSAVE 4000 ON-LINE</v>
       </c>
       <c r="F335" s="10">
-        <f>C335/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>3445000</v>
       </c>
       <c r="G335" s="19"/>
@@ -17481,15 +17481,15 @@
         <v>6850000</v>
       </c>
       <c r="D336" s="26">
-        <f>C336-(C336/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>1141666.666666666</v>
       </c>
       <c r="E336" s="16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWERSAVE 7500 ON-LINE</v>
       </c>
       <c r="F336" s="10">
-        <f>C336/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>5708333.333333334</v>
       </c>
       <c r="G336" s="19"/>
@@ -17524,15 +17524,15 @@
         <v>11712000</v>
       </c>
       <c r="D337" s="65">
-        <f>C337-(C337/(1+$G$2))</f>
+        <f t="shared" si="15"/>
         <v>1952000</v>
       </c>
       <c r="E337" s="66" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>GR.CONT.POWERSAVE 12500 ON-LINE</v>
       </c>
       <c r="F337" s="67">
-        <f>C337/(1+$G$2)</f>
+        <f t="shared" si="16"/>
         <v>9760000</v>
       </c>
       <c r="G337" s="19"/>
@@ -31756,13 +31756,13 @@
     </row>
     <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="68" t="s">
         <v>594</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="68" t="s">
         <v>593</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="68" t="s">
         <v>592</v>
       </c>
       <c r="G9" s="4"/>
@@ -58716,7 +58716,7 @@
         <v>13</v>
       </c>
       <c r="G15" s="37"/>
-      <c r="I15" s="70" t="s">
+      <c r="I15" s="68" t="s">
         <v>595</v>
       </c>
     </row>
@@ -63587,7 +63587,7 @@
       <c r="C3" s="52" t="s">
         <v>499</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="77" t="s">
         <v>596</v>
       </c>
     </row>
@@ -64033,10 +64033,10 @@
       <c r="A1" s="39" t="s">
         <v>582</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="78" t="s">
         <v>577</v>
       </c>
-      <c r="C1" s="69"/>
+      <c r="C1" s="79"/>
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
@@ -64054,13 +64054,13 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="73" t="s">
         <v>571</v>
       </c>
-      <c r="B3" s="71">
+      <c r="B3" s="69">
         <v>0</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="71" t="s">
         <v>581</v>
       </c>
       <c r="D3" s="20"/>
@@ -64068,13 +64068,13 @@
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="73" t="s">
         <v>572</v>
       </c>
-      <c r="B4" s="71">
+      <c r="B4" s="69">
         <v>40</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="71" t="s">
         <v>580</v>
       </c>
       <c r="D4" s="20"/>
@@ -64082,25 +64082,25 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="73" t="s">
         <v>573</v>
       </c>
-      <c r="B5" s="71">
+      <c r="B5" s="69">
         <v>60</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="71" t="s">
         <v>579</v>
       </c>
       <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="74" t="s">
         <v>574</v>
       </c>
-      <c r="B6" s="72">
+      <c r="B6" s="70">
         <v>70</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="72" t="s">
         <v>578</v>
       </c>
       <c r="D6" s="20"/>

--- a/ESERCIZIO_M2-1-1_dati - Copia.xlsx
+++ b/ESERCIZIO_M2-1-1_dati - Copia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3965ca6def52ccf6/Desktop/GitHub/Esercizi Condivisi/Esercizi-Data-Analyst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="742" documentId="8_{016B3A27-A793-41D9-80CF-710967D4E75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{714D9907-478F-4AB2-A997-12FFD38F404E}"/>
+  <xr:revisionPtr revIDLastSave="744" documentId="8_{016B3A27-A793-41D9-80CF-710967D4E75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A365BA3F-C6B0-491E-BAC5-948315C0FB66}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="798" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assoluti_Iva" sheetId="1" r:id="rId1"/>
@@ -2044,7 +2044,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2072,6 +2072,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2404,7 +2410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2490,9 +2496,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2528,9 +2531,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2594,6 +2594,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3173,7 +3176,7 @@
       <c r="B1" s="14" t="s">
         <v>591</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="59" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
@@ -3182,10 +3185,10 @@
       <c r="E1" s="14" t="s">
         <v>569</v>
       </c>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="60" t="s">
         <v>575</v>
       </c>
-      <c r="G1" s="76" t="s">
+      <c r="G1" s="74" t="s">
         <v>568</v>
       </c>
       <c r="I1" s="8"/>
@@ -3229,7 +3232,7 @@
         <f t="shared" ref="F2:F65" si="1">C2/(1+$G$2)</f>
         <v>234166.66666666669</v>
       </c>
-      <c r="G2" s="75">
+      <c r="G2" s="73">
         <v>0.2</v>
       </c>
       <c r="H2" s="27"/>
@@ -16883,7 +16886,7 @@
         <v>153000</v>
       </c>
       <c r="D322" s="26">
-        <f t="shared" ref="D322:D385" si="15">C322-(C322/(1+$G$2))</f>
+        <f t="shared" ref="D322:D337" si="15">C322-(C322/(1+$G$2))</f>
         <v>25500</v>
       </c>
       <c r="E322" s="16" t="str">
@@ -17514,24 +17517,24 @@
       <c r="Z336" s="1"/>
     </row>
     <row r="337" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="63" t="s">
+      <c r="A337" s="61" t="s">
         <v>482</v>
       </c>
-      <c r="B337" s="63" t="s">
+      <c r="B337" s="61" t="s">
         <v>480</v>
       </c>
-      <c r="C337" s="64">
+      <c r="C337" s="62">
         <v>11712000</v>
       </c>
-      <c r="D337" s="65">
+      <c r="D337" s="63">
         <f t="shared" si="15"/>
         <v>1952000</v>
       </c>
-      <c r="E337" s="66" t="str">
+      <c r="E337" s="64" t="str">
         <f t="shared" si="17"/>
         <v>GR.CONT.POWERSAVE 12500 ON-LINE</v>
       </c>
-      <c r="F337" s="67">
+      <c r="F337" s="65">
         <f t="shared" si="16"/>
         <v>9760000</v>
       </c>
@@ -31756,13 +31759,13 @@
     </row>
     <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="66" t="s">
         <v>594</v>
       </c>
-      <c r="D9" s="68" t="s">
+      <c r="D9" s="66" t="s">
         <v>593</v>
       </c>
-      <c r="E9" s="68" t="s">
+      <c r="E9" s="66" t="s">
         <v>592</v>
       </c>
       <c r="G9" s="4"/>
@@ -58309,42 +58312,42 @@
   <dimension ref="A1:S1047602"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" style="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.109375" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" style="49" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25" style="49" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25" style="48" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.5546875" style="20" customWidth="1"/>
     <col min="7" max="7" width="22.77734375" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="40" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.5546875" customWidth="1"/>
     <col min="10" max="19" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="34" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>492</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="45" t="s">
         <v>493</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="46" t="s">
         <v>495</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="46" t="s">
         <v>496</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="56" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="54" t="s">
         <v>584</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="54" t="s">
         <v>583</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="I1" s="41" t="s">
         <v>590</v>
       </c>
       <c r="J1" s="33"/>
@@ -58359,5182 +58362,5182 @@
       <c r="S1" s="33"/>
     </row>
     <row r="2" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48">
+      <c r="A2" s="47">
         <v>36529</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>497</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D2" s="51">
+      <c r="D2" s="50">
         <v>50000</v>
       </c>
-      <c r="E2" s="51">
+      <c r="E2" s="50">
         <v>16</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="42" t="s">
         <v>498</v>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="40">
         <v>11</v>
       </c>
-      <c r="I2" s="59">
+      <c r="I2" s="57">
         <f>SUMIF(C2:C80,G2,D2:D80)</f>
         <v>611780</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="48">
+      <c r="A3" s="47">
         <v>36534</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="49" t="s">
         <v>499</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="50">
         <v>29970</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="50">
         <v>29</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="42" t="s">
         <v>505</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="40">
         <v>9</v>
       </c>
-      <c r="I3" s="59">
+      <c r="I3" s="57">
         <f t="shared" ref="I3:I5" si="0">SUMIF(C3:C81,G3,D3:D81)</f>
         <v>54000</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48">
+      <c r="A4" s="47">
         <v>36537</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="49" t="s">
         <v>500</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="50">
         <v>27560</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="50">
         <v>21</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="42" t="s">
         <v>546</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="40">
         <v>8</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="57">
         <f t="shared" si="0"/>
         <v>6765600</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="48">
+      <c r="A5" s="47">
         <v>36543</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="49" t="s">
         <v>502</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="49" t="s">
         <v>503</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="50">
         <v>43500</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="50">
         <v>29</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="42" t="s">
         <v>557</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="40">
         <v>8</v>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="57">
         <f t="shared" si="0"/>
         <v>30860</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="48">
+      <c r="A6" s="47">
         <v>36545</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="49" t="s">
         <v>504</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="49" t="s">
         <v>505</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="50">
         <v>13500</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="50">
         <v>15</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="55" t="s">
         <v>589</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="55" t="s">
         <v>583</v>
       </c>
-      <c r="I6" s="44" t="s">
+      <c r="I6" s="43" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="48">
+      <c r="A7" s="47">
         <v>36547</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="49" t="s">
         <v>506</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>507</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="50">
         <v>50800</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="50">
         <v>22</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="42" t="s">
         <v>506</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="40">
         <v>1</v>
       </c>
-      <c r="I7" s="59">
+      <c r="I7" s="57">
         <f>SUMIF(B2:B80,G7,D2:D80)</f>
         <v>50800</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="48">
+      <c r="A8" s="47">
         <v>36548</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="49" t="s">
         <v>508</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="49" t="s">
         <v>509</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="50">
         <v>98450</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="50">
         <v>21</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="42" t="s">
         <v>508</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="40">
         <v>1</v>
       </c>
-      <c r="I8" s="59">
+      <c r="I8" s="57">
         <f t="shared" ref="I8:I13" si="1">SUMIF(B3:B81,G8,D3:D81)</f>
         <v>98450</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="48">
+      <c r="A9" s="47">
         <v>36551</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="49" t="s">
         <v>500</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="50">
         <v>45890</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="50">
         <v>18</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="42" t="s">
         <v>500</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="40">
         <v>2</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="57">
         <f t="shared" si="1"/>
         <v>73450</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48">
+      <c r="A10" s="47">
         <v>36552</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="49" t="s">
         <v>510</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="49" t="s">
         <v>511</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="50">
         <v>7950</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="50">
         <v>23</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="42" t="s">
         <v>510</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="40">
         <v>1</v>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="57">
         <f t="shared" si="1"/>
         <v>7950</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48">
+      <c r="A11" s="47">
         <v>36553</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="49" t="s">
         <v>512</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="49" t="s">
         <v>509</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="50">
         <v>87450</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="50">
         <v>24</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="42" t="s">
         <v>524</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="40">
         <v>4</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="57">
         <f t="shared" si="1"/>
         <v>283000</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48">
+      <c r="A12" s="47">
         <v>36554</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="49" t="s">
         <v>513</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="49" t="s">
         <v>514</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <v>295000</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="50">
         <v>27</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="42" t="s">
         <v>527</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="40">
         <v>2</v>
       </c>
-      <c r="I12" s="59">
+      <c r="I12" s="57">
         <f t="shared" si="1"/>
         <v>107700</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48">
+      <c r="A13" s="47">
         <v>36555</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="49" t="s">
         <v>502</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="49" t="s">
         <v>515</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="50">
         <v>348980</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="50">
         <v>15</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="44" t="s">
         <v>528</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13" s="56">
         <v>1</v>
       </c>
-      <c r="I13" s="60">
+      <c r="I13" s="58">
         <f t="shared" si="1"/>
         <v>27270</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48">
+      <c r="A14" s="47">
         <v>36558</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="49" t="s">
         <v>516</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="49" t="s">
         <v>517</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="50">
         <v>127490</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="50">
         <v>17</v>
       </c>
-      <c r="G14" s="37"/>
+      <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48">
+      <c r="A15" s="47">
         <v>36558</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="49" t="s">
         <v>518</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="50">
         <v>49400</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="50">
         <v>13</v>
       </c>
-      <c r="G15" s="37"/>
-      <c r="I15" s="68" t="s">
+      <c r="G15" s="36"/>
+      <c r="I15" s="66" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48">
+      <c r="A16" s="47">
         <v>36573</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="49" t="s">
         <v>519</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="49" t="s">
         <v>520</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="50">
         <v>201000</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="50">
         <v>14</v>
       </c>
-      <c r="G16" s="37"/>
+      <c r="G16" s="36"/>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48">
+      <c r="A17" s="47">
         <v>36573</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="49" t="s">
         <v>521</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="49" t="s">
         <v>520</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="50">
         <v>1368000</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="50">
         <v>28</v>
       </c>
-      <c r="G17" s="37"/>
+      <c r="G17" s="36"/>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48">
+      <c r="A18" s="47">
         <v>36576</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="49" t="s">
         <v>522</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="49" t="s">
         <v>523</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="50">
         <v>36850</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="50">
         <v>16</v>
       </c>
-      <c r="G18" s="37"/>
+      <c r="G18" s="36"/>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48">
+      <c r="A19" s="47">
         <v>36580</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="49" t="s">
         <v>524</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="50">
         <v>151500</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="50">
         <v>13</v>
       </c>
-      <c r="G19" s="37"/>
+      <c r="G19" s="36"/>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48">
+      <c r="A20" s="47">
         <v>36589</v>
       </c>
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="49" t="s">
         <v>504</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="49" t="s">
         <v>505</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="50">
         <v>13500</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="50">
         <v>20</v>
       </c>
-      <c r="G20" s="37"/>
+      <c r="G20" s="36"/>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="48">
+      <c r="A21" s="47">
         <v>36593</v>
       </c>
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="49" t="s">
         <v>525</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="49" t="s">
         <v>526</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="50">
         <v>17000</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="50">
         <v>18</v>
       </c>
-      <c r="G21" s="37"/>
+      <c r="G21" s="36"/>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48">
+      <c r="A22" s="47">
         <v>36594</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="49" t="s">
         <v>527</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="50">
         <v>35900</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="50">
         <v>16</v>
       </c>
-      <c r="G22" s="37"/>
+      <c r="G22" s="36"/>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="48">
+      <c r="A23" s="47">
         <v>36594</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="49" t="s">
         <v>528</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="49" t="s">
         <v>529</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="50">
         <v>27270</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="50">
         <v>14</v>
       </c>
-      <c r="G23" s="37"/>
+      <c r="G23" s="36"/>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48">
+      <c r="A24" s="47">
         <v>36594</v>
       </c>
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="49" t="s">
         <v>530</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="49" t="s">
         <v>529</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="50">
         <v>13400</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="50">
         <v>14</v>
       </c>
-      <c r="G24" s="37"/>
+      <c r="G24" s="36"/>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48">
+      <c r="A25" s="47">
         <v>36595</v>
       </c>
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="49" t="s">
         <v>524</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="50">
         <v>19000</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="50">
         <v>17</v>
       </c>
-      <c r="G25" s="37"/>
+      <c r="G25" s="36"/>
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="48">
+      <c r="A26" s="47">
         <v>36595</v>
       </c>
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="49" t="s">
         <v>527</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="50">
         <v>71800</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="50">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="48">
+      <c r="A27" s="47">
         <v>36595</v>
       </c>
-      <c r="B27" s="50" t="s">
+      <c r="B27" s="49" t="s">
         <v>530</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="49" t="s">
         <v>529</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="50">
         <v>12280</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="50">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="48">
+      <c r="A28" s="47">
         <v>36595</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="49" t="s">
         <v>530</v>
       </c>
-      <c r="C28" s="50" t="s">
+      <c r="C28" s="49" t="s">
         <v>529</v>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="50">
         <v>14670</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="50">
         <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="48">
+      <c r="A29" s="47">
         <v>36596</v>
       </c>
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="49" t="s">
         <v>531</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="50">
         <v>163500</v>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="50">
         <v>18</v>
       </c>
-      <c r="G29" s="37"/>
+      <c r="G29" s="36"/>
     </row>
     <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48">
+      <c r="A30" s="47">
         <v>36596</v>
       </c>
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="49" t="s">
         <v>532</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="49" t="s">
         <v>515</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="50">
         <v>183900</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="50">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48">
+      <c r="A31" s="47">
         <v>36596</v>
       </c>
-      <c r="B31" s="50" t="s">
+      <c r="B31" s="49" t="s">
         <v>533</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="49" t="s">
         <v>534</v>
       </c>
-      <c r="D31" s="51">
+      <c r="D31" s="50">
         <v>43500</v>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="50">
         <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="48">
+      <c r="A32" s="47">
         <v>36596</v>
       </c>
-      <c r="B32" s="50" t="s">
+      <c r="B32" s="49" t="s">
         <v>535</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="49" t="s">
         <v>529</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="50">
         <v>10730</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="50">
         <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="48">
+      <c r="A33" s="47">
         <v>36596</v>
       </c>
-      <c r="B33" s="50" t="s">
+      <c r="B33" s="49" t="s">
         <v>536</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="49" t="s">
         <v>529</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="50">
         <v>11210</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="50">
         <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48">
+      <c r="A34" s="47">
         <v>36596</v>
       </c>
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="49" t="s">
         <v>537</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="49" t="s">
         <v>526</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="50">
         <v>127950</v>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="50">
         <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="48">
+      <c r="A35" s="47">
         <v>36597</v>
       </c>
-      <c r="B35" s="50" t="s">
+      <c r="B35" s="49" t="s">
         <v>538</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="49" t="s">
         <v>539</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="50">
         <v>20000</v>
       </c>
-      <c r="E35" s="51">
+      <c r="E35" s="50">
         <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48">
+      <c r="A36" s="47">
         <v>36597</v>
       </c>
-      <c r="B36" s="50" t="s">
+      <c r="B36" s="49" t="s">
         <v>540</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="49" t="s">
         <v>529</v>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="50">
         <v>7850</v>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="50">
         <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48">
+      <c r="A37" s="47">
         <v>36598</v>
       </c>
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="49" t="s">
         <v>516</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="49" t="s">
         <v>517</v>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="50">
         <v>127490</v>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="50">
         <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48">
+      <c r="A38" s="47">
         <v>36598</v>
       </c>
-      <c r="B38" s="50" t="s">
+      <c r="B38" s="49" t="s">
         <v>541</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="49" t="s">
         <v>523</v>
       </c>
-      <c r="D38" s="51">
+      <c r="D38" s="50">
         <v>3950</v>
       </c>
-      <c r="E38" s="51">
+      <c r="E38" s="50">
         <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48">
+      <c r="A39" s="47">
         <v>36598</v>
       </c>
-      <c r="B39" s="50" t="s">
+      <c r="B39" s="49" t="s">
         <v>497</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="49" t="s">
         <v>542</v>
       </c>
-      <c r="D39" s="51">
+      <c r="D39" s="50">
         <v>50000</v>
       </c>
-      <c r="E39" s="51">
+      <c r="E39" s="50">
         <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48">
+      <c r="A40" s="47">
         <v>36600</v>
       </c>
-      <c r="B40" s="50" t="s">
+      <c r="B40" s="49" t="s">
         <v>543</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="49" t="s">
         <v>544</v>
       </c>
-      <c r="D40" s="51">
+      <c r="D40" s="50">
         <v>16650</v>
       </c>
-      <c r="E40" s="51">
+      <c r="E40" s="50">
         <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48">
+      <c r="A41" s="47">
         <v>36603</v>
       </c>
-      <c r="B41" s="50" t="s">
+      <c r="B41" s="49" t="s">
         <v>518</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D41" s="51">
+      <c r="D41" s="50">
         <v>87300</v>
       </c>
-      <c r="E41" s="51">
+      <c r="E41" s="50">
         <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48">
+      <c r="A42" s="47">
         <v>36604</v>
       </c>
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="49" t="s">
         <v>545</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="C42" s="49" t="s">
         <v>546</v>
       </c>
-      <c r="D42" s="51">
+      <c r="D42" s="50">
         <v>2425000</v>
       </c>
-      <c r="E42" s="51">
+      <c r="E42" s="50">
         <v>11</v>
       </c>
-      <c r="G42" s="37"/>
+      <c r="G42" s="36"/>
     </row>
     <row r="43" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48">
+      <c r="A43" s="47">
         <v>36608</v>
       </c>
-      <c r="B43" s="50" t="s">
+      <c r="B43" s="49" t="s">
         <v>547</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D43" s="51">
+      <c r="D43" s="50">
         <v>18230</v>
       </c>
-      <c r="E43" s="51">
+      <c r="E43" s="50">
         <v>21</v>
       </c>
-      <c r="G43" s="37"/>
+      <c r="G43" s="36"/>
     </row>
     <row r="44" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48">
+      <c r="A44" s="47">
         <v>36609</v>
       </c>
-      <c r="B44" s="50" t="s">
+      <c r="B44" s="49" t="s">
         <v>537</v>
       </c>
-      <c r="C44" s="50" t="s">
+      <c r="C44" s="49" t="s">
         <v>526</v>
       </c>
-      <c r="D44" s="51">
+      <c r="D44" s="50">
         <v>78530</v>
       </c>
-      <c r="E44" s="51">
+      <c r="E44" s="50">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48">
+      <c r="A45" s="47">
         <v>36609</v>
       </c>
-      <c r="B45" s="50" t="s">
+      <c r="B45" s="49" t="s">
         <v>548</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="49" t="s">
         <v>526</v>
       </c>
-      <c r="D45" s="51">
+      <c r="D45" s="50">
         <v>21000</v>
       </c>
-      <c r="E45" s="51">
+      <c r="E45" s="50">
         <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48">
+      <c r="A46" s="47">
         <v>36612</v>
       </c>
-      <c r="B46" s="50" t="s">
+      <c r="B46" s="49" t="s">
         <v>549</v>
       </c>
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="49" t="s">
         <v>550</v>
       </c>
-      <c r="D46" s="51">
+      <c r="D46" s="50">
         <v>34900</v>
       </c>
-      <c r="E46" s="51">
+      <c r="E46" s="50">
         <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="48">
+      <c r="A47" s="47">
         <v>36614</v>
       </c>
-      <c r="B47" s="50" t="s">
+      <c r="B47" s="49" t="s">
         <v>541</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="49" t="s">
         <v>523</v>
       </c>
-      <c r="D47" s="51">
+      <c r="D47" s="50">
         <v>8000</v>
       </c>
-      <c r="E47" s="51">
+      <c r="E47" s="50">
         <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="48">
+      <c r="A48" s="47">
         <v>36614</v>
       </c>
-      <c r="B48" s="50" t="s">
+      <c r="B48" s="49" t="s">
         <v>551</v>
       </c>
-      <c r="C48" s="50" t="s">
+      <c r="C48" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D48" s="51">
+      <c r="D48" s="50">
         <v>24660</v>
       </c>
-      <c r="E48" s="51">
+      <c r="E48" s="50">
         <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="48">
+      <c r="A49" s="47">
         <v>36616</v>
       </c>
-      <c r="B49" s="50" t="s">
+      <c r="B49" s="49" t="s">
         <v>552</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="49" t="s">
         <v>550</v>
       </c>
-      <c r="D49" s="51">
+      <c r="D49" s="50">
         <v>22450</v>
       </c>
-      <c r="E49" s="51">
+      <c r="E49" s="50">
         <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="48">
+      <c r="A50" s="47">
         <v>36622</v>
       </c>
-      <c r="B50" s="50" t="s">
+      <c r="B50" s="49" t="s">
         <v>552</v>
       </c>
-      <c r="C50" s="50" t="s">
+      <c r="C50" s="49" t="s">
         <v>550</v>
       </c>
-      <c r="D50" s="51">
+      <c r="D50" s="50">
         <v>44950</v>
       </c>
-      <c r="E50" s="51">
+      <c r="E50" s="50">
         <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="48">
+      <c r="A51" s="47">
         <v>36624</v>
       </c>
-      <c r="B51" s="50" t="s">
+      <c r="B51" s="49" t="s">
         <v>553</v>
       </c>
-      <c r="C51" s="50" t="s">
+      <c r="C51" s="49" t="s">
         <v>546</v>
       </c>
-      <c r="D51" s="51">
+      <c r="D51" s="50">
         <v>55600</v>
       </c>
-      <c r="E51" s="51">
+      <c r="E51" s="50">
         <v>11</v>
       </c>
-      <c r="G51" s="37"/>
+      <c r="G51" s="36"/>
     </row>
     <row r="52" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="48">
+      <c r="A52" s="47">
         <v>36629</v>
       </c>
-      <c r="B52" s="50" t="s">
+      <c r="B52" s="49" t="s">
         <v>554</v>
       </c>
-      <c r="C52" s="50" t="s">
+      <c r="C52" s="49" t="s">
         <v>555</v>
       </c>
-      <c r="D52" s="51">
+      <c r="D52" s="50">
         <v>84500</v>
       </c>
-      <c r="E52" s="51">
+      <c r="E52" s="50">
         <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="48">
+      <c r="A53" s="47">
         <v>36632</v>
       </c>
-      <c r="B53" s="50" t="s">
+      <c r="B53" s="49" t="s">
         <v>531</v>
       </c>
-      <c r="C53" s="50" t="s">
+      <c r="C53" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D53" s="51">
+      <c r="D53" s="50">
         <v>51800</v>
       </c>
-      <c r="E53" s="51">
+      <c r="E53" s="50">
         <v>21</v>
       </c>
-      <c r="G53" s="37"/>
+      <c r="G53" s="36"/>
     </row>
     <row r="54" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="48">
+      <c r="A54" s="47">
         <v>36632</v>
       </c>
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="49" t="s">
         <v>524</v>
       </c>
-      <c r="C54" s="50" t="s">
+      <c r="C54" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D54" s="51">
+      <c r="D54" s="50">
         <v>31000</v>
       </c>
-      <c r="E54" s="51">
+      <c r="E54" s="50">
         <v>16</v>
       </c>
-      <c r="G54" s="37"/>
+      <c r="G54" s="36"/>
     </row>
     <row r="55" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="48">
+      <c r="A55" s="47">
         <v>36637</v>
       </c>
-      <c r="B55" s="50" t="s">
+      <c r="B55" s="49" t="s">
         <v>524</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D55" s="51">
+      <c r="D55" s="50">
         <v>81500</v>
       </c>
-      <c r="E55" s="51">
+      <c r="E55" s="50">
         <v>25</v>
       </c>
-      <c r="G55" s="37"/>
+      <c r="G55" s="36"/>
     </row>
     <row r="56" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="48">
+      <c r="A56" s="47">
         <v>36637</v>
       </c>
-      <c r="B56" s="50" t="s">
+      <c r="B56" s="49" t="s">
         <v>532</v>
       </c>
-      <c r="C56" s="50" t="s">
+      <c r="C56" s="49" t="s">
         <v>515</v>
       </c>
-      <c r="D56" s="51">
+      <c r="D56" s="50">
         <v>183900</v>
       </c>
-      <c r="E56" s="51">
+      <c r="E56" s="50">
         <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="48">
+      <c r="A57" s="47">
         <v>36637</v>
       </c>
-      <c r="B57" s="50" t="s">
+      <c r="B57" s="49" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="50" t="s">
+      <c r="C57" s="49" t="s">
         <v>505</v>
       </c>
-      <c r="D57" s="51">
+      <c r="D57" s="50">
         <v>13500</v>
       </c>
-      <c r="E57" s="51">
+      <c r="E57" s="50">
         <v>18</v>
       </c>
-      <c r="G57" s="37"/>
+      <c r="G57" s="36"/>
     </row>
     <row r="58" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="48">
+      <c r="A58" s="47">
         <v>36638</v>
       </c>
-      <c r="B58" s="50" t="s">
+      <c r="B58" s="49" t="s">
         <v>556</v>
       </c>
-      <c r="C58" s="50" t="s">
+      <c r="C58" s="49" t="s">
         <v>557</v>
       </c>
-      <c r="D58" s="51">
+      <c r="D58" s="50">
         <v>2010</v>
       </c>
-      <c r="E58" s="51">
+      <c r="E58" s="50">
         <v>21</v>
       </c>
-      <c r="G58" s="37"/>
+      <c r="G58" s="36"/>
     </row>
     <row r="59" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="48">
+      <c r="A59" s="47">
         <v>36640</v>
       </c>
-      <c r="B59" s="50" t="s">
+      <c r="B59" s="49" t="s">
         <v>558</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="C59" s="49" t="s">
         <v>550</v>
       </c>
-      <c r="D59" s="51">
+      <c r="D59" s="50">
         <v>36300</v>
       </c>
-      <c r="E59" s="51">
+      <c r="E59" s="50">
         <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="48">
+      <c r="A60" s="47">
         <v>36642</v>
       </c>
-      <c r="B60" s="50" t="s">
+      <c r="B60" s="49" t="s">
         <v>547</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="C60" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D60" s="51">
+      <c r="D60" s="50">
         <v>7640</v>
       </c>
-      <c r="E60" s="51">
+      <c r="E60" s="50">
         <v>20</v>
       </c>
-      <c r="G60" s="37"/>
+      <c r="G60" s="36"/>
     </row>
     <row r="61" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="48">
+      <c r="A61" s="47">
         <v>36644</v>
       </c>
-      <c r="B61" s="50" t="s">
+      <c r="B61" s="49" t="s">
         <v>525</v>
       </c>
-      <c r="C61" s="50" t="s">
+      <c r="C61" s="49" t="s">
         <v>526</v>
       </c>
-      <c r="D61" s="51">
+      <c r="D61" s="50">
         <v>18000</v>
       </c>
-      <c r="E61" s="51">
+      <c r="E61" s="50">
         <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="48">
+      <c r="A62" s="47">
         <v>36645</v>
       </c>
-      <c r="B62" s="50" t="s">
+      <c r="B62" s="49" t="s">
         <v>556</v>
       </c>
-      <c r="C62" s="50" t="s">
+      <c r="C62" s="49" t="s">
         <v>557</v>
       </c>
-      <c r="D62" s="51">
+      <c r="D62" s="50">
         <v>8730</v>
       </c>
-      <c r="E62" s="51">
+      <c r="E62" s="50">
         <v>18</v>
       </c>
-      <c r="G62" s="37"/>
+      <c r="G62" s="36"/>
     </row>
     <row r="63" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="48">
+      <c r="A63" s="47">
         <v>36645</v>
       </c>
-      <c r="B63" s="50" t="s">
+      <c r="B63" s="49" t="s">
         <v>525</v>
       </c>
-      <c r="C63" s="50" t="s">
+      <c r="C63" s="49" t="s">
         <v>526</v>
       </c>
-      <c r="D63" s="51">
+      <c r="D63" s="50">
         <v>19000</v>
       </c>
-      <c r="E63" s="51">
+      <c r="E63" s="50">
         <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="48">
+      <c r="A64" s="47">
         <v>36649</v>
       </c>
-      <c r="B64" s="50" t="s">
+      <c r="B64" s="49" t="s">
         <v>545</v>
       </c>
-      <c r="C64" s="50" t="s">
+      <c r="C64" s="49" t="s">
         <v>546</v>
       </c>
-      <c r="D64" s="51">
+      <c r="D64" s="50">
         <v>2425000</v>
       </c>
-      <c r="E64" s="51">
+      <c r="E64" s="50">
         <v>21</v>
       </c>
-      <c r="G64" s="37"/>
+      <c r="G64" s="36"/>
     </row>
     <row r="65" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="48">
+      <c r="A65" s="47">
         <v>36651</v>
       </c>
-      <c r="B65" s="50" t="s">
+      <c r="B65" s="49" t="s">
         <v>545</v>
       </c>
-      <c r="C65" s="50" t="s">
+      <c r="C65" s="49" t="s">
         <v>546</v>
       </c>
-      <c r="D65" s="51">
+      <c r="D65" s="50">
         <v>1860000</v>
       </c>
-      <c r="E65" s="51">
+      <c r="E65" s="50">
         <v>19</v>
       </c>
-      <c r="G65" s="37"/>
+      <c r="G65" s="36"/>
     </row>
     <row r="66" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="48">
+      <c r="A66" s="47">
         <v>36652</v>
       </c>
-      <c r="B66" s="50" t="s">
+      <c r="B66" s="49" t="s">
         <v>559</v>
       </c>
-      <c r="C66" s="50" t="s">
+      <c r="C66" s="49" t="s">
         <v>557</v>
       </c>
-      <c r="D66" s="51">
+      <c r="D66" s="50">
         <v>6570</v>
       </c>
-      <c r="E66" s="51">
+      <c r="E66" s="50">
         <v>13</v>
       </c>
-      <c r="G66" s="37"/>
+      <c r="G66" s="36"/>
     </row>
     <row r="67" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="48">
+      <c r="A67" s="47">
         <v>36653</v>
       </c>
-      <c r="B67" s="50" t="s">
+      <c r="B67" s="49" t="s">
         <v>560</v>
       </c>
-      <c r="C67" s="50" t="s">
+      <c r="C67" s="49" t="s">
         <v>561</v>
       </c>
-      <c r="D67" s="51">
+      <c r="D67" s="50">
         <v>14000</v>
       </c>
-      <c r="E67" s="51">
+      <c r="E67" s="50">
         <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="48">
+      <c r="A68" s="47">
         <v>36665</v>
       </c>
-      <c r="B68" s="50" t="s">
+      <c r="B68" s="49" t="s">
         <v>562</v>
       </c>
-      <c r="C68" s="50" t="s">
+      <c r="C68" s="49" t="s">
         <v>503</v>
       </c>
-      <c r="D68" s="51">
+      <c r="D68" s="50">
         <v>29980</v>
       </c>
-      <c r="E68" s="51">
+      <c r="E68" s="50">
         <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="48">
+      <c r="A69" s="47">
         <v>36666</v>
       </c>
-      <c r="B69" s="50" t="s">
+      <c r="B69" s="49" t="s">
         <v>563</v>
       </c>
-      <c r="C69" s="50" t="s">
+      <c r="C69" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D69" s="51">
+      <c r="D69" s="50">
         <v>17950</v>
       </c>
-      <c r="E69" s="51">
+      <c r="E69" s="50">
         <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="48">
+      <c r="A70" s="47">
         <v>36666</v>
       </c>
-      <c r="B70" s="50" t="s">
+      <c r="B70" s="49" t="s">
         <v>551</v>
       </c>
-      <c r="C70" s="50" t="s">
+      <c r="C70" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D70" s="51">
+      <c r="D70" s="50">
         <v>32320</v>
       </c>
-      <c r="E70" s="51">
+      <c r="E70" s="50">
         <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="48">
+      <c r="A71" s="47">
         <v>36667</v>
       </c>
-      <c r="B71" s="50" t="s">
+      <c r="B71" s="49" t="s">
         <v>564</v>
       </c>
-      <c r="C71" s="50" t="s">
+      <c r="C71" s="49" t="s">
         <v>542</v>
       </c>
-      <c r="D71" s="51">
+      <c r="D71" s="50">
         <v>27350</v>
       </c>
-      <c r="E71" s="51">
+      <c r="E71" s="50">
         <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="48">
+      <c r="A72" s="47">
         <v>36672</v>
       </c>
-      <c r="B72" s="50" t="s">
+      <c r="B72" s="49" t="s">
         <v>560</v>
       </c>
-      <c r="C72" s="50" t="s">
+      <c r="C72" s="49" t="s">
         <v>561</v>
       </c>
-      <c r="D72" s="51">
+      <c r="D72" s="50">
         <v>15000</v>
       </c>
-      <c r="E72" s="51">
+      <c r="E72" s="50">
         <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="48">
+      <c r="A73" s="47">
         <v>36681</v>
       </c>
-      <c r="B73" s="50" t="s">
+      <c r="B73" s="49" t="s">
         <v>504</v>
       </c>
-      <c r="C73" s="50" t="s">
+      <c r="C73" s="49" t="s">
         <v>505</v>
       </c>
-      <c r="D73" s="51">
+      <c r="D73" s="50">
         <v>13500</v>
       </c>
-      <c r="E73" s="51">
+      <c r="E73" s="50">
         <v>21</v>
       </c>
-      <c r="G73" s="37"/>
+      <c r="G73" s="36"/>
     </row>
     <row r="74" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="48">
+      <c r="A74" s="47">
         <v>36682</v>
       </c>
-      <c r="B74" s="50" t="s">
+      <c r="B74" s="49" t="s">
         <v>559</v>
       </c>
-      <c r="C74" s="50" t="s">
+      <c r="C74" s="49" t="s">
         <v>557</v>
       </c>
-      <c r="D74" s="51">
+      <c r="D74" s="50">
         <v>8600</v>
       </c>
-      <c r="E74" s="51">
+      <c r="E74" s="50">
         <v>22</v>
       </c>
-      <c r="G74" s="37"/>
+      <c r="G74" s="36"/>
     </row>
     <row r="75" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="48">
+      <c r="A75" s="47">
         <v>36685</v>
       </c>
-      <c r="B75" s="50" t="s">
+      <c r="B75" s="49" t="s">
         <v>502</v>
       </c>
-      <c r="C75" s="50" t="s">
+      <c r="C75" s="49" t="s">
         <v>503</v>
       </c>
-      <c r="D75" s="51">
+      <c r="D75" s="50">
         <v>15980</v>
       </c>
-      <c r="E75" s="51">
+      <c r="E75" s="50">
         <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="48">
+      <c r="A76" s="47">
         <v>36686</v>
       </c>
-      <c r="B76" s="50" t="s">
+      <c r="B76" s="49" t="s">
         <v>547</v>
       </c>
-      <c r="C76" s="50" t="s">
+      <c r="C76" s="49" t="s">
         <v>498</v>
       </c>
-      <c r="D76" s="51">
+      <c r="D76" s="50">
         <v>7640</v>
       </c>
-      <c r="E76" s="51">
+      <c r="E76" s="50">
         <v>22</v>
       </c>
-      <c r="G76" s="37"/>
+      <c r="G76" s="36"/>
     </row>
     <row r="77" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="48">
+      <c r="A77" s="47">
         <v>36697</v>
       </c>
-      <c r="B77" s="50" t="s">
+      <c r="B77" s="49" t="s">
         <v>565</v>
       </c>
-      <c r="C77" s="50" t="s">
+      <c r="C77" s="49" t="s">
         <v>523</v>
       </c>
-      <c r="D77" s="51">
+      <c r="D77" s="50">
         <v>40650</v>
       </c>
-      <c r="E77" s="51">
+      <c r="E77" s="50">
         <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="48">
+      <c r="A78" s="47">
         <v>36700</v>
       </c>
-      <c r="B78" s="50" t="s">
+      <c r="B78" s="49" t="s">
         <v>566</v>
       </c>
-      <c r="C78" s="50" t="s">
+      <c r="C78" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D78" s="51">
+      <c r="D78" s="50">
         <v>50280</v>
       </c>
-      <c r="E78" s="51">
+      <c r="E78" s="50">
         <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="48">
+      <c r="A79" s="47">
         <v>36700</v>
       </c>
-      <c r="B79" s="50" t="s">
+      <c r="B79" s="49" t="s">
         <v>566</v>
       </c>
-      <c r="C79" s="50" t="s">
+      <c r="C79" s="49" t="s">
         <v>501</v>
       </c>
-      <c r="D79" s="51">
+      <c r="D79" s="50">
         <v>1050</v>
       </c>
-      <c r="E79" s="51">
+      <c r="E79" s="50">
         <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="48">
+      <c r="A80" s="47">
         <v>36705</v>
       </c>
-      <c r="B80" s="50" t="s">
+      <c r="B80" s="49" t="s">
         <v>567</v>
       </c>
-      <c r="C80" s="50" t="s">
+      <c r="C80" s="49" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="51">
+      <c r="D80" s="50">
         <v>4950</v>
       </c>
-      <c r="E80" s="51">
+      <c r="E80" s="50">
         <v>28</v>
       </c>
-      <c r="G80" s="37"/>
+      <c r="G80" s="36"/>
     </row>
     <row r="81" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D81" s="51"/>
-      <c r="E81" s="51"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
     </row>
     <row r="82" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D82" s="51"/>
-      <c r="E82" s="51"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
     </row>
     <row r="83" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
     </row>
     <row r="84" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D84" s="51"/>
-      <c r="E84" s="51"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
     </row>
     <row r="85" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D85" s="51"/>
-      <c r="E85" s="51"/>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
     </row>
     <row r="86" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
     </row>
     <row r="87" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
     </row>
     <row r="88" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
+      <c r="D88" s="50"/>
+      <c r="E88" s="50"/>
     </row>
     <row r="89" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D89" s="51"/>
-      <c r="E89" s="51"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
     </row>
     <row r="90" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D90" s="51"/>
-      <c r="E90" s="51"/>
+      <c r="D90" s="50"/>
+      <c r="E90" s="50"/>
     </row>
     <row r="91" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D91" s="51"/>
-      <c r="E91" s="51"/>
+      <c r="D91" s="50"/>
+      <c r="E91" s="50"/>
     </row>
     <row r="92" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D92" s="51"/>
-      <c r="E92" s="51"/>
+      <c r="D92" s="50"/>
+      <c r="E92" s="50"/>
     </row>
     <row r="93" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D93" s="51"/>
-      <c r="E93" s="51"/>
+      <c r="D93" s="50"/>
+      <c r="E93" s="50"/>
     </row>
     <row r="94" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D94" s="51"/>
-      <c r="E94" s="51"/>
+      <c r="D94" s="50"/>
+      <c r="E94" s="50"/>
     </row>
     <row r="95" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D95" s="51"/>
-      <c r="E95" s="51"/>
+      <c r="D95" s="50"/>
+      <c r="E95" s="50"/>
     </row>
     <row r="96" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D96" s="51"/>
-      <c r="E96" s="51"/>
+      <c r="D96" s="50"/>
+      <c r="E96" s="50"/>
     </row>
     <row r="97" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="51"/>
-      <c r="E97" s="51"/>
+      <c r="D97" s="50"/>
+      <c r="E97" s="50"/>
     </row>
     <row r="98" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
+      <c r="D98" s="50"/>
+      <c r="E98" s="50"/>
     </row>
     <row r="99" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
     </row>
     <row r="100" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
     </row>
     <row r="101" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
     </row>
     <row r="102" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D102" s="51"/>
-      <c r="E102" s="51"/>
+      <c r="D102" s="50"/>
+      <c r="E102" s="50"/>
     </row>
     <row r="103" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
+      <c r="D103" s="50"/>
+      <c r="E103" s="50"/>
     </row>
     <row r="104" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
+      <c r="D104" s="50"/>
+      <c r="E104" s="50"/>
     </row>
     <row r="105" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D105" s="51"/>
-      <c r="E105" s="51"/>
+      <c r="D105" s="50"/>
+      <c r="E105" s="50"/>
     </row>
     <row r="106" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D106" s="51"/>
-      <c r="E106" s="51"/>
+      <c r="D106" s="50"/>
+      <c r="E106" s="50"/>
     </row>
     <row r="107" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D107" s="51"/>
-      <c r="E107" s="51"/>
+      <c r="D107" s="50"/>
+      <c r="E107" s="50"/>
     </row>
     <row r="108" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D108" s="51"/>
-      <c r="E108" s="51"/>
+      <c r="D108" s="50"/>
+      <c r="E108" s="50"/>
     </row>
     <row r="109" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D109" s="51"/>
-      <c r="E109" s="51"/>
+      <c r="D109" s="50"/>
+      <c r="E109" s="50"/>
     </row>
     <row r="110" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D110" s="51"/>
-      <c r="E110" s="51"/>
+      <c r="D110" s="50"/>
+      <c r="E110" s="50"/>
     </row>
     <row r="111" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D111" s="51"/>
-      <c r="E111" s="51"/>
+      <c r="D111" s="50"/>
+      <c r="E111" s="50"/>
     </row>
     <row r="112" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D112" s="51"/>
-      <c r="E112" s="51"/>
+      <c r="D112" s="50"/>
+      <c r="E112" s="50"/>
     </row>
     <row r="113" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D113" s="51"/>
-      <c r="E113" s="51"/>
+      <c r="D113" s="50"/>
+      <c r="E113" s="50"/>
     </row>
     <row r="114" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D114" s="51"/>
-      <c r="E114" s="51"/>
+      <c r="D114" s="50"/>
+      <c r="E114" s="50"/>
     </row>
     <row r="115" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D115" s="51"/>
-      <c r="E115" s="51"/>
+      <c r="D115" s="50"/>
+      <c r="E115" s="50"/>
     </row>
     <row r="116" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D116" s="51"/>
-      <c r="E116" s="51"/>
+      <c r="D116" s="50"/>
+      <c r="E116" s="50"/>
     </row>
     <row r="117" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D117" s="51"/>
-      <c r="E117" s="51"/>
+      <c r="D117" s="50"/>
+      <c r="E117" s="50"/>
     </row>
     <row r="118" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D118" s="51"/>
-      <c r="E118" s="51"/>
+      <c r="D118" s="50"/>
+      <c r="E118" s="50"/>
     </row>
     <row r="119" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D119" s="51"/>
-      <c r="E119" s="51"/>
+      <c r="D119" s="50"/>
+      <c r="E119" s="50"/>
     </row>
     <row r="120" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D120" s="51"/>
-      <c r="E120" s="51"/>
+      <c r="D120" s="50"/>
+      <c r="E120" s="50"/>
     </row>
     <row r="121" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D121" s="51"/>
-      <c r="E121" s="51"/>
+      <c r="D121" s="50"/>
+      <c r="E121" s="50"/>
     </row>
     <row r="122" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D122" s="51"/>
-      <c r="E122" s="51"/>
+      <c r="D122" s="50"/>
+      <c r="E122" s="50"/>
     </row>
     <row r="123" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D123" s="51"/>
-      <c r="E123" s="51"/>
+      <c r="D123" s="50"/>
+      <c r="E123" s="50"/>
     </row>
     <row r="124" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D124" s="51"/>
-      <c r="E124" s="51"/>
+      <c r="D124" s="50"/>
+      <c r="E124" s="50"/>
     </row>
     <row r="125" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D125" s="51"/>
-      <c r="E125" s="51"/>
+      <c r="D125" s="50"/>
+      <c r="E125" s="50"/>
     </row>
     <row r="126" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D126" s="51"/>
-      <c r="E126" s="51"/>
+      <c r="D126" s="50"/>
+      <c r="E126" s="50"/>
     </row>
     <row r="127" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D127" s="51"/>
-      <c r="E127" s="51"/>
+      <c r="D127" s="50"/>
+      <c r="E127" s="50"/>
     </row>
     <row r="128" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D128" s="51"/>
-      <c r="E128" s="51"/>
+      <c r="D128" s="50"/>
+      <c r="E128" s="50"/>
     </row>
     <row r="129" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D129" s="51"/>
-      <c r="E129" s="51"/>
+      <c r="D129" s="50"/>
+      <c r="E129" s="50"/>
     </row>
     <row r="130" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D130" s="51"/>
-      <c r="E130" s="51"/>
+      <c r="D130" s="50"/>
+      <c r="E130" s="50"/>
     </row>
     <row r="131" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D131" s="51"/>
-      <c r="E131" s="51"/>
+      <c r="D131" s="50"/>
+      <c r="E131" s="50"/>
     </row>
     <row r="132" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D132" s="51"/>
-      <c r="E132" s="51"/>
+      <c r="D132" s="50"/>
+      <c r="E132" s="50"/>
     </row>
     <row r="133" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D133" s="51"/>
-      <c r="E133" s="51"/>
+      <c r="D133" s="50"/>
+      <c r="E133" s="50"/>
     </row>
     <row r="134" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D134" s="51"/>
-      <c r="E134" s="51"/>
+      <c r="D134" s="50"/>
+      <c r="E134" s="50"/>
     </row>
     <row r="135" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D135" s="51"/>
-      <c r="E135" s="51"/>
+      <c r="D135" s="50"/>
+      <c r="E135" s="50"/>
     </row>
     <row r="136" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D136" s="51"/>
-      <c r="E136" s="51"/>
+      <c r="D136" s="50"/>
+      <c r="E136" s="50"/>
     </row>
     <row r="137" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D137" s="51"/>
-      <c r="E137" s="51"/>
+      <c r="D137" s="50"/>
+      <c r="E137" s="50"/>
     </row>
     <row r="138" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D138" s="51"/>
-      <c r="E138" s="51"/>
+      <c r="D138" s="50"/>
+      <c r="E138" s="50"/>
     </row>
     <row r="139" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D139" s="51"/>
-      <c r="E139" s="51"/>
+      <c r="D139" s="50"/>
+      <c r="E139" s="50"/>
     </row>
     <row r="140" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D140" s="51"/>
-      <c r="E140" s="51"/>
+      <c r="D140" s="50"/>
+      <c r="E140" s="50"/>
     </row>
     <row r="141" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D141" s="51"/>
-      <c r="E141" s="51"/>
+      <c r="D141" s="50"/>
+      <c r="E141" s="50"/>
     </row>
     <row r="142" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D142" s="51"/>
-      <c r="E142" s="51"/>
+      <c r="D142" s="50"/>
+      <c r="E142" s="50"/>
     </row>
     <row r="143" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D143" s="51"/>
-      <c r="E143" s="51"/>
+      <c r="D143" s="50"/>
+      <c r="E143" s="50"/>
     </row>
     <row r="144" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D144" s="51"/>
-      <c r="E144" s="51"/>
+      <c r="D144" s="50"/>
+      <c r="E144" s="50"/>
     </row>
     <row r="145" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D145" s="51"/>
-      <c r="E145" s="51"/>
+      <c r="D145" s="50"/>
+      <c r="E145" s="50"/>
     </row>
     <row r="146" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D146" s="51"/>
-      <c r="E146" s="51"/>
+      <c r="D146" s="50"/>
+      <c r="E146" s="50"/>
     </row>
     <row r="147" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D147" s="51"/>
-      <c r="E147" s="51"/>
+      <c r="D147" s="50"/>
+      <c r="E147" s="50"/>
     </row>
     <row r="148" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D148" s="51"/>
-      <c r="E148" s="51"/>
+      <c r="D148" s="50"/>
+      <c r="E148" s="50"/>
     </row>
     <row r="149" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D149" s="51"/>
-      <c r="E149" s="51"/>
+      <c r="D149" s="50"/>
+      <c r="E149" s="50"/>
     </row>
     <row r="150" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D150" s="51"/>
-      <c r="E150" s="51"/>
+      <c r="D150" s="50"/>
+      <c r="E150" s="50"/>
     </row>
     <row r="151" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D151" s="51"/>
-      <c r="E151" s="51"/>
+      <c r="D151" s="50"/>
+      <c r="E151" s="50"/>
     </row>
     <row r="152" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D152" s="51"/>
-      <c r="E152" s="51"/>
+      <c r="D152" s="50"/>
+      <c r="E152" s="50"/>
     </row>
     <row r="153" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D153" s="51"/>
-      <c r="E153" s="51"/>
+      <c r="D153" s="50"/>
+      <c r="E153" s="50"/>
     </row>
     <row r="154" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D154" s="51"/>
-      <c r="E154" s="51"/>
+      <c r="D154" s="50"/>
+      <c r="E154" s="50"/>
     </row>
     <row r="155" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D155" s="51"/>
-      <c r="E155" s="51"/>
+      <c r="D155" s="50"/>
+      <c r="E155" s="50"/>
     </row>
     <row r="156" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D156" s="51"/>
-      <c r="E156" s="51"/>
+      <c r="D156" s="50"/>
+      <c r="E156" s="50"/>
     </row>
     <row r="157" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D157" s="51"/>
-      <c r="E157" s="51"/>
+      <c r="D157" s="50"/>
+      <c r="E157" s="50"/>
     </row>
     <row r="158" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D158" s="51"/>
-      <c r="E158" s="51"/>
+      <c r="D158" s="50"/>
+      <c r="E158" s="50"/>
     </row>
     <row r="159" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D159" s="51"/>
-      <c r="E159" s="51"/>
+      <c r="D159" s="50"/>
+      <c r="E159" s="50"/>
     </row>
     <row r="160" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D160" s="51"/>
-      <c r="E160" s="51"/>
+      <c r="D160" s="50"/>
+      <c r="E160" s="50"/>
     </row>
     <row r="161" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D161" s="51"/>
-      <c r="E161" s="51"/>
+      <c r="D161" s="50"/>
+      <c r="E161" s="50"/>
     </row>
     <row r="162" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D162" s="51"/>
-      <c r="E162" s="51"/>
+      <c r="D162" s="50"/>
+      <c r="E162" s="50"/>
     </row>
     <row r="163" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D163" s="51"/>
-      <c r="E163" s="51"/>
+      <c r="D163" s="50"/>
+      <c r="E163" s="50"/>
     </row>
     <row r="164" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D164" s="51"/>
-      <c r="E164" s="51"/>
+      <c r="D164" s="50"/>
+      <c r="E164" s="50"/>
     </row>
     <row r="165" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D165" s="51"/>
-      <c r="E165" s="51"/>
+      <c r="D165" s="50"/>
+      <c r="E165" s="50"/>
     </row>
     <row r="166" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D166" s="51"/>
-      <c r="E166" s="51"/>
+      <c r="D166" s="50"/>
+      <c r="E166" s="50"/>
     </row>
     <row r="167" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D167" s="51"/>
-      <c r="E167" s="51"/>
+      <c r="D167" s="50"/>
+      <c r="E167" s="50"/>
     </row>
     <row r="168" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D168" s="51"/>
-      <c r="E168" s="51"/>
+      <c r="D168" s="50"/>
+      <c r="E168" s="50"/>
     </row>
     <row r="169" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D169" s="51"/>
-      <c r="E169" s="51"/>
+      <c r="D169" s="50"/>
+      <c r="E169" s="50"/>
     </row>
     <row r="170" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D170" s="51"/>
-      <c r="E170" s="51"/>
+      <c r="D170" s="50"/>
+      <c r="E170" s="50"/>
     </row>
     <row r="171" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D171" s="51"/>
-      <c r="E171" s="51"/>
+      <c r="D171" s="50"/>
+      <c r="E171" s="50"/>
     </row>
     <row r="172" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D172" s="51"/>
-      <c r="E172" s="51"/>
+      <c r="D172" s="50"/>
+      <c r="E172" s="50"/>
     </row>
     <row r="173" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D173" s="51"/>
-      <c r="E173" s="51"/>
+      <c r="D173" s="50"/>
+      <c r="E173" s="50"/>
     </row>
     <row r="174" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D174" s="51"/>
-      <c r="E174" s="51"/>
+      <c r="D174" s="50"/>
+      <c r="E174" s="50"/>
     </row>
     <row r="175" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D175" s="51"/>
-      <c r="E175" s="51"/>
+      <c r="D175" s="50"/>
+      <c r="E175" s="50"/>
     </row>
     <row r="176" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D176" s="51"/>
-      <c r="E176" s="51"/>
+      <c r="D176" s="50"/>
+      <c r="E176" s="50"/>
     </row>
     <row r="177" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D177" s="51"/>
-      <c r="E177" s="51"/>
+      <c r="D177" s="50"/>
+      <c r="E177" s="50"/>
     </row>
     <row r="178" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D178" s="51"/>
-      <c r="E178" s="51"/>
+      <c r="D178" s="50"/>
+      <c r="E178" s="50"/>
     </row>
     <row r="179" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D179" s="51"/>
-      <c r="E179" s="51"/>
+      <c r="D179" s="50"/>
+      <c r="E179" s="50"/>
     </row>
     <row r="180" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D180" s="51"/>
-      <c r="E180" s="51"/>
+      <c r="D180" s="50"/>
+      <c r="E180" s="50"/>
     </row>
     <row r="181" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D181" s="51"/>
-      <c r="E181" s="51"/>
+      <c r="D181" s="50"/>
+      <c r="E181" s="50"/>
     </row>
     <row r="182" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D182" s="51"/>
-      <c r="E182" s="51"/>
+      <c r="D182" s="50"/>
+      <c r="E182" s="50"/>
     </row>
     <row r="183" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D183" s="51"/>
-      <c r="E183" s="51"/>
+      <c r="D183" s="50"/>
+      <c r="E183" s="50"/>
     </row>
     <row r="184" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D184" s="51"/>
-      <c r="E184" s="51"/>
+      <c r="D184" s="50"/>
+      <c r="E184" s="50"/>
     </row>
     <row r="185" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D185" s="51"/>
-      <c r="E185" s="51"/>
+      <c r="D185" s="50"/>
+      <c r="E185" s="50"/>
     </row>
     <row r="186" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D186" s="51"/>
-      <c r="E186" s="51"/>
+      <c r="D186" s="50"/>
+      <c r="E186" s="50"/>
     </row>
     <row r="187" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D187" s="51"/>
-      <c r="E187" s="51"/>
+      <c r="D187" s="50"/>
+      <c r="E187" s="50"/>
     </row>
     <row r="188" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D188" s="51"/>
-      <c r="E188" s="51"/>
+      <c r="D188" s="50"/>
+      <c r="E188" s="50"/>
     </row>
     <row r="189" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D189" s="51"/>
-      <c r="E189" s="51"/>
+      <c r="D189" s="50"/>
+      <c r="E189" s="50"/>
     </row>
     <row r="190" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D190" s="51"/>
-      <c r="E190" s="51"/>
+      <c r="D190" s="50"/>
+      <c r="E190" s="50"/>
     </row>
     <row r="191" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D191" s="51"/>
-      <c r="E191" s="51"/>
+      <c r="D191" s="50"/>
+      <c r="E191" s="50"/>
     </row>
     <row r="192" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D192" s="51"/>
-      <c r="E192" s="51"/>
+      <c r="D192" s="50"/>
+      <c r="E192" s="50"/>
     </row>
     <row r="193" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D193" s="51"/>
-      <c r="E193" s="51"/>
+      <c r="D193" s="50"/>
+      <c r="E193" s="50"/>
     </row>
     <row r="194" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D194" s="51"/>
-      <c r="E194" s="51"/>
+      <c r="D194" s="50"/>
+      <c r="E194" s="50"/>
     </row>
     <row r="195" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D195" s="51"/>
-      <c r="E195" s="51"/>
+      <c r="D195" s="50"/>
+      <c r="E195" s="50"/>
     </row>
     <row r="196" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D196" s="51"/>
-      <c r="E196" s="51"/>
+      <c r="D196" s="50"/>
+      <c r="E196" s="50"/>
     </row>
     <row r="197" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D197" s="51"/>
-      <c r="E197" s="51"/>
+      <c r="D197" s="50"/>
+      <c r="E197" s="50"/>
     </row>
     <row r="198" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D198" s="51"/>
-      <c r="E198" s="51"/>
+      <c r="D198" s="50"/>
+      <c r="E198" s="50"/>
     </row>
     <row r="199" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D199" s="51"/>
-      <c r="E199" s="51"/>
+      <c r="D199" s="50"/>
+      <c r="E199" s="50"/>
     </row>
     <row r="200" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D200" s="51"/>
-      <c r="E200" s="51"/>
+      <c r="D200" s="50"/>
+      <c r="E200" s="50"/>
     </row>
     <row r="201" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D201" s="51"/>
-      <c r="E201" s="51"/>
+      <c r="D201" s="50"/>
+      <c r="E201" s="50"/>
     </row>
     <row r="202" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D202" s="51"/>
-      <c r="E202" s="51"/>
+      <c r="D202" s="50"/>
+      <c r="E202" s="50"/>
     </row>
     <row r="203" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D203" s="51"/>
-      <c r="E203" s="51"/>
+      <c r="D203" s="50"/>
+      <c r="E203" s="50"/>
     </row>
     <row r="204" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D204" s="51"/>
-      <c r="E204" s="51"/>
+      <c r="D204" s="50"/>
+      <c r="E204" s="50"/>
     </row>
     <row r="205" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D205" s="51"/>
-      <c r="E205" s="51"/>
+      <c r="D205" s="50"/>
+      <c r="E205" s="50"/>
     </row>
     <row r="206" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D206" s="51"/>
-      <c r="E206" s="51"/>
+      <c r="D206" s="50"/>
+      <c r="E206" s="50"/>
     </row>
     <row r="207" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D207" s="51"/>
-      <c r="E207" s="51"/>
+      <c r="D207" s="50"/>
+      <c r="E207" s="50"/>
     </row>
     <row r="208" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D208" s="51"/>
-      <c r="E208" s="51"/>
+      <c r="D208" s="50"/>
+      <c r="E208" s="50"/>
     </row>
     <row r="209" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D209" s="51"/>
-      <c r="E209" s="51"/>
+      <c r="D209" s="50"/>
+      <c r="E209" s="50"/>
     </row>
     <row r="210" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D210" s="51"/>
-      <c r="E210" s="51"/>
+      <c r="D210" s="50"/>
+      <c r="E210" s="50"/>
     </row>
     <row r="211" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D211" s="51"/>
-      <c r="E211" s="51"/>
+      <c r="D211" s="50"/>
+      <c r="E211" s="50"/>
     </row>
     <row r="212" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D212" s="51"/>
-      <c r="E212" s="51"/>
+      <c r="D212" s="50"/>
+      <c r="E212" s="50"/>
     </row>
     <row r="213" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D213" s="51"/>
-      <c r="E213" s="51"/>
+      <c r="D213" s="50"/>
+      <c r="E213" s="50"/>
     </row>
     <row r="214" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D214" s="51"/>
-      <c r="E214" s="51"/>
+      <c r="D214" s="50"/>
+      <c r="E214" s="50"/>
     </row>
     <row r="215" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D215" s="51"/>
-      <c r="E215" s="51"/>
+      <c r="D215" s="50"/>
+      <c r="E215" s="50"/>
     </row>
     <row r="216" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D216" s="51"/>
-      <c r="E216" s="51"/>
+      <c r="D216" s="50"/>
+      <c r="E216" s="50"/>
     </row>
     <row r="217" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D217" s="51"/>
-      <c r="E217" s="51"/>
+      <c r="D217" s="50"/>
+      <c r="E217" s="50"/>
     </row>
     <row r="218" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D218" s="51"/>
-      <c r="E218" s="51"/>
+      <c r="D218" s="50"/>
+      <c r="E218" s="50"/>
     </row>
     <row r="219" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D219" s="51"/>
-      <c r="E219" s="51"/>
+      <c r="D219" s="50"/>
+      <c r="E219" s="50"/>
     </row>
     <row r="220" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D220" s="51"/>
-      <c r="E220" s="51"/>
+      <c r="D220" s="50"/>
+      <c r="E220" s="50"/>
     </row>
     <row r="221" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D221" s="51"/>
-      <c r="E221" s="51"/>
+      <c r="D221" s="50"/>
+      <c r="E221" s="50"/>
     </row>
     <row r="222" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D222" s="51"/>
-      <c r="E222" s="51"/>
+      <c r="D222" s="50"/>
+      <c r="E222" s="50"/>
     </row>
     <row r="223" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D223" s="51"/>
-      <c r="E223" s="51"/>
+      <c r="D223" s="50"/>
+      <c r="E223" s="50"/>
     </row>
     <row r="224" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D224" s="51"/>
-      <c r="E224" s="51"/>
+      <c r="D224" s="50"/>
+      <c r="E224" s="50"/>
     </row>
     <row r="225" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D225" s="51"/>
-      <c r="E225" s="51"/>
+      <c r="D225" s="50"/>
+      <c r="E225" s="50"/>
     </row>
     <row r="226" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D226" s="51"/>
-      <c r="E226" s="51"/>
+      <c r="D226" s="50"/>
+      <c r="E226" s="50"/>
     </row>
     <row r="227" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D227" s="51"/>
-      <c r="E227" s="51"/>
+      <c r="D227" s="50"/>
+      <c r="E227" s="50"/>
     </row>
     <row r="228" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D228" s="51"/>
-      <c r="E228" s="51"/>
+      <c r="D228" s="50"/>
+      <c r="E228" s="50"/>
     </row>
     <row r="229" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D229" s="51"/>
-      <c r="E229" s="51"/>
+      <c r="D229" s="50"/>
+      <c r="E229" s="50"/>
     </row>
     <row r="230" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D230" s="51"/>
-      <c r="E230" s="51"/>
+      <c r="D230" s="50"/>
+      <c r="E230" s="50"/>
     </row>
     <row r="231" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D231" s="51"/>
-      <c r="E231" s="51"/>
+      <c r="D231" s="50"/>
+      <c r="E231" s="50"/>
     </row>
     <row r="232" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D232" s="51"/>
-      <c r="E232" s="51"/>
+      <c r="D232" s="50"/>
+      <c r="E232" s="50"/>
     </row>
     <row r="233" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D233" s="51"/>
-      <c r="E233" s="51"/>
+      <c r="D233" s="50"/>
+      <c r="E233" s="50"/>
     </row>
     <row r="234" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D234" s="51"/>
-      <c r="E234" s="51"/>
+      <c r="D234" s="50"/>
+      <c r="E234" s="50"/>
     </row>
     <row r="235" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D235" s="51"/>
-      <c r="E235" s="51"/>
+      <c r="D235" s="50"/>
+      <c r="E235" s="50"/>
     </row>
     <row r="236" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D236" s="51"/>
-      <c r="E236" s="51"/>
+      <c r="D236" s="50"/>
+      <c r="E236" s="50"/>
     </row>
     <row r="237" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D237" s="51"/>
-      <c r="E237" s="51"/>
+      <c r="D237" s="50"/>
+      <c r="E237" s="50"/>
     </row>
     <row r="238" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D238" s="51"/>
-      <c r="E238" s="51"/>
+      <c r="D238" s="50"/>
+      <c r="E238" s="50"/>
     </row>
     <row r="239" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D239" s="51"/>
-      <c r="E239" s="51"/>
+      <c r="D239" s="50"/>
+      <c r="E239" s="50"/>
     </row>
     <row r="240" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D240" s="51"/>
-      <c r="E240" s="51"/>
+      <c r="D240" s="50"/>
+      <c r="E240" s="50"/>
     </row>
     <row r="241" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D241" s="51"/>
-      <c r="E241" s="51"/>
+      <c r="D241" s="50"/>
+      <c r="E241" s="50"/>
     </row>
     <row r="242" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D242" s="51"/>
-      <c r="E242" s="51"/>
+      <c r="D242" s="50"/>
+      <c r="E242" s="50"/>
     </row>
     <row r="243" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D243" s="51"/>
-      <c r="E243" s="51"/>
+      <c r="D243" s="50"/>
+      <c r="E243" s="50"/>
     </row>
     <row r="244" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D244" s="51"/>
-      <c r="E244" s="51"/>
+      <c r="D244" s="50"/>
+      <c r="E244" s="50"/>
     </row>
     <row r="245" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D245" s="51"/>
-      <c r="E245" s="51"/>
+      <c r="D245" s="50"/>
+      <c r="E245" s="50"/>
     </row>
     <row r="246" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D246" s="51"/>
-      <c r="E246" s="51"/>
+      <c r="D246" s="50"/>
+      <c r="E246" s="50"/>
     </row>
     <row r="247" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D247" s="51"/>
-      <c r="E247" s="51"/>
+      <c r="D247" s="50"/>
+      <c r="E247" s="50"/>
     </row>
     <row r="248" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D248" s="51"/>
-      <c r="E248" s="51"/>
+      <c r="D248" s="50"/>
+      <c r="E248" s="50"/>
     </row>
     <row r="249" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D249" s="51"/>
-      <c r="E249" s="51"/>
+      <c r="D249" s="50"/>
+      <c r="E249" s="50"/>
     </row>
     <row r="250" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D250" s="51"/>
-      <c r="E250" s="51"/>
+      <c r="D250" s="50"/>
+      <c r="E250" s="50"/>
     </row>
     <row r="251" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D251" s="51"/>
-      <c r="E251" s="51"/>
+      <c r="D251" s="50"/>
+      <c r="E251" s="50"/>
     </row>
     <row r="252" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D252" s="51"/>
-      <c r="E252" s="51"/>
+      <c r="D252" s="50"/>
+      <c r="E252" s="50"/>
     </row>
     <row r="253" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D253" s="51"/>
-      <c r="E253" s="51"/>
+      <c r="D253" s="50"/>
+      <c r="E253" s="50"/>
     </row>
     <row r="254" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D254" s="51"/>
-      <c r="E254" s="51"/>
+      <c r="D254" s="50"/>
+      <c r="E254" s="50"/>
     </row>
     <row r="255" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D255" s="51"/>
-      <c r="E255" s="51"/>
+      <c r="D255" s="50"/>
+      <c r="E255" s="50"/>
     </row>
     <row r="256" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D256" s="51"/>
-      <c r="E256" s="51"/>
+      <c r="D256" s="50"/>
+      <c r="E256" s="50"/>
     </row>
     <row r="257" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D257" s="51"/>
-      <c r="E257" s="51"/>
+      <c r="D257" s="50"/>
+      <c r="E257" s="50"/>
     </row>
     <row r="258" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D258" s="51"/>
-      <c r="E258" s="51"/>
+      <c r="D258" s="50"/>
+      <c r="E258" s="50"/>
     </row>
     <row r="259" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D259" s="51"/>
-      <c r="E259" s="51"/>
+      <c r="D259" s="50"/>
+      <c r="E259" s="50"/>
     </row>
     <row r="260" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D260" s="51"/>
-      <c r="E260" s="51"/>
+      <c r="D260" s="50"/>
+      <c r="E260" s="50"/>
     </row>
     <row r="261" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D261" s="51"/>
-      <c r="E261" s="51"/>
+      <c r="D261" s="50"/>
+      <c r="E261" s="50"/>
     </row>
     <row r="262" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D262" s="51"/>
-      <c r="E262" s="51"/>
+      <c r="D262" s="50"/>
+      <c r="E262" s="50"/>
     </row>
     <row r="263" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D263" s="51"/>
-      <c r="E263" s="51"/>
+      <c r="D263" s="50"/>
+      <c r="E263" s="50"/>
     </row>
     <row r="264" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D264" s="51"/>
-      <c r="E264" s="51"/>
+      <c r="D264" s="50"/>
+      <c r="E264" s="50"/>
     </row>
     <row r="265" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D265" s="51"/>
-      <c r="E265" s="51"/>
+      <c r="D265" s="50"/>
+      <c r="E265" s="50"/>
     </row>
     <row r="266" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D266" s="51"/>
-      <c r="E266" s="51"/>
+      <c r="D266" s="50"/>
+      <c r="E266" s="50"/>
     </row>
     <row r="267" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D267" s="51"/>
-      <c r="E267" s="51"/>
+      <c r="D267" s="50"/>
+      <c r="E267" s="50"/>
     </row>
     <row r="268" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D268" s="51"/>
-      <c r="E268" s="51"/>
+      <c r="D268" s="50"/>
+      <c r="E268" s="50"/>
     </row>
     <row r="269" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D269" s="51"/>
-      <c r="E269" s="51"/>
+      <c r="D269" s="50"/>
+      <c r="E269" s="50"/>
     </row>
     <row r="270" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D270" s="51"/>
-      <c r="E270" s="51"/>
+      <c r="D270" s="50"/>
+      <c r="E270" s="50"/>
     </row>
     <row r="271" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D271" s="51"/>
-      <c r="E271" s="51"/>
+      <c r="D271" s="50"/>
+      <c r="E271" s="50"/>
     </row>
     <row r="272" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D272" s="51"/>
-      <c r="E272" s="51"/>
+      <c r="D272" s="50"/>
+      <c r="E272" s="50"/>
     </row>
     <row r="273" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D273" s="51"/>
-      <c r="E273" s="51"/>
+      <c r="D273" s="50"/>
+      <c r="E273" s="50"/>
     </row>
     <row r="274" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D274" s="51"/>
-      <c r="E274" s="51"/>
+      <c r="D274" s="50"/>
+      <c r="E274" s="50"/>
     </row>
     <row r="275" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D275" s="51"/>
-      <c r="E275" s="51"/>
+      <c r="D275" s="50"/>
+      <c r="E275" s="50"/>
     </row>
     <row r="276" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D276" s="51"/>
-      <c r="E276" s="51"/>
+      <c r="D276" s="50"/>
+      <c r="E276" s="50"/>
     </row>
     <row r="277" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D277" s="51"/>
-      <c r="E277" s="51"/>
+      <c r="D277" s="50"/>
+      <c r="E277" s="50"/>
     </row>
     <row r="278" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D278" s="51"/>
-      <c r="E278" s="51"/>
+      <c r="D278" s="50"/>
+      <c r="E278" s="50"/>
     </row>
     <row r="279" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D279" s="51"/>
-      <c r="E279" s="51"/>
+      <c r="D279" s="50"/>
+      <c r="E279" s="50"/>
     </row>
     <row r="280" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D280" s="51"/>
-      <c r="E280" s="51"/>
+      <c r="D280" s="50"/>
+      <c r="E280" s="50"/>
     </row>
     <row r="281" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D281" s="51"/>
-      <c r="E281" s="51"/>
+      <c r="D281" s="50"/>
+      <c r="E281" s="50"/>
     </row>
     <row r="282" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D282" s="51"/>
-      <c r="E282" s="51"/>
+      <c r="D282" s="50"/>
+      <c r="E282" s="50"/>
     </row>
     <row r="283" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D283" s="51"/>
-      <c r="E283" s="51"/>
+      <c r="D283" s="50"/>
+      <c r="E283" s="50"/>
     </row>
     <row r="284" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D284" s="51"/>
-      <c r="E284" s="51"/>
+      <c r="D284" s="50"/>
+      <c r="E284" s="50"/>
     </row>
     <row r="285" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D285" s="51"/>
-      <c r="E285" s="51"/>
+      <c r="D285" s="50"/>
+      <c r="E285" s="50"/>
     </row>
     <row r="286" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D286" s="51"/>
-      <c r="E286" s="51"/>
+      <c r="D286" s="50"/>
+      <c r="E286" s="50"/>
     </row>
     <row r="287" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D287" s="51"/>
-      <c r="E287" s="51"/>
+      <c r="D287" s="50"/>
+      <c r="E287" s="50"/>
     </row>
     <row r="288" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D288" s="51"/>
-      <c r="E288" s="51"/>
+      <c r="D288" s="50"/>
+      <c r="E288" s="50"/>
     </row>
     <row r="289" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D289" s="51"/>
-      <c r="E289" s="51"/>
+      <c r="D289" s="50"/>
+      <c r="E289" s="50"/>
     </row>
     <row r="290" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D290" s="51"/>
-      <c r="E290" s="51"/>
+      <c r="D290" s="50"/>
+      <c r="E290" s="50"/>
     </row>
     <row r="291" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D291" s="51"/>
-      <c r="E291" s="51"/>
+      <c r="D291" s="50"/>
+      <c r="E291" s="50"/>
     </row>
     <row r="292" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D292" s="51"/>
-      <c r="E292" s="51"/>
+      <c r="D292" s="50"/>
+      <c r="E292" s="50"/>
     </row>
     <row r="293" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D293" s="51"/>
-      <c r="E293" s="51"/>
+      <c r="D293" s="50"/>
+      <c r="E293" s="50"/>
     </row>
     <row r="294" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D294" s="51"/>
-      <c r="E294" s="51"/>
+      <c r="D294" s="50"/>
+      <c r="E294" s="50"/>
     </row>
     <row r="295" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D295" s="51"/>
-      <c r="E295" s="51"/>
+      <c r="D295" s="50"/>
+      <c r="E295" s="50"/>
     </row>
     <row r="296" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D296" s="51"/>
-      <c r="E296" s="51"/>
+      <c r="D296" s="50"/>
+      <c r="E296" s="50"/>
     </row>
     <row r="297" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D297" s="51"/>
-      <c r="E297" s="51"/>
+      <c r="D297" s="50"/>
+      <c r="E297" s="50"/>
     </row>
     <row r="298" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D298" s="51"/>
-      <c r="E298" s="51"/>
+      <c r="D298" s="50"/>
+      <c r="E298" s="50"/>
     </row>
     <row r="299" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D299" s="51"/>
-      <c r="E299" s="51"/>
+      <c r="D299" s="50"/>
+      <c r="E299" s="50"/>
     </row>
     <row r="300" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D300" s="51"/>
-      <c r="E300" s="51"/>
+      <c r="D300" s="50"/>
+      <c r="E300" s="50"/>
     </row>
     <row r="301" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D301" s="51"/>
-      <c r="E301" s="51"/>
+      <c r="D301" s="50"/>
+      <c r="E301" s="50"/>
     </row>
     <row r="302" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D302" s="51"/>
-      <c r="E302" s="51"/>
+      <c r="D302" s="50"/>
+      <c r="E302" s="50"/>
     </row>
     <row r="303" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D303" s="51"/>
-      <c r="E303" s="51"/>
+      <c r="D303" s="50"/>
+      <c r="E303" s="50"/>
     </row>
     <row r="304" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D304" s="51"/>
-      <c r="E304" s="51"/>
+      <c r="D304" s="50"/>
+      <c r="E304" s="50"/>
     </row>
     <row r="305" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D305" s="51"/>
-      <c r="E305" s="51"/>
+      <c r="D305" s="50"/>
+      <c r="E305" s="50"/>
     </row>
     <row r="306" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D306" s="51"/>
-      <c r="E306" s="51"/>
+      <c r="D306" s="50"/>
+      <c r="E306" s="50"/>
     </row>
     <row r="307" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D307" s="51"/>
-      <c r="E307" s="51"/>
+      <c r="D307" s="50"/>
+      <c r="E307" s="50"/>
     </row>
     <row r="308" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D308" s="51"/>
-      <c r="E308" s="51"/>
+      <c r="D308" s="50"/>
+      <c r="E308" s="50"/>
     </row>
     <row r="309" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D309" s="51"/>
-      <c r="E309" s="51"/>
+      <c r="D309" s="50"/>
+      <c r="E309" s="50"/>
     </row>
     <row r="310" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D310" s="51"/>
-      <c r="E310" s="51"/>
+      <c r="D310" s="50"/>
+      <c r="E310" s="50"/>
     </row>
     <row r="311" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D311" s="51"/>
-      <c r="E311" s="51"/>
+      <c r="D311" s="50"/>
+      <c r="E311" s="50"/>
     </row>
     <row r="312" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D312" s="51"/>
-      <c r="E312" s="51"/>
+      <c r="D312" s="50"/>
+      <c r="E312" s="50"/>
     </row>
     <row r="313" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D313" s="51"/>
-      <c r="E313" s="51"/>
+      <c r="D313" s="50"/>
+      <c r="E313" s="50"/>
     </row>
     <row r="314" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D314" s="51"/>
-      <c r="E314" s="51"/>
+      <c r="D314" s="50"/>
+      <c r="E314" s="50"/>
     </row>
     <row r="315" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D315" s="51"/>
-      <c r="E315" s="51"/>
+      <c r="D315" s="50"/>
+      <c r="E315" s="50"/>
     </row>
     <row r="316" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D316" s="51"/>
-      <c r="E316" s="51"/>
+      <c r="D316" s="50"/>
+      <c r="E316" s="50"/>
     </row>
     <row r="317" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D317" s="51"/>
-      <c r="E317" s="51"/>
+      <c r="D317" s="50"/>
+      <c r="E317" s="50"/>
     </row>
     <row r="318" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D318" s="51"/>
-      <c r="E318" s="51"/>
+      <c r="D318" s="50"/>
+      <c r="E318" s="50"/>
     </row>
     <row r="319" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D319" s="51"/>
-      <c r="E319" s="51"/>
+      <c r="D319" s="50"/>
+      <c r="E319" s="50"/>
     </row>
     <row r="320" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D320" s="51"/>
-      <c r="E320" s="51"/>
+      <c r="D320" s="50"/>
+      <c r="E320" s="50"/>
     </row>
     <row r="321" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D321" s="51"/>
-      <c r="E321" s="51"/>
+      <c r="D321" s="50"/>
+      <c r="E321" s="50"/>
     </row>
     <row r="322" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D322" s="51"/>
-      <c r="E322" s="51"/>
+      <c r="D322" s="50"/>
+      <c r="E322" s="50"/>
     </row>
     <row r="323" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D323" s="51"/>
-      <c r="E323" s="51"/>
+      <c r="D323" s="50"/>
+      <c r="E323" s="50"/>
     </row>
     <row r="324" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D324" s="51"/>
-      <c r="E324" s="51"/>
+      <c r="D324" s="50"/>
+      <c r="E324" s="50"/>
     </row>
     <row r="325" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D325" s="51"/>
-      <c r="E325" s="51"/>
+      <c r="D325" s="50"/>
+      <c r="E325" s="50"/>
     </row>
     <row r="326" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D326" s="51"/>
-      <c r="E326" s="51"/>
+      <c r="D326" s="50"/>
+      <c r="E326" s="50"/>
     </row>
     <row r="327" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D327" s="51"/>
-      <c r="E327" s="51"/>
+      <c r="D327" s="50"/>
+      <c r="E327" s="50"/>
     </row>
     <row r="328" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D328" s="51"/>
-      <c r="E328" s="51"/>
+      <c r="D328" s="50"/>
+      <c r="E328" s="50"/>
     </row>
     <row r="329" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D329" s="51"/>
-      <c r="E329" s="51"/>
+      <c r="D329" s="50"/>
+      <c r="E329" s="50"/>
     </row>
     <row r="330" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D330" s="51"/>
-      <c r="E330" s="51"/>
+      <c r="D330" s="50"/>
+      <c r="E330" s="50"/>
     </row>
     <row r="331" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D331" s="51"/>
-      <c r="E331" s="51"/>
+      <c r="D331" s="50"/>
+      <c r="E331" s="50"/>
     </row>
     <row r="332" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D332" s="51"/>
-      <c r="E332" s="51"/>
+      <c r="D332" s="50"/>
+      <c r="E332" s="50"/>
     </row>
     <row r="333" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D333" s="51"/>
-      <c r="E333" s="51"/>
+      <c r="D333" s="50"/>
+      <c r="E333" s="50"/>
     </row>
     <row r="334" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D334" s="51"/>
-      <c r="E334" s="51"/>
+      <c r="D334" s="50"/>
+      <c r="E334" s="50"/>
     </row>
     <row r="335" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D335" s="51"/>
-      <c r="E335" s="51"/>
+      <c r="D335" s="50"/>
+      <c r="E335" s="50"/>
     </row>
     <row r="336" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D336" s="51"/>
-      <c r="E336" s="51"/>
+      <c r="D336" s="50"/>
+      <c r="E336" s="50"/>
     </row>
     <row r="337" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D337" s="51"/>
-      <c r="E337" s="51"/>
+      <c r="D337" s="50"/>
+      <c r="E337" s="50"/>
     </row>
     <row r="338" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D338" s="51"/>
-      <c r="E338" s="51"/>
+      <c r="D338" s="50"/>
+      <c r="E338" s="50"/>
     </row>
     <row r="339" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D339" s="51"/>
-      <c r="E339" s="51"/>
+      <c r="D339" s="50"/>
+      <c r="E339" s="50"/>
     </row>
     <row r="340" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D340" s="51"/>
-      <c r="E340" s="51"/>
+      <c r="D340" s="50"/>
+      <c r="E340" s="50"/>
     </row>
     <row r="341" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D341" s="51"/>
-      <c r="E341" s="51"/>
+      <c r="D341" s="50"/>
+      <c r="E341" s="50"/>
     </row>
     <row r="342" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D342" s="51"/>
-      <c r="E342" s="51"/>
+      <c r="D342" s="50"/>
+      <c r="E342" s="50"/>
     </row>
     <row r="343" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D343" s="51"/>
-      <c r="E343" s="51"/>
+      <c r="D343" s="50"/>
+      <c r="E343" s="50"/>
     </row>
     <row r="344" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D344" s="51"/>
-      <c r="E344" s="51"/>
+      <c r="D344" s="50"/>
+      <c r="E344" s="50"/>
     </row>
     <row r="345" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D345" s="51"/>
-      <c r="E345" s="51"/>
+      <c r="D345" s="50"/>
+      <c r="E345" s="50"/>
     </row>
     <row r="346" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D346" s="51"/>
-      <c r="E346" s="51"/>
+      <c r="D346" s="50"/>
+      <c r="E346" s="50"/>
     </row>
     <row r="347" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D347" s="51"/>
-      <c r="E347" s="51"/>
+      <c r="D347" s="50"/>
+      <c r="E347" s="50"/>
     </row>
     <row r="348" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D348" s="51"/>
-      <c r="E348" s="51"/>
+      <c r="D348" s="50"/>
+      <c r="E348" s="50"/>
     </row>
     <row r="349" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D349" s="51"/>
-      <c r="E349" s="51"/>
+      <c r="D349" s="50"/>
+      <c r="E349" s="50"/>
     </row>
     <row r="350" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D350" s="51"/>
-      <c r="E350" s="51"/>
+      <c r="D350" s="50"/>
+      <c r="E350" s="50"/>
     </row>
     <row r="351" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D351" s="51"/>
-      <c r="E351" s="51"/>
+      <c r="D351" s="50"/>
+      <c r="E351" s="50"/>
     </row>
     <row r="352" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D352" s="51"/>
-      <c r="E352" s="51"/>
+      <c r="D352" s="50"/>
+      <c r="E352" s="50"/>
     </row>
     <row r="353" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D353" s="51"/>
-      <c r="E353" s="51"/>
+      <c r="D353" s="50"/>
+      <c r="E353" s="50"/>
     </row>
     <row r="354" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D354" s="51"/>
-      <c r="E354" s="51"/>
+      <c r="D354" s="50"/>
+      <c r="E354" s="50"/>
     </row>
     <row r="355" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D355" s="51"/>
-      <c r="E355" s="51"/>
+      <c r="D355" s="50"/>
+      <c r="E355" s="50"/>
     </row>
     <row r="356" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D356" s="51"/>
-      <c r="E356" s="51"/>
+      <c r="D356" s="50"/>
+      <c r="E356" s="50"/>
     </row>
     <row r="357" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D357" s="51"/>
-      <c r="E357" s="51"/>
+      <c r="D357" s="50"/>
+      <c r="E357" s="50"/>
     </row>
     <row r="358" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D358" s="51"/>
-      <c r="E358" s="51"/>
+      <c r="D358" s="50"/>
+      <c r="E358" s="50"/>
     </row>
     <row r="359" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D359" s="51"/>
-      <c r="E359" s="51"/>
+      <c r="D359" s="50"/>
+      <c r="E359" s="50"/>
     </row>
     <row r="360" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D360" s="51"/>
-      <c r="E360" s="51"/>
+      <c r="D360" s="50"/>
+      <c r="E360" s="50"/>
     </row>
     <row r="361" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D361" s="51"/>
-      <c r="E361" s="51"/>
+      <c r="D361" s="50"/>
+      <c r="E361" s="50"/>
     </row>
     <row r="362" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D362" s="51"/>
-      <c r="E362" s="51"/>
+      <c r="D362" s="50"/>
+      <c r="E362" s="50"/>
     </row>
     <row r="363" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D363" s="51"/>
-      <c r="E363" s="51"/>
+      <c r="D363" s="50"/>
+      <c r="E363" s="50"/>
     </row>
     <row r="364" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D364" s="51"/>
-      <c r="E364" s="51"/>
+      <c r="D364" s="50"/>
+      <c r="E364" s="50"/>
     </row>
     <row r="365" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D365" s="51"/>
-      <c r="E365" s="51"/>
+      <c r="D365" s="50"/>
+      <c r="E365" s="50"/>
     </row>
     <row r="366" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D366" s="51"/>
-      <c r="E366" s="51"/>
+      <c r="D366" s="50"/>
+      <c r="E366" s="50"/>
     </row>
     <row r="367" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D367" s="51"/>
-      <c r="E367" s="51"/>
+      <c r="D367" s="50"/>
+      <c r="E367" s="50"/>
     </row>
     <row r="368" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D368" s="51"/>
-      <c r="E368" s="51"/>
+      <c r="D368" s="50"/>
+      <c r="E368" s="50"/>
     </row>
     <row r="369" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D369" s="51"/>
-      <c r="E369" s="51"/>
+      <c r="D369" s="50"/>
+      <c r="E369" s="50"/>
     </row>
     <row r="370" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D370" s="51"/>
-      <c r="E370" s="51"/>
+      <c r="D370" s="50"/>
+      <c r="E370" s="50"/>
     </row>
     <row r="371" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D371" s="51"/>
-      <c r="E371" s="51"/>
+      <c r="D371" s="50"/>
+      <c r="E371" s="50"/>
     </row>
     <row r="372" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D372" s="51"/>
-      <c r="E372" s="51"/>
+      <c r="D372" s="50"/>
+      <c r="E372" s="50"/>
     </row>
     <row r="373" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D373" s="51"/>
-      <c r="E373" s="51"/>
+      <c r="D373" s="50"/>
+      <c r="E373" s="50"/>
     </row>
     <row r="374" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D374" s="51"/>
-      <c r="E374" s="51"/>
+      <c r="D374" s="50"/>
+      <c r="E374" s="50"/>
     </row>
     <row r="375" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D375" s="51"/>
-      <c r="E375" s="51"/>
+      <c r="D375" s="50"/>
+      <c r="E375" s="50"/>
     </row>
     <row r="376" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D376" s="51"/>
-      <c r="E376" s="51"/>
+      <c r="D376" s="50"/>
+      <c r="E376" s="50"/>
     </row>
     <row r="377" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D377" s="51"/>
-      <c r="E377" s="51"/>
+      <c r="D377" s="50"/>
+      <c r="E377" s="50"/>
     </row>
     <row r="378" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D378" s="51"/>
-      <c r="E378" s="51"/>
+      <c r="D378" s="50"/>
+      <c r="E378" s="50"/>
     </row>
     <row r="379" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D379" s="51"/>
-      <c r="E379" s="51"/>
+      <c r="D379" s="50"/>
+      <c r="E379" s="50"/>
     </row>
     <row r="380" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D380" s="51"/>
-      <c r="E380" s="51"/>
+      <c r="D380" s="50"/>
+      <c r="E380" s="50"/>
     </row>
     <row r="381" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D381" s="51"/>
-      <c r="E381" s="51"/>
+      <c r="D381" s="50"/>
+      <c r="E381" s="50"/>
     </row>
     <row r="382" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D382" s="51"/>
-      <c r="E382" s="51"/>
+      <c r="D382" s="50"/>
+      <c r="E382" s="50"/>
     </row>
     <row r="383" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D383" s="51"/>
-      <c r="E383" s="51"/>
+      <c r="D383" s="50"/>
+      <c r="E383" s="50"/>
     </row>
     <row r="384" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D384" s="51"/>
-      <c r="E384" s="51"/>
+      <c r="D384" s="50"/>
+      <c r="E384" s="50"/>
     </row>
     <row r="385" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D385" s="51"/>
-      <c r="E385" s="51"/>
+      <c r="D385" s="50"/>
+      <c r="E385" s="50"/>
     </row>
     <row r="386" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D386" s="51"/>
-      <c r="E386" s="51"/>
+      <c r="D386" s="50"/>
+      <c r="E386" s="50"/>
     </row>
     <row r="387" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D387" s="51"/>
-      <c r="E387" s="51"/>
+      <c r="D387" s="50"/>
+      <c r="E387" s="50"/>
     </row>
     <row r="388" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D388" s="51"/>
-      <c r="E388" s="51"/>
+      <c r="D388" s="50"/>
+      <c r="E388" s="50"/>
     </row>
     <row r="389" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D389" s="51"/>
-      <c r="E389" s="51"/>
+      <c r="D389" s="50"/>
+      <c r="E389" s="50"/>
     </row>
     <row r="390" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D390" s="51"/>
-      <c r="E390" s="51"/>
+      <c r="D390" s="50"/>
+      <c r="E390" s="50"/>
     </row>
     <row r="391" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D391" s="51"/>
-      <c r="E391" s="51"/>
+      <c r="D391" s="50"/>
+      <c r="E391" s="50"/>
     </row>
     <row r="392" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D392" s="51"/>
-      <c r="E392" s="51"/>
+      <c r="D392" s="50"/>
+      <c r="E392" s="50"/>
     </row>
     <row r="393" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D393" s="51"/>
-      <c r="E393" s="51"/>
+      <c r="D393" s="50"/>
+      <c r="E393" s="50"/>
     </row>
     <row r="394" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D394" s="51"/>
-      <c r="E394" s="51"/>
+      <c r="D394" s="50"/>
+      <c r="E394" s="50"/>
     </row>
     <row r="395" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D395" s="51"/>
-      <c r="E395" s="51"/>
+      <c r="D395" s="50"/>
+      <c r="E395" s="50"/>
     </row>
     <row r="396" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D396" s="51"/>
-      <c r="E396" s="51"/>
+      <c r="D396" s="50"/>
+      <c r="E396" s="50"/>
     </row>
     <row r="397" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D397" s="51"/>
-      <c r="E397" s="51"/>
+      <c r="D397" s="50"/>
+      <c r="E397" s="50"/>
     </row>
     <row r="398" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D398" s="51"/>
-      <c r="E398" s="51"/>
+      <c r="D398" s="50"/>
+      <c r="E398" s="50"/>
     </row>
     <row r="399" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D399" s="51"/>
-      <c r="E399" s="51"/>
+      <c r="D399" s="50"/>
+      <c r="E399" s="50"/>
     </row>
     <row r="400" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D400" s="51"/>
-      <c r="E400" s="51"/>
+      <c r="D400" s="50"/>
+      <c r="E400" s="50"/>
     </row>
     <row r="401" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D401" s="51"/>
-      <c r="E401" s="51"/>
+      <c r="D401" s="50"/>
+      <c r="E401" s="50"/>
     </row>
     <row r="402" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D402" s="51"/>
-      <c r="E402" s="51"/>
+      <c r="D402" s="50"/>
+      <c r="E402" s="50"/>
     </row>
     <row r="403" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D403" s="51"/>
-      <c r="E403" s="51"/>
+      <c r="D403" s="50"/>
+      <c r="E403" s="50"/>
     </row>
     <row r="404" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D404" s="51"/>
-      <c r="E404" s="51"/>
+      <c r="D404" s="50"/>
+      <c r="E404" s="50"/>
     </row>
     <row r="405" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D405" s="51"/>
-      <c r="E405" s="51"/>
+      <c r="D405" s="50"/>
+      <c r="E405" s="50"/>
     </row>
     <row r="406" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D406" s="51"/>
-      <c r="E406" s="51"/>
+      <c r="D406" s="50"/>
+      <c r="E406" s="50"/>
     </row>
     <row r="407" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D407" s="51"/>
-      <c r="E407" s="51"/>
+      <c r="D407" s="50"/>
+      <c r="E407" s="50"/>
     </row>
     <row r="408" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D408" s="51"/>
-      <c r="E408" s="51"/>
+      <c r="D408" s="50"/>
+      <c r="E408" s="50"/>
     </row>
     <row r="409" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D409" s="51"/>
-      <c r="E409" s="51"/>
+      <c r="D409" s="50"/>
+      <c r="E409" s="50"/>
     </row>
     <row r="410" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D410" s="51"/>
-      <c r="E410" s="51"/>
+      <c r="D410" s="50"/>
+      <c r="E410" s="50"/>
     </row>
     <row r="411" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D411" s="51"/>
-      <c r="E411" s="51"/>
+      <c r="D411" s="50"/>
+      <c r="E411" s="50"/>
     </row>
     <row r="412" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D412" s="51"/>
-      <c r="E412" s="51"/>
+      <c r="D412" s="50"/>
+      <c r="E412" s="50"/>
     </row>
     <row r="413" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D413" s="51"/>
-      <c r="E413" s="51"/>
+      <c r="D413" s="50"/>
+      <c r="E413" s="50"/>
     </row>
     <row r="414" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D414" s="51"/>
-      <c r="E414" s="51"/>
+      <c r="D414" s="50"/>
+      <c r="E414" s="50"/>
     </row>
     <row r="415" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D415" s="51"/>
-      <c r="E415" s="51"/>
+      <c r="D415" s="50"/>
+      <c r="E415" s="50"/>
     </row>
     <row r="416" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D416" s="51"/>
-      <c r="E416" s="51"/>
+      <c r="D416" s="50"/>
+      <c r="E416" s="50"/>
     </row>
     <row r="417" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D417" s="51"/>
-      <c r="E417" s="51"/>
+      <c r="D417" s="50"/>
+      <c r="E417" s="50"/>
     </row>
     <row r="418" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D418" s="51"/>
-      <c r="E418" s="51"/>
+      <c r="D418" s="50"/>
+      <c r="E418" s="50"/>
     </row>
     <row r="419" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D419" s="51"/>
-      <c r="E419" s="51"/>
+      <c r="D419" s="50"/>
+      <c r="E419" s="50"/>
     </row>
     <row r="420" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D420" s="51"/>
-      <c r="E420" s="51"/>
+      <c r="D420" s="50"/>
+      <c r="E420" s="50"/>
     </row>
     <row r="421" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D421" s="51"/>
-      <c r="E421" s="51"/>
+      <c r="D421" s="50"/>
+      <c r="E421" s="50"/>
     </row>
     <row r="422" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D422" s="51"/>
-      <c r="E422" s="51"/>
+      <c r="D422" s="50"/>
+      <c r="E422" s="50"/>
     </row>
     <row r="423" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D423" s="51"/>
-      <c r="E423" s="51"/>
+      <c r="D423" s="50"/>
+      <c r="E423" s="50"/>
     </row>
     <row r="424" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D424" s="51"/>
-      <c r="E424" s="51"/>
+      <c r="D424" s="50"/>
+      <c r="E424" s="50"/>
     </row>
     <row r="425" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D425" s="51"/>
-      <c r="E425" s="51"/>
+      <c r="D425" s="50"/>
+      <c r="E425" s="50"/>
     </row>
     <row r="426" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D426" s="51"/>
-      <c r="E426" s="51"/>
+      <c r="D426" s="50"/>
+      <c r="E426" s="50"/>
     </row>
     <row r="427" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D427" s="51"/>
-      <c r="E427" s="51"/>
+      <c r="D427" s="50"/>
+      <c r="E427" s="50"/>
     </row>
     <row r="428" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D428" s="51"/>
-      <c r="E428" s="51"/>
+      <c r="D428" s="50"/>
+      <c r="E428" s="50"/>
     </row>
     <row r="429" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D429" s="51"/>
-      <c r="E429" s="51"/>
+      <c r="D429" s="50"/>
+      <c r="E429" s="50"/>
     </row>
     <row r="430" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D430" s="51"/>
-      <c r="E430" s="51"/>
+      <c r="D430" s="50"/>
+      <c r="E430" s="50"/>
     </row>
     <row r="431" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D431" s="51"/>
-      <c r="E431" s="51"/>
+      <c r="D431" s="50"/>
+      <c r="E431" s="50"/>
     </row>
     <row r="432" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D432" s="51"/>
-      <c r="E432" s="51"/>
+      <c r="D432" s="50"/>
+      <c r="E432" s="50"/>
     </row>
     <row r="433" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D433" s="51"/>
-      <c r="E433" s="51"/>
+      <c r="D433" s="50"/>
+      <c r="E433" s="50"/>
     </row>
     <row r="434" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D434" s="51"/>
-      <c r="E434" s="51"/>
+      <c r="D434" s="50"/>
+      <c r="E434" s="50"/>
     </row>
     <row r="435" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D435" s="51"/>
-      <c r="E435" s="51"/>
+      <c r="D435" s="50"/>
+      <c r="E435" s="50"/>
     </row>
     <row r="436" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D436" s="51"/>
-      <c r="E436" s="51"/>
+      <c r="D436" s="50"/>
+      <c r="E436" s="50"/>
     </row>
     <row r="437" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D437" s="51"/>
-      <c r="E437" s="51"/>
+      <c r="D437" s="50"/>
+      <c r="E437" s="50"/>
     </row>
     <row r="438" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D438" s="51"/>
-      <c r="E438" s="51"/>
+      <c r="D438" s="50"/>
+      <c r="E438" s="50"/>
     </row>
     <row r="439" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D439" s="51"/>
-      <c r="E439" s="51"/>
+      <c r="D439" s="50"/>
+      <c r="E439" s="50"/>
     </row>
     <row r="440" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D440" s="51"/>
-      <c r="E440" s="51"/>
+      <c r="D440" s="50"/>
+      <c r="E440" s="50"/>
     </row>
     <row r="441" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D441" s="51"/>
-      <c r="E441" s="51"/>
+      <c r="D441" s="50"/>
+      <c r="E441" s="50"/>
     </row>
     <row r="442" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D442" s="51"/>
-      <c r="E442" s="51"/>
+      <c r="D442" s="50"/>
+      <c r="E442" s="50"/>
     </row>
     <row r="443" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D443" s="51"/>
-      <c r="E443" s="51"/>
+      <c r="D443" s="50"/>
+      <c r="E443" s="50"/>
     </row>
     <row r="444" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D444" s="51"/>
-      <c r="E444" s="51"/>
+      <c r="D444" s="50"/>
+      <c r="E444" s="50"/>
     </row>
     <row r="445" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D445" s="51"/>
-      <c r="E445" s="51"/>
+      <c r="D445" s="50"/>
+      <c r="E445" s="50"/>
     </row>
     <row r="446" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D446" s="51"/>
-      <c r="E446" s="51"/>
+      <c r="D446" s="50"/>
+      <c r="E446" s="50"/>
     </row>
     <row r="447" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D447" s="51"/>
-      <c r="E447" s="51"/>
+      <c r="D447" s="50"/>
+      <c r="E447" s="50"/>
     </row>
     <row r="448" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D448" s="51"/>
-      <c r="E448" s="51"/>
+      <c r="D448" s="50"/>
+      <c r="E448" s="50"/>
     </row>
     <row r="449" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D449" s="51"/>
-      <c r="E449" s="51"/>
+      <c r="D449" s="50"/>
+      <c r="E449" s="50"/>
     </row>
     <row r="450" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D450" s="51"/>
-      <c r="E450" s="51"/>
+      <c r="D450" s="50"/>
+      <c r="E450" s="50"/>
     </row>
     <row r="451" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D451" s="51"/>
-      <c r="E451" s="51"/>
+      <c r="D451" s="50"/>
+      <c r="E451" s="50"/>
     </row>
     <row r="452" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D452" s="51"/>
-      <c r="E452" s="51"/>
+      <c r="D452" s="50"/>
+      <c r="E452" s="50"/>
     </row>
     <row r="453" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D453" s="51"/>
-      <c r="E453" s="51"/>
+      <c r="D453" s="50"/>
+      <c r="E453" s="50"/>
     </row>
     <row r="454" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D454" s="51"/>
-      <c r="E454" s="51"/>
+      <c r="D454" s="50"/>
+      <c r="E454" s="50"/>
     </row>
     <row r="455" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D455" s="51"/>
-      <c r="E455" s="51"/>
+      <c r="D455" s="50"/>
+      <c r="E455" s="50"/>
     </row>
     <row r="456" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D456" s="51"/>
-      <c r="E456" s="51"/>
+      <c r="D456" s="50"/>
+      <c r="E456" s="50"/>
     </row>
     <row r="457" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D457" s="51"/>
-      <c r="E457" s="51"/>
+      <c r="D457" s="50"/>
+      <c r="E457" s="50"/>
     </row>
     <row r="458" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D458" s="51"/>
-      <c r="E458" s="51"/>
+      <c r="D458" s="50"/>
+      <c r="E458" s="50"/>
     </row>
     <row r="459" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D459" s="51"/>
-      <c r="E459" s="51"/>
+      <c r="D459" s="50"/>
+      <c r="E459" s="50"/>
     </row>
     <row r="460" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D460" s="51"/>
-      <c r="E460" s="51"/>
+      <c r="D460" s="50"/>
+      <c r="E460" s="50"/>
     </row>
     <row r="461" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D461" s="51"/>
-      <c r="E461" s="51"/>
+      <c r="D461" s="50"/>
+      <c r="E461" s="50"/>
     </row>
     <row r="462" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D462" s="51"/>
-      <c r="E462" s="51"/>
+      <c r="D462" s="50"/>
+      <c r="E462" s="50"/>
     </row>
     <row r="463" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D463" s="51"/>
-      <c r="E463" s="51"/>
+      <c r="D463" s="50"/>
+      <c r="E463" s="50"/>
     </row>
     <row r="464" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D464" s="51"/>
-      <c r="E464" s="51"/>
+      <c r="D464" s="50"/>
+      <c r="E464" s="50"/>
     </row>
     <row r="465" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D465" s="51"/>
-      <c r="E465" s="51"/>
+      <c r="D465" s="50"/>
+      <c r="E465" s="50"/>
     </row>
     <row r="466" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D466" s="51"/>
-      <c r="E466" s="51"/>
+      <c r="D466" s="50"/>
+      <c r="E466" s="50"/>
     </row>
     <row r="467" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D467" s="51"/>
-      <c r="E467" s="51"/>
+      <c r="D467" s="50"/>
+      <c r="E467" s="50"/>
     </row>
     <row r="468" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D468" s="51"/>
-      <c r="E468" s="51"/>
+      <c r="D468" s="50"/>
+      <c r="E468" s="50"/>
     </row>
     <row r="469" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D469" s="51"/>
-      <c r="E469" s="51"/>
+      <c r="D469" s="50"/>
+      <c r="E469" s="50"/>
     </row>
     <row r="470" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D470" s="51"/>
-      <c r="E470" s="51"/>
+      <c r="D470" s="50"/>
+      <c r="E470" s="50"/>
     </row>
     <row r="471" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D471" s="51"/>
-      <c r="E471" s="51"/>
+      <c r="D471" s="50"/>
+      <c r="E471" s="50"/>
     </row>
     <row r="472" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D472" s="51"/>
-      <c r="E472" s="51"/>
+      <c r="D472" s="50"/>
+      <c r="E472" s="50"/>
     </row>
     <row r="473" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D473" s="51"/>
-      <c r="E473" s="51"/>
+      <c r="D473" s="50"/>
+      <c r="E473" s="50"/>
     </row>
     <row r="474" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D474" s="51"/>
-      <c r="E474" s="51"/>
+      <c r="D474" s="50"/>
+      <c r="E474" s="50"/>
     </row>
     <row r="475" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D475" s="51"/>
-      <c r="E475" s="51"/>
+      <c r="D475" s="50"/>
+      <c r="E475" s="50"/>
     </row>
     <row r="476" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D476" s="51"/>
-      <c r="E476" s="51"/>
+      <c r="D476" s="50"/>
+      <c r="E476" s="50"/>
     </row>
     <row r="477" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D477" s="51"/>
-      <c r="E477" s="51"/>
+      <c r="D477" s="50"/>
+      <c r="E477" s="50"/>
     </row>
     <row r="478" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D478" s="51"/>
-      <c r="E478" s="51"/>
+      <c r="D478" s="50"/>
+      <c r="E478" s="50"/>
     </row>
     <row r="479" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D479" s="51"/>
-      <c r="E479" s="51"/>
+      <c r="D479" s="50"/>
+      <c r="E479" s="50"/>
     </row>
     <row r="480" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D480" s="51"/>
-      <c r="E480" s="51"/>
+      <c r="D480" s="50"/>
+      <c r="E480" s="50"/>
     </row>
     <row r="481" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D481" s="51"/>
-      <c r="E481" s="51"/>
+      <c r="D481" s="50"/>
+      <c r="E481" s="50"/>
     </row>
     <row r="482" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D482" s="51"/>
-      <c r="E482" s="51"/>
+      <c r="D482" s="50"/>
+      <c r="E482" s="50"/>
     </row>
     <row r="483" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D483" s="51"/>
-      <c r="E483" s="51"/>
+      <c r="D483" s="50"/>
+      <c r="E483" s="50"/>
     </row>
     <row r="484" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D484" s="51"/>
-      <c r="E484" s="51"/>
+      <c r="D484" s="50"/>
+      <c r="E484" s="50"/>
     </row>
     <row r="485" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D485" s="51"/>
-      <c r="E485" s="51"/>
+      <c r="D485" s="50"/>
+      <c r="E485" s="50"/>
     </row>
     <row r="486" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D486" s="51"/>
-      <c r="E486" s="51"/>
+      <c r="D486" s="50"/>
+      <c r="E486" s="50"/>
     </row>
     <row r="487" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D487" s="51"/>
-      <c r="E487" s="51"/>
+      <c r="D487" s="50"/>
+      <c r="E487" s="50"/>
     </row>
     <row r="488" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D488" s="51"/>
-      <c r="E488" s="51"/>
+      <c r="D488" s="50"/>
+      <c r="E488" s="50"/>
     </row>
     <row r="489" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D489" s="51"/>
-      <c r="E489" s="51"/>
+      <c r="D489" s="50"/>
+      <c r="E489" s="50"/>
     </row>
     <row r="490" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D490" s="51"/>
-      <c r="E490" s="51"/>
+      <c r="D490" s="50"/>
+      <c r="E490" s="50"/>
     </row>
     <row r="491" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D491" s="51"/>
-      <c r="E491" s="51"/>
+      <c r="D491" s="50"/>
+      <c r="E491" s="50"/>
     </row>
     <row r="492" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D492" s="51"/>
-      <c r="E492" s="51"/>
+      <c r="D492" s="50"/>
+      <c r="E492" s="50"/>
     </row>
     <row r="493" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D493" s="51"/>
-      <c r="E493" s="51"/>
+      <c r="D493" s="50"/>
+      <c r="E493" s="50"/>
     </row>
     <row r="494" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D494" s="51"/>
-      <c r="E494" s="51"/>
+      <c r="D494" s="50"/>
+      <c r="E494" s="50"/>
     </row>
     <row r="495" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D495" s="51"/>
-      <c r="E495" s="51"/>
+      <c r="D495" s="50"/>
+      <c r="E495" s="50"/>
     </row>
     <row r="496" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D496" s="51"/>
-      <c r="E496" s="51"/>
+      <c r="D496" s="50"/>
+      <c r="E496" s="50"/>
     </row>
     <row r="497" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D497" s="51"/>
-      <c r="E497" s="51"/>
+      <c r="D497" s="50"/>
+      <c r="E497" s="50"/>
     </row>
     <row r="498" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D498" s="51"/>
-      <c r="E498" s="51"/>
+      <c r="D498" s="50"/>
+      <c r="E498" s="50"/>
     </row>
     <row r="499" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D499" s="51"/>
-      <c r="E499" s="51"/>
+      <c r="D499" s="50"/>
+      <c r="E499" s="50"/>
     </row>
     <row r="500" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D500" s="51"/>
-      <c r="E500" s="51"/>
+      <c r="D500" s="50"/>
+      <c r="E500" s="50"/>
     </row>
     <row r="501" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D501" s="51"/>
-      <c r="E501" s="51"/>
+      <c r="D501" s="50"/>
+      <c r="E501" s="50"/>
     </row>
     <row r="502" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D502" s="51"/>
-      <c r="E502" s="51"/>
+      <c r="D502" s="50"/>
+      <c r="E502" s="50"/>
     </row>
     <row r="503" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D503" s="51"/>
-      <c r="E503" s="51"/>
+      <c r="D503" s="50"/>
+      <c r="E503" s="50"/>
     </row>
     <row r="504" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D504" s="51"/>
-      <c r="E504" s="51"/>
+      <c r="D504" s="50"/>
+      <c r="E504" s="50"/>
     </row>
     <row r="505" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D505" s="51"/>
-      <c r="E505" s="51"/>
+      <c r="D505" s="50"/>
+      <c r="E505" s="50"/>
     </row>
     <row r="506" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D506" s="51"/>
-      <c r="E506" s="51"/>
+      <c r="D506" s="50"/>
+      <c r="E506" s="50"/>
     </row>
     <row r="507" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D507" s="51"/>
-      <c r="E507" s="51"/>
+      <c r="D507" s="50"/>
+      <c r="E507" s="50"/>
     </row>
     <row r="508" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D508" s="51"/>
-      <c r="E508" s="51"/>
+      <c r="D508" s="50"/>
+      <c r="E508" s="50"/>
     </row>
     <row r="509" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D509" s="51"/>
-      <c r="E509" s="51"/>
+      <c r="D509" s="50"/>
+      <c r="E509" s="50"/>
     </row>
     <row r="510" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D510" s="51"/>
-      <c r="E510" s="51"/>
+      <c r="D510" s="50"/>
+      <c r="E510" s="50"/>
     </row>
     <row r="511" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D511" s="51"/>
-      <c r="E511" s="51"/>
+      <c r="D511" s="50"/>
+      <c r="E511" s="50"/>
     </row>
     <row r="512" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D512" s="51"/>
-      <c r="E512" s="51"/>
+      <c r="D512" s="50"/>
+      <c r="E512" s="50"/>
     </row>
     <row r="513" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D513" s="51"/>
-      <c r="E513" s="51"/>
+      <c r="D513" s="50"/>
+      <c r="E513" s="50"/>
     </row>
     <row r="514" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D514" s="51"/>
-      <c r="E514" s="51"/>
+      <c r="D514" s="50"/>
+      <c r="E514" s="50"/>
     </row>
     <row r="515" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D515" s="51"/>
-      <c r="E515" s="51"/>
+      <c r="D515" s="50"/>
+      <c r="E515" s="50"/>
     </row>
     <row r="516" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D516" s="51"/>
-      <c r="E516" s="51"/>
+      <c r="D516" s="50"/>
+      <c r="E516" s="50"/>
     </row>
     <row r="517" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D517" s="51"/>
-      <c r="E517" s="51"/>
+      <c r="D517" s="50"/>
+      <c r="E517" s="50"/>
     </row>
     <row r="518" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D518" s="51"/>
-      <c r="E518" s="51"/>
+      <c r="D518" s="50"/>
+      <c r="E518" s="50"/>
     </row>
     <row r="519" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D519" s="51"/>
-      <c r="E519" s="51"/>
+      <c r="D519" s="50"/>
+      <c r="E519" s="50"/>
     </row>
     <row r="520" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D520" s="51"/>
-      <c r="E520" s="51"/>
+      <c r="D520" s="50"/>
+      <c r="E520" s="50"/>
     </row>
     <row r="521" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D521" s="51"/>
-      <c r="E521" s="51"/>
+      <c r="D521" s="50"/>
+      <c r="E521" s="50"/>
     </row>
     <row r="522" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D522" s="51"/>
-      <c r="E522" s="51"/>
+      <c r="D522" s="50"/>
+      <c r="E522" s="50"/>
     </row>
     <row r="523" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D523" s="51"/>
-      <c r="E523" s="51"/>
+      <c r="D523" s="50"/>
+      <c r="E523" s="50"/>
     </row>
     <row r="524" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D524" s="51"/>
-      <c r="E524" s="51"/>
+      <c r="D524" s="50"/>
+      <c r="E524" s="50"/>
     </row>
     <row r="525" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D525" s="51"/>
-      <c r="E525" s="51"/>
+      <c r="D525" s="50"/>
+      <c r="E525" s="50"/>
     </row>
     <row r="526" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D526" s="51"/>
-      <c r="E526" s="51"/>
+      <c r="D526" s="50"/>
+      <c r="E526" s="50"/>
     </row>
     <row r="527" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D527" s="51"/>
-      <c r="E527" s="51"/>
+      <c r="D527" s="50"/>
+      <c r="E527" s="50"/>
     </row>
     <row r="528" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D528" s="51"/>
-      <c r="E528" s="51"/>
+      <c r="D528" s="50"/>
+      <c r="E528" s="50"/>
     </row>
     <row r="529" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D529" s="51"/>
-      <c r="E529" s="51"/>
+      <c r="D529" s="50"/>
+      <c r="E529" s="50"/>
     </row>
     <row r="530" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D530" s="51"/>
-      <c r="E530" s="51"/>
+      <c r="D530" s="50"/>
+      <c r="E530" s="50"/>
     </row>
     <row r="531" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D531" s="51"/>
-      <c r="E531" s="51"/>
+      <c r="D531" s="50"/>
+      <c r="E531" s="50"/>
     </row>
     <row r="532" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D532" s="51"/>
-      <c r="E532" s="51"/>
+      <c r="D532" s="50"/>
+      <c r="E532" s="50"/>
     </row>
     <row r="533" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D533" s="51"/>
-      <c r="E533" s="51"/>
+      <c r="D533" s="50"/>
+      <c r="E533" s="50"/>
     </row>
     <row r="534" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D534" s="51"/>
-      <c r="E534" s="51"/>
+      <c r="D534" s="50"/>
+      <c r="E534" s="50"/>
     </row>
     <row r="535" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D535" s="51"/>
-      <c r="E535" s="51"/>
+      <c r="D535" s="50"/>
+      <c r="E535" s="50"/>
     </row>
     <row r="536" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D536" s="51"/>
-      <c r="E536" s="51"/>
+      <c r="D536" s="50"/>
+      <c r="E536" s="50"/>
     </row>
     <row r="537" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D537" s="51"/>
-      <c r="E537" s="51"/>
+      <c r="D537" s="50"/>
+      <c r="E537" s="50"/>
     </row>
     <row r="538" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D538" s="51"/>
-      <c r="E538" s="51"/>
+      <c r="D538" s="50"/>
+      <c r="E538" s="50"/>
     </row>
     <row r="539" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D539" s="51"/>
-      <c r="E539" s="51"/>
+      <c r="D539" s="50"/>
+      <c r="E539" s="50"/>
     </row>
     <row r="540" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D540" s="51"/>
-      <c r="E540" s="51"/>
+      <c r="D540" s="50"/>
+      <c r="E540" s="50"/>
     </row>
     <row r="541" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D541" s="51"/>
-      <c r="E541" s="51"/>
+      <c r="D541" s="50"/>
+      <c r="E541" s="50"/>
     </row>
     <row r="542" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D542" s="51"/>
-      <c r="E542" s="51"/>
+      <c r="D542" s="50"/>
+      <c r="E542" s="50"/>
     </row>
     <row r="543" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D543" s="51"/>
-      <c r="E543" s="51"/>
+      <c r="D543" s="50"/>
+      <c r="E543" s="50"/>
     </row>
     <row r="544" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D544" s="51"/>
-      <c r="E544" s="51"/>
+      <c r="D544" s="50"/>
+      <c r="E544" s="50"/>
     </row>
     <row r="545" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D545" s="51"/>
-      <c r="E545" s="51"/>
+      <c r="D545" s="50"/>
+      <c r="E545" s="50"/>
     </row>
     <row r="546" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D546" s="51"/>
-      <c r="E546" s="51"/>
+      <c r="D546" s="50"/>
+      <c r="E546" s="50"/>
     </row>
     <row r="547" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D547" s="51"/>
-      <c r="E547" s="51"/>
+      <c r="D547" s="50"/>
+      <c r="E547" s="50"/>
     </row>
     <row r="548" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D548" s="51"/>
-      <c r="E548" s="51"/>
+      <c r="D548" s="50"/>
+      <c r="E548" s="50"/>
     </row>
     <row r="549" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D549" s="51"/>
-      <c r="E549" s="51"/>
+      <c r="D549" s="50"/>
+      <c r="E549" s="50"/>
     </row>
     <row r="550" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D550" s="51"/>
-      <c r="E550" s="51"/>
+      <c r="D550" s="50"/>
+      <c r="E550" s="50"/>
     </row>
     <row r="551" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D551" s="51"/>
-      <c r="E551" s="51"/>
+      <c r="D551" s="50"/>
+      <c r="E551" s="50"/>
     </row>
     <row r="552" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D552" s="51"/>
-      <c r="E552" s="51"/>
+      <c r="D552" s="50"/>
+      <c r="E552" s="50"/>
     </row>
     <row r="553" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D553" s="51"/>
-      <c r="E553" s="51"/>
+      <c r="D553" s="50"/>
+      <c r="E553" s="50"/>
     </row>
     <row r="554" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D554" s="51"/>
-      <c r="E554" s="51"/>
+      <c r="D554" s="50"/>
+      <c r="E554" s="50"/>
     </row>
     <row r="555" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D555" s="51"/>
-      <c r="E555" s="51"/>
+      <c r="D555" s="50"/>
+      <c r="E555" s="50"/>
     </row>
     <row r="556" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D556" s="51"/>
-      <c r="E556" s="51"/>
+      <c r="D556" s="50"/>
+      <c r="E556" s="50"/>
     </row>
     <row r="557" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D557" s="51"/>
-      <c r="E557" s="51"/>
+      <c r="D557" s="50"/>
+      <c r="E557" s="50"/>
     </row>
     <row r="558" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D558" s="51"/>
-      <c r="E558" s="51"/>
+      <c r="D558" s="50"/>
+      <c r="E558" s="50"/>
     </row>
     <row r="559" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D559" s="51"/>
-      <c r="E559" s="51"/>
+      <c r="D559" s="50"/>
+      <c r="E559" s="50"/>
     </row>
     <row r="560" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D560" s="51"/>
-      <c r="E560" s="51"/>
+      <c r="D560" s="50"/>
+      <c r="E560" s="50"/>
     </row>
     <row r="561" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D561" s="51"/>
-      <c r="E561" s="51"/>
+      <c r="D561" s="50"/>
+      <c r="E561" s="50"/>
     </row>
     <row r="562" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D562" s="51"/>
-      <c r="E562" s="51"/>
+      <c r="D562" s="50"/>
+      <c r="E562" s="50"/>
     </row>
     <row r="563" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D563" s="51"/>
-      <c r="E563" s="51"/>
+      <c r="D563" s="50"/>
+      <c r="E563" s="50"/>
     </row>
     <row r="564" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D564" s="51"/>
-      <c r="E564" s="51"/>
+      <c r="D564" s="50"/>
+      <c r="E564" s="50"/>
     </row>
     <row r="565" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D565" s="51"/>
-      <c r="E565" s="51"/>
+      <c r="D565" s="50"/>
+      <c r="E565" s="50"/>
     </row>
     <row r="566" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D566" s="51"/>
-      <c r="E566" s="51"/>
+      <c r="D566" s="50"/>
+      <c r="E566" s="50"/>
     </row>
     <row r="567" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D567" s="51"/>
-      <c r="E567" s="51"/>
+      <c r="D567" s="50"/>
+      <c r="E567" s="50"/>
     </row>
     <row r="568" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D568" s="51"/>
-      <c r="E568" s="51"/>
+      <c r="D568" s="50"/>
+      <c r="E568" s="50"/>
     </row>
     <row r="569" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D569" s="51"/>
-      <c r="E569" s="51"/>
+      <c r="D569" s="50"/>
+      <c r="E569" s="50"/>
     </row>
     <row r="570" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D570" s="51"/>
-      <c r="E570" s="51"/>
+      <c r="D570" s="50"/>
+      <c r="E570" s="50"/>
     </row>
     <row r="571" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D571" s="51"/>
-      <c r="E571" s="51"/>
+      <c r="D571" s="50"/>
+      <c r="E571" s="50"/>
     </row>
     <row r="572" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D572" s="51"/>
-      <c r="E572" s="51"/>
+      <c r="D572" s="50"/>
+      <c r="E572" s="50"/>
     </row>
     <row r="573" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D573" s="51"/>
-      <c r="E573" s="51"/>
+      <c r="D573" s="50"/>
+      <c r="E573" s="50"/>
     </row>
     <row r="574" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D574" s="51"/>
-      <c r="E574" s="51"/>
+      <c r="D574" s="50"/>
+      <c r="E574" s="50"/>
     </row>
     <row r="575" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D575" s="51"/>
-      <c r="E575" s="51"/>
+      <c r="D575" s="50"/>
+      <c r="E575" s="50"/>
     </row>
     <row r="576" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D576" s="51"/>
-      <c r="E576" s="51"/>
+      <c r="D576" s="50"/>
+      <c r="E576" s="50"/>
     </row>
     <row r="577" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D577" s="51"/>
-      <c r="E577" s="51"/>
+      <c r="D577" s="50"/>
+      <c r="E577" s="50"/>
     </row>
     <row r="578" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D578" s="51"/>
-      <c r="E578" s="51"/>
+      <c r="D578" s="50"/>
+      <c r="E578" s="50"/>
     </row>
     <row r="579" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D579" s="51"/>
-      <c r="E579" s="51"/>
+      <c r="D579" s="50"/>
+      <c r="E579" s="50"/>
     </row>
     <row r="580" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D580" s="51"/>
-      <c r="E580" s="51"/>
+      <c r="D580" s="50"/>
+      <c r="E580" s="50"/>
     </row>
     <row r="581" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D581" s="51"/>
-      <c r="E581" s="51"/>
+      <c r="D581" s="50"/>
+      <c r="E581" s="50"/>
     </row>
     <row r="582" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D582" s="51"/>
-      <c r="E582" s="51"/>
+      <c r="D582" s="50"/>
+      <c r="E582" s="50"/>
     </row>
     <row r="583" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D583" s="51"/>
-      <c r="E583" s="51"/>
+      <c r="D583" s="50"/>
+      <c r="E583" s="50"/>
     </row>
     <row r="584" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D584" s="51"/>
-      <c r="E584" s="51"/>
+      <c r="D584" s="50"/>
+      <c r="E584" s="50"/>
     </row>
     <row r="585" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D585" s="51"/>
-      <c r="E585" s="51"/>
+      <c r="D585" s="50"/>
+      <c r="E585" s="50"/>
     </row>
     <row r="586" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D586" s="51"/>
-      <c r="E586" s="51"/>
+      <c r="D586" s="50"/>
+      <c r="E586" s="50"/>
     </row>
     <row r="587" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D587" s="51"/>
-      <c r="E587" s="51"/>
+      <c r="D587" s="50"/>
+      <c r="E587" s="50"/>
     </row>
     <row r="588" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D588" s="51"/>
-      <c r="E588" s="51"/>
+      <c r="D588" s="50"/>
+      <c r="E588" s="50"/>
     </row>
     <row r="589" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D589" s="51"/>
-      <c r="E589" s="51"/>
+      <c r="D589" s="50"/>
+      <c r="E589" s="50"/>
     </row>
     <row r="590" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D590" s="51"/>
-      <c r="E590" s="51"/>
+      <c r="D590" s="50"/>
+      <c r="E590" s="50"/>
     </row>
     <row r="591" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D591" s="51"/>
-      <c r="E591" s="51"/>
+      <c r="D591" s="50"/>
+      <c r="E591" s="50"/>
     </row>
     <row r="592" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D592" s="51"/>
-      <c r="E592" s="51"/>
+      <c r="D592" s="50"/>
+      <c r="E592" s="50"/>
     </row>
     <row r="593" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D593" s="51"/>
-      <c r="E593" s="51"/>
+      <c r="D593" s="50"/>
+      <c r="E593" s="50"/>
     </row>
     <row r="594" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D594" s="51"/>
-      <c r="E594" s="51"/>
+      <c r="D594" s="50"/>
+      <c r="E594" s="50"/>
     </row>
     <row r="595" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D595" s="51"/>
-      <c r="E595" s="51"/>
+      <c r="D595" s="50"/>
+      <c r="E595" s="50"/>
     </row>
     <row r="596" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D596" s="51"/>
-      <c r="E596" s="51"/>
+      <c r="D596" s="50"/>
+      <c r="E596" s="50"/>
     </row>
     <row r="597" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D597" s="51"/>
-      <c r="E597" s="51"/>
+      <c r="D597" s="50"/>
+      <c r="E597" s="50"/>
     </row>
     <row r="598" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D598" s="51"/>
-      <c r="E598" s="51"/>
+      <c r="D598" s="50"/>
+      <c r="E598" s="50"/>
     </row>
     <row r="599" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D599" s="51"/>
-      <c r="E599" s="51"/>
+      <c r="D599" s="50"/>
+      <c r="E599" s="50"/>
     </row>
     <row r="600" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D600" s="51"/>
-      <c r="E600" s="51"/>
+      <c r="D600" s="50"/>
+      <c r="E600" s="50"/>
     </row>
     <row r="601" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D601" s="51"/>
-      <c r="E601" s="51"/>
+      <c r="D601" s="50"/>
+      <c r="E601" s="50"/>
     </row>
     <row r="602" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D602" s="51"/>
-      <c r="E602" s="51"/>
+      <c r="D602" s="50"/>
+      <c r="E602" s="50"/>
     </row>
     <row r="603" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D603" s="51"/>
-      <c r="E603" s="51"/>
+      <c r="D603" s="50"/>
+      <c r="E603" s="50"/>
     </row>
     <row r="604" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D604" s="51"/>
-      <c r="E604" s="51"/>
+      <c r="D604" s="50"/>
+      <c r="E604" s="50"/>
     </row>
     <row r="605" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D605" s="51"/>
-      <c r="E605" s="51"/>
+      <c r="D605" s="50"/>
+      <c r="E605" s="50"/>
     </row>
     <row r="606" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D606" s="51"/>
-      <c r="E606" s="51"/>
+      <c r="D606" s="50"/>
+      <c r="E606" s="50"/>
     </row>
     <row r="607" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D607" s="51"/>
-      <c r="E607" s="51"/>
+      <c r="D607" s="50"/>
+      <c r="E607" s="50"/>
     </row>
     <row r="608" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D608" s="51"/>
-      <c r="E608" s="51"/>
+      <c r="D608" s="50"/>
+      <c r="E608" s="50"/>
     </row>
     <row r="609" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D609" s="51"/>
-      <c r="E609" s="51"/>
+      <c r="D609" s="50"/>
+      <c r="E609" s="50"/>
     </row>
     <row r="610" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D610" s="51"/>
-      <c r="E610" s="51"/>
+      <c r="D610" s="50"/>
+      <c r="E610" s="50"/>
     </row>
     <row r="611" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D611" s="51"/>
-      <c r="E611" s="51"/>
+      <c r="D611" s="50"/>
+      <c r="E611" s="50"/>
     </row>
     <row r="612" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D612" s="51"/>
-      <c r="E612" s="51"/>
+      <c r="D612" s="50"/>
+      <c r="E612" s="50"/>
     </row>
     <row r="613" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D613" s="51"/>
-      <c r="E613" s="51"/>
+      <c r="D613" s="50"/>
+      <c r="E613" s="50"/>
     </row>
     <row r="614" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D614" s="51"/>
-      <c r="E614" s="51"/>
+      <c r="D614" s="50"/>
+      <c r="E614" s="50"/>
     </row>
     <row r="615" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D615" s="51"/>
-      <c r="E615" s="51"/>
+      <c r="D615" s="50"/>
+      <c r="E615" s="50"/>
     </row>
     <row r="616" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D616" s="51"/>
-      <c r="E616" s="51"/>
+      <c r="D616" s="50"/>
+      <c r="E616" s="50"/>
     </row>
     <row r="617" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D617" s="51"/>
-      <c r="E617" s="51"/>
+      <c r="D617" s="50"/>
+      <c r="E617" s="50"/>
     </row>
     <row r="618" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D618" s="51"/>
-      <c r="E618" s="51"/>
+      <c r="D618" s="50"/>
+      <c r="E618" s="50"/>
     </row>
     <row r="619" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D619" s="51"/>
-      <c r="E619" s="51"/>
+      <c r="D619" s="50"/>
+      <c r="E619" s="50"/>
     </row>
     <row r="620" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D620" s="51"/>
-      <c r="E620" s="51"/>
+      <c r="D620" s="50"/>
+      <c r="E620" s="50"/>
     </row>
     <row r="621" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D621" s="51"/>
-      <c r="E621" s="51"/>
+      <c r="D621" s="50"/>
+      <c r="E621" s="50"/>
     </row>
     <row r="622" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D622" s="51"/>
-      <c r="E622" s="51"/>
+      <c r="D622" s="50"/>
+      <c r="E622" s="50"/>
     </row>
     <row r="623" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D623" s="51"/>
-      <c r="E623" s="51"/>
+      <c r="D623" s="50"/>
+      <c r="E623" s="50"/>
     </row>
     <row r="624" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D624" s="51"/>
-      <c r="E624" s="51"/>
+      <c r="D624" s="50"/>
+      <c r="E624" s="50"/>
     </row>
     <row r="625" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D625" s="51"/>
-      <c r="E625" s="51"/>
+      <c r="D625" s="50"/>
+      <c r="E625" s="50"/>
     </row>
     <row r="626" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D626" s="51"/>
-      <c r="E626" s="51"/>
+      <c r="D626" s="50"/>
+      <c r="E626" s="50"/>
     </row>
     <row r="627" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D627" s="51"/>
-      <c r="E627" s="51"/>
+      <c r="D627" s="50"/>
+      <c r="E627" s="50"/>
     </row>
     <row r="628" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D628" s="51"/>
-      <c r="E628" s="51"/>
+      <c r="D628" s="50"/>
+      <c r="E628" s="50"/>
     </row>
     <row r="629" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D629" s="51"/>
-      <c r="E629" s="51"/>
+      <c r="D629" s="50"/>
+      <c r="E629" s="50"/>
     </row>
     <row r="630" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D630" s="51"/>
-      <c r="E630" s="51"/>
+      <c r="D630" s="50"/>
+      <c r="E630" s="50"/>
     </row>
     <row r="631" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D631" s="51"/>
-      <c r="E631" s="51"/>
+      <c r="D631" s="50"/>
+      <c r="E631" s="50"/>
     </row>
     <row r="632" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D632" s="51"/>
-      <c r="E632" s="51"/>
+      <c r="D632" s="50"/>
+      <c r="E632" s="50"/>
     </row>
     <row r="633" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D633" s="51"/>
-      <c r="E633" s="51"/>
+      <c r="D633" s="50"/>
+      <c r="E633" s="50"/>
     </row>
     <row r="634" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D634" s="51"/>
-      <c r="E634" s="51"/>
+      <c r="D634" s="50"/>
+      <c r="E634" s="50"/>
     </row>
     <row r="635" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D635" s="51"/>
-      <c r="E635" s="51"/>
+      <c r="D635" s="50"/>
+      <c r="E635" s="50"/>
     </row>
     <row r="636" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D636" s="51"/>
-      <c r="E636" s="51"/>
+      <c r="D636" s="50"/>
+      <c r="E636" s="50"/>
     </row>
     <row r="637" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D637" s="51"/>
-      <c r="E637" s="51"/>
+      <c r="D637" s="50"/>
+      <c r="E637" s="50"/>
     </row>
     <row r="638" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D638" s="51"/>
-      <c r="E638" s="51"/>
+      <c r="D638" s="50"/>
+      <c r="E638" s="50"/>
     </row>
     <row r="639" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D639" s="51"/>
-      <c r="E639" s="51"/>
+      <c r="D639" s="50"/>
+      <c r="E639" s="50"/>
     </row>
     <row r="640" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D640" s="51"/>
-      <c r="E640" s="51"/>
+      <c r="D640" s="50"/>
+      <c r="E640" s="50"/>
     </row>
     <row r="641" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D641" s="51"/>
-      <c r="E641" s="51"/>
+      <c r="D641" s="50"/>
+      <c r="E641" s="50"/>
     </row>
     <row r="642" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D642" s="51"/>
-      <c r="E642" s="51"/>
+      <c r="D642" s="50"/>
+      <c r="E642" s="50"/>
     </row>
     <row r="643" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D643" s="51"/>
-      <c r="E643" s="51"/>
+      <c r="D643" s="50"/>
+      <c r="E643" s="50"/>
     </row>
     <row r="644" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D644" s="51"/>
-      <c r="E644" s="51"/>
+      <c r="D644" s="50"/>
+      <c r="E644" s="50"/>
     </row>
     <row r="645" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D645" s="51"/>
-      <c r="E645" s="51"/>
+      <c r="D645" s="50"/>
+      <c r="E645" s="50"/>
     </row>
     <row r="646" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D646" s="51"/>
-      <c r="E646" s="51"/>
+      <c r="D646" s="50"/>
+      <c r="E646" s="50"/>
     </row>
     <row r="647" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D647" s="51"/>
-      <c r="E647" s="51"/>
+      <c r="D647" s="50"/>
+      <c r="E647" s="50"/>
     </row>
     <row r="648" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D648" s="51"/>
-      <c r="E648" s="51"/>
+      <c r="D648" s="50"/>
+      <c r="E648" s="50"/>
     </row>
     <row r="649" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D649" s="51"/>
-      <c r="E649" s="51"/>
+      <c r="D649" s="50"/>
+      <c r="E649" s="50"/>
     </row>
     <row r="650" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D650" s="51"/>
-      <c r="E650" s="51"/>
+      <c r="D650" s="50"/>
+      <c r="E650" s="50"/>
     </row>
     <row r="651" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D651" s="51"/>
-      <c r="E651" s="51"/>
+      <c r="D651" s="50"/>
+      <c r="E651" s="50"/>
     </row>
     <row r="652" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D652" s="51"/>
-      <c r="E652" s="51"/>
+      <c r="D652" s="50"/>
+      <c r="E652" s="50"/>
     </row>
     <row r="653" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D653" s="51"/>
-      <c r="E653" s="51"/>
+      <c r="D653" s="50"/>
+      <c r="E653" s="50"/>
     </row>
     <row r="654" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D654" s="51"/>
-      <c r="E654" s="51"/>
+      <c r="D654" s="50"/>
+      <c r="E654" s="50"/>
     </row>
     <row r="655" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D655" s="51"/>
-      <c r="E655" s="51"/>
+      <c r="D655" s="50"/>
+      <c r="E655" s="50"/>
     </row>
     <row r="656" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D656" s="51"/>
-      <c r="E656" s="51"/>
+      <c r="D656" s="50"/>
+      <c r="E656" s="50"/>
     </row>
     <row r="657" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D657" s="51"/>
-      <c r="E657" s="51"/>
+      <c r="D657" s="50"/>
+      <c r="E657" s="50"/>
     </row>
     <row r="658" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D658" s="51"/>
-      <c r="E658" s="51"/>
+      <c r="D658" s="50"/>
+      <c r="E658" s="50"/>
     </row>
     <row r="659" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D659" s="51"/>
-      <c r="E659" s="51"/>
+      <c r="D659" s="50"/>
+      <c r="E659" s="50"/>
     </row>
     <row r="660" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D660" s="51"/>
-      <c r="E660" s="51"/>
+      <c r="D660" s="50"/>
+      <c r="E660" s="50"/>
     </row>
     <row r="661" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D661" s="51"/>
-      <c r="E661" s="51"/>
+      <c r="D661" s="50"/>
+      <c r="E661" s="50"/>
     </row>
     <row r="662" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D662" s="51"/>
-      <c r="E662" s="51"/>
+      <c r="D662" s="50"/>
+      <c r="E662" s="50"/>
     </row>
     <row r="663" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D663" s="51"/>
-      <c r="E663" s="51"/>
+      <c r="D663" s="50"/>
+      <c r="E663" s="50"/>
     </row>
     <row r="664" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D664" s="51"/>
-      <c r="E664" s="51"/>
+      <c r="D664" s="50"/>
+      <c r="E664" s="50"/>
     </row>
     <row r="665" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D665" s="51"/>
-      <c r="E665" s="51"/>
+      <c r="D665" s="50"/>
+      <c r="E665" s="50"/>
     </row>
     <row r="666" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D666" s="51"/>
-      <c r="E666" s="51"/>
+      <c r="D666" s="50"/>
+      <c r="E666" s="50"/>
     </row>
     <row r="667" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D667" s="51"/>
-      <c r="E667" s="51"/>
+      <c r="D667" s="50"/>
+      <c r="E667" s="50"/>
     </row>
     <row r="668" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D668" s="51"/>
-      <c r="E668" s="51"/>
+      <c r="D668" s="50"/>
+      <c r="E668" s="50"/>
     </row>
     <row r="669" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D669" s="51"/>
-      <c r="E669" s="51"/>
+      <c r="D669" s="50"/>
+      <c r="E669" s="50"/>
     </row>
     <row r="670" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D670" s="51"/>
-      <c r="E670" s="51"/>
+      <c r="D670" s="50"/>
+      <c r="E670" s="50"/>
     </row>
     <row r="671" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D671" s="51"/>
-      <c r="E671" s="51"/>
+      <c r="D671" s="50"/>
+      <c r="E671" s="50"/>
     </row>
     <row r="672" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D672" s="51"/>
-      <c r="E672" s="51"/>
+      <c r="D672" s="50"/>
+      <c r="E672" s="50"/>
     </row>
     <row r="673" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D673" s="51"/>
-      <c r="E673" s="51"/>
+      <c r="D673" s="50"/>
+      <c r="E673" s="50"/>
     </row>
     <row r="674" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D674" s="51"/>
-      <c r="E674" s="51"/>
+      <c r="D674" s="50"/>
+      <c r="E674" s="50"/>
     </row>
     <row r="675" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D675" s="51"/>
-      <c r="E675" s="51"/>
+      <c r="D675" s="50"/>
+      <c r="E675" s="50"/>
     </row>
     <row r="676" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D676" s="51"/>
-      <c r="E676" s="51"/>
+      <c r="D676" s="50"/>
+      <c r="E676" s="50"/>
     </row>
     <row r="677" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D677" s="51"/>
-      <c r="E677" s="51"/>
+      <c r="D677" s="50"/>
+      <c r="E677" s="50"/>
     </row>
     <row r="678" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D678" s="51"/>
-      <c r="E678" s="51"/>
+      <c r="D678" s="50"/>
+      <c r="E678" s="50"/>
     </row>
     <row r="679" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D679" s="51"/>
-      <c r="E679" s="51"/>
+      <c r="D679" s="50"/>
+      <c r="E679" s="50"/>
     </row>
     <row r="680" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D680" s="51"/>
-      <c r="E680" s="51"/>
+      <c r="D680" s="50"/>
+      <c r="E680" s="50"/>
     </row>
     <row r="681" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D681" s="51"/>
-      <c r="E681" s="51"/>
+      <c r="D681" s="50"/>
+      <c r="E681" s="50"/>
     </row>
     <row r="682" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D682" s="51"/>
-      <c r="E682" s="51"/>
+      <c r="D682" s="50"/>
+      <c r="E682" s="50"/>
     </row>
     <row r="683" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D683" s="51"/>
-      <c r="E683" s="51"/>
+      <c r="D683" s="50"/>
+      <c r="E683" s="50"/>
     </row>
     <row r="684" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D684" s="51"/>
-      <c r="E684" s="51"/>
+      <c r="D684" s="50"/>
+      <c r="E684" s="50"/>
     </row>
     <row r="685" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D685" s="51"/>
-      <c r="E685" s="51"/>
+      <c r="D685" s="50"/>
+      <c r="E685" s="50"/>
     </row>
     <row r="686" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D686" s="51"/>
-      <c r="E686" s="51"/>
+      <c r="D686" s="50"/>
+      <c r="E686" s="50"/>
     </row>
     <row r="687" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D687" s="51"/>
-      <c r="E687" s="51"/>
+      <c r="D687" s="50"/>
+      <c r="E687" s="50"/>
     </row>
     <row r="688" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D688" s="51"/>
-      <c r="E688" s="51"/>
+      <c r="D688" s="50"/>
+      <c r="E688" s="50"/>
     </row>
     <row r="689" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D689" s="51"/>
-      <c r="E689" s="51"/>
+      <c r="D689" s="50"/>
+      <c r="E689" s="50"/>
     </row>
     <row r="690" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D690" s="51"/>
-      <c r="E690" s="51"/>
+      <c r="D690" s="50"/>
+      <c r="E690" s="50"/>
     </row>
     <row r="691" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D691" s="51"/>
-      <c r="E691" s="51"/>
+      <c r="D691" s="50"/>
+      <c r="E691" s="50"/>
     </row>
     <row r="692" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D692" s="51"/>
-      <c r="E692" s="51"/>
+      <c r="D692" s="50"/>
+      <c r="E692" s="50"/>
     </row>
     <row r="693" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D693" s="51"/>
-      <c r="E693" s="51"/>
+      <c r="D693" s="50"/>
+      <c r="E693" s="50"/>
     </row>
     <row r="694" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D694" s="51"/>
-      <c r="E694" s="51"/>
+      <c r="D694" s="50"/>
+      <c r="E694" s="50"/>
     </row>
     <row r="695" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D695" s="51"/>
-      <c r="E695" s="51"/>
+      <c r="D695" s="50"/>
+      <c r="E695" s="50"/>
     </row>
     <row r="696" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D696" s="51"/>
-      <c r="E696" s="51"/>
+      <c r="D696" s="50"/>
+      <c r="E696" s="50"/>
     </row>
     <row r="697" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D697" s="51"/>
-      <c r="E697" s="51"/>
+      <c r="D697" s="50"/>
+      <c r="E697" s="50"/>
     </row>
     <row r="698" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D698" s="51"/>
-      <c r="E698" s="51"/>
+      <c r="D698" s="50"/>
+      <c r="E698" s="50"/>
     </row>
     <row r="699" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D699" s="51"/>
-      <c r="E699" s="51"/>
+      <c r="D699" s="50"/>
+      <c r="E699" s="50"/>
     </row>
     <row r="700" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D700" s="51"/>
-      <c r="E700" s="51"/>
+      <c r="D700" s="50"/>
+      <c r="E700" s="50"/>
     </row>
     <row r="701" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D701" s="51"/>
-      <c r="E701" s="51"/>
+      <c r="D701" s="50"/>
+      <c r="E701" s="50"/>
     </row>
     <row r="702" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D702" s="51"/>
-      <c r="E702" s="51"/>
+      <c r="D702" s="50"/>
+      <c r="E702" s="50"/>
     </row>
     <row r="703" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D703" s="51"/>
-      <c r="E703" s="51"/>
+      <c r="D703" s="50"/>
+      <c r="E703" s="50"/>
     </row>
     <row r="704" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D704" s="51"/>
-      <c r="E704" s="51"/>
+      <c r="D704" s="50"/>
+      <c r="E704" s="50"/>
     </row>
     <row r="705" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D705" s="51"/>
-      <c r="E705" s="51"/>
+      <c r="D705" s="50"/>
+      <c r="E705" s="50"/>
     </row>
     <row r="706" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D706" s="51"/>
-      <c r="E706" s="51"/>
+      <c r="D706" s="50"/>
+      <c r="E706" s="50"/>
     </row>
     <row r="707" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D707" s="51"/>
-      <c r="E707" s="51"/>
+      <c r="D707" s="50"/>
+      <c r="E707" s="50"/>
     </row>
     <row r="708" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D708" s="51"/>
-      <c r="E708" s="51"/>
+      <c r="D708" s="50"/>
+      <c r="E708" s="50"/>
     </row>
     <row r="709" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D709" s="51"/>
-      <c r="E709" s="51"/>
+      <c r="D709" s="50"/>
+      <c r="E709" s="50"/>
     </row>
     <row r="710" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D710" s="51"/>
-      <c r="E710" s="51"/>
+      <c r="D710" s="50"/>
+      <c r="E710" s="50"/>
     </row>
     <row r="711" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D711" s="51"/>
-      <c r="E711" s="51"/>
+      <c r="D711" s="50"/>
+      <c r="E711" s="50"/>
     </row>
     <row r="712" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D712" s="51"/>
-      <c r="E712" s="51"/>
+      <c r="D712" s="50"/>
+      <c r="E712" s="50"/>
     </row>
     <row r="713" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D713" s="51"/>
-      <c r="E713" s="51"/>
+      <c r="D713" s="50"/>
+      <c r="E713" s="50"/>
     </row>
     <row r="714" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D714" s="51"/>
-      <c r="E714" s="51"/>
+      <c r="D714" s="50"/>
+      <c r="E714" s="50"/>
     </row>
     <row r="715" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D715" s="51"/>
-      <c r="E715" s="51"/>
+      <c r="D715" s="50"/>
+      <c r="E715" s="50"/>
     </row>
     <row r="716" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D716" s="51"/>
-      <c r="E716" s="51"/>
+      <c r="D716" s="50"/>
+      <c r="E716" s="50"/>
     </row>
     <row r="717" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D717" s="51"/>
-      <c r="E717" s="51"/>
+      <c r="D717" s="50"/>
+      <c r="E717" s="50"/>
     </row>
     <row r="718" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D718" s="51"/>
-      <c r="E718" s="51"/>
+      <c r="D718" s="50"/>
+      <c r="E718" s="50"/>
     </row>
     <row r="719" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D719" s="51"/>
-      <c r="E719" s="51"/>
+      <c r="D719" s="50"/>
+      <c r="E719" s="50"/>
     </row>
     <row r="720" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D720" s="51"/>
-      <c r="E720" s="51"/>
+      <c r="D720" s="50"/>
+      <c r="E720" s="50"/>
     </row>
     <row r="721" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D721" s="51"/>
-      <c r="E721" s="51"/>
+      <c r="D721" s="50"/>
+      <c r="E721" s="50"/>
     </row>
     <row r="722" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D722" s="51"/>
-      <c r="E722" s="51"/>
+      <c r="D722" s="50"/>
+      <c r="E722" s="50"/>
     </row>
     <row r="723" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D723" s="51"/>
-      <c r="E723" s="51"/>
+      <c r="D723" s="50"/>
+      <c r="E723" s="50"/>
     </row>
     <row r="724" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D724" s="51"/>
-      <c r="E724" s="51"/>
+      <c r="D724" s="50"/>
+      <c r="E724" s="50"/>
     </row>
     <row r="725" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D725" s="51"/>
-      <c r="E725" s="51"/>
+      <c r="D725" s="50"/>
+      <c r="E725" s="50"/>
     </row>
     <row r="726" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D726" s="51"/>
-      <c r="E726" s="51"/>
+      <c r="D726" s="50"/>
+      <c r="E726" s="50"/>
     </row>
     <row r="727" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D727" s="51"/>
-      <c r="E727" s="51"/>
+      <c r="D727" s="50"/>
+      <c r="E727" s="50"/>
     </row>
     <row r="728" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D728" s="51"/>
-      <c r="E728" s="51"/>
+      <c r="D728" s="50"/>
+      <c r="E728" s="50"/>
     </row>
     <row r="729" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D729" s="51"/>
-      <c r="E729" s="51"/>
+      <c r="D729" s="50"/>
+      <c r="E729" s="50"/>
     </row>
     <row r="730" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D730" s="51"/>
-      <c r="E730" s="51"/>
+      <c r="D730" s="50"/>
+      <c r="E730" s="50"/>
     </row>
     <row r="731" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D731" s="51"/>
-      <c r="E731" s="51"/>
+      <c r="D731" s="50"/>
+      <c r="E731" s="50"/>
     </row>
     <row r="732" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D732" s="51"/>
-      <c r="E732" s="51"/>
+      <c r="D732" s="50"/>
+      <c r="E732" s="50"/>
     </row>
     <row r="733" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D733" s="51"/>
-      <c r="E733" s="51"/>
+      <c r="D733" s="50"/>
+      <c r="E733" s="50"/>
     </row>
     <row r="734" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D734" s="51"/>
-      <c r="E734" s="51"/>
+      <c r="D734" s="50"/>
+      <c r="E734" s="50"/>
     </row>
     <row r="735" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D735" s="51"/>
-      <c r="E735" s="51"/>
+      <c r="D735" s="50"/>
+      <c r="E735" s="50"/>
     </row>
     <row r="736" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D736" s="51"/>
-      <c r="E736" s="51"/>
+      <c r="D736" s="50"/>
+      <c r="E736" s="50"/>
     </row>
     <row r="737" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D737" s="51"/>
-      <c r="E737" s="51"/>
+      <c r="D737" s="50"/>
+      <c r="E737" s="50"/>
     </row>
     <row r="738" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D738" s="51"/>
-      <c r="E738" s="51"/>
+      <c r="D738" s="50"/>
+      <c r="E738" s="50"/>
     </row>
     <row r="739" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D739" s="51"/>
-      <c r="E739" s="51"/>
+      <c r="D739" s="50"/>
+      <c r="E739" s="50"/>
     </row>
     <row r="740" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D740" s="51"/>
-      <c r="E740" s="51"/>
+      <c r="D740" s="50"/>
+      <c r="E740" s="50"/>
     </row>
     <row r="741" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D741" s="51"/>
-      <c r="E741" s="51"/>
+      <c r="D741" s="50"/>
+      <c r="E741" s="50"/>
     </row>
     <row r="742" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D742" s="51"/>
-      <c r="E742" s="51"/>
+      <c r="D742" s="50"/>
+      <c r="E742" s="50"/>
     </row>
     <row r="743" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D743" s="51"/>
-      <c r="E743" s="51"/>
+      <c r="D743" s="50"/>
+      <c r="E743" s="50"/>
     </row>
     <row r="744" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D744" s="51"/>
-      <c r="E744" s="51"/>
+      <c r="D744" s="50"/>
+      <c r="E744" s="50"/>
     </row>
     <row r="745" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D745" s="51"/>
-      <c r="E745" s="51"/>
+      <c r="D745" s="50"/>
+      <c r="E745" s="50"/>
     </row>
     <row r="746" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D746" s="51"/>
-      <c r="E746" s="51"/>
+      <c r="D746" s="50"/>
+      <c r="E746" s="50"/>
     </row>
     <row r="747" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D747" s="51"/>
-      <c r="E747" s="51"/>
+      <c r="D747" s="50"/>
+      <c r="E747" s="50"/>
     </row>
     <row r="748" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D748" s="51"/>
-      <c r="E748" s="51"/>
+      <c r="D748" s="50"/>
+      <c r="E748" s="50"/>
     </row>
     <row r="749" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D749" s="51"/>
-      <c r="E749" s="51"/>
+      <c r="D749" s="50"/>
+      <c r="E749" s="50"/>
     </row>
     <row r="750" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D750" s="51"/>
-      <c r="E750" s="51"/>
+      <c r="D750" s="50"/>
+      <c r="E750" s="50"/>
     </row>
     <row r="751" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D751" s="51"/>
-      <c r="E751" s="51"/>
+      <c r="D751" s="50"/>
+      <c r="E751" s="50"/>
     </row>
     <row r="752" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D752" s="51"/>
-      <c r="E752" s="51"/>
+      <c r="D752" s="50"/>
+      <c r="E752" s="50"/>
     </row>
     <row r="753" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D753" s="51"/>
-      <c r="E753" s="51"/>
+      <c r="D753" s="50"/>
+      <c r="E753" s="50"/>
     </row>
     <row r="754" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D754" s="51"/>
-      <c r="E754" s="51"/>
+      <c r="D754" s="50"/>
+      <c r="E754" s="50"/>
     </row>
     <row r="755" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D755" s="51"/>
-      <c r="E755" s="51"/>
+      <c r="D755" s="50"/>
+      <c r="E755" s="50"/>
     </row>
     <row r="756" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D756" s="51"/>
-      <c r="E756" s="51"/>
+      <c r="D756" s="50"/>
+      <c r="E756" s="50"/>
     </row>
     <row r="757" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D757" s="51"/>
-      <c r="E757" s="51"/>
+      <c r="D757" s="50"/>
+      <c r="E757" s="50"/>
     </row>
     <row r="758" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D758" s="51"/>
-      <c r="E758" s="51"/>
+      <c r="D758" s="50"/>
+      <c r="E758" s="50"/>
     </row>
     <row r="759" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D759" s="51"/>
-      <c r="E759" s="51"/>
+      <c r="D759" s="50"/>
+      <c r="E759" s="50"/>
     </row>
     <row r="760" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D760" s="51"/>
-      <c r="E760" s="51"/>
+      <c r="D760" s="50"/>
+      <c r="E760" s="50"/>
     </row>
     <row r="761" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D761" s="51"/>
-      <c r="E761" s="51"/>
+      <c r="D761" s="50"/>
+      <c r="E761" s="50"/>
     </row>
     <row r="762" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D762" s="51"/>
-      <c r="E762" s="51"/>
+      <c r="D762" s="50"/>
+      <c r="E762" s="50"/>
     </row>
     <row r="763" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D763" s="51"/>
-      <c r="E763" s="51"/>
+      <c r="D763" s="50"/>
+      <c r="E763" s="50"/>
     </row>
     <row r="764" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D764" s="51"/>
-      <c r="E764" s="51"/>
+      <c r="D764" s="50"/>
+      <c r="E764" s="50"/>
     </row>
     <row r="765" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D765" s="51"/>
-      <c r="E765" s="51"/>
+      <c r="D765" s="50"/>
+      <c r="E765" s="50"/>
     </row>
     <row r="766" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D766" s="51"/>
-      <c r="E766" s="51"/>
+      <c r="D766" s="50"/>
+      <c r="E766" s="50"/>
     </row>
     <row r="767" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D767" s="51"/>
-      <c r="E767" s="51"/>
+      <c r="D767" s="50"/>
+      <c r="E767" s="50"/>
     </row>
     <row r="768" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D768" s="51"/>
-      <c r="E768" s="51"/>
+      <c r="D768" s="50"/>
+      <c r="E768" s="50"/>
     </row>
     <row r="769" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D769" s="51"/>
-      <c r="E769" s="51"/>
+      <c r="D769" s="50"/>
+      <c r="E769" s="50"/>
     </row>
     <row r="770" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D770" s="51"/>
-      <c r="E770" s="51"/>
+      <c r="D770" s="50"/>
+      <c r="E770" s="50"/>
     </row>
     <row r="771" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D771" s="51"/>
-      <c r="E771" s="51"/>
+      <c r="D771" s="50"/>
+      <c r="E771" s="50"/>
     </row>
     <row r="772" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D772" s="51"/>
-      <c r="E772" s="51"/>
+      <c r="D772" s="50"/>
+      <c r="E772" s="50"/>
     </row>
     <row r="773" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D773" s="51"/>
-      <c r="E773" s="51"/>
+      <c r="D773" s="50"/>
+      <c r="E773" s="50"/>
     </row>
     <row r="774" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D774" s="51"/>
-      <c r="E774" s="51"/>
+      <c r="D774" s="50"/>
+      <c r="E774" s="50"/>
     </row>
     <row r="775" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D775" s="51"/>
-      <c r="E775" s="51"/>
+      <c r="D775" s="50"/>
+      <c r="E775" s="50"/>
     </row>
     <row r="776" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D776" s="51"/>
-      <c r="E776" s="51"/>
+      <c r="D776" s="50"/>
+      <c r="E776" s="50"/>
     </row>
     <row r="777" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D777" s="51"/>
-      <c r="E777" s="51"/>
+      <c r="D777" s="50"/>
+      <c r="E777" s="50"/>
     </row>
     <row r="778" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D778" s="51"/>
-      <c r="E778" s="51"/>
+      <c r="D778" s="50"/>
+      <c r="E778" s="50"/>
     </row>
     <row r="779" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D779" s="51"/>
-      <c r="E779" s="51"/>
+      <c r="D779" s="50"/>
+      <c r="E779" s="50"/>
     </row>
     <row r="780" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D780" s="51"/>
-      <c r="E780" s="51"/>
+      <c r="D780" s="50"/>
+      <c r="E780" s="50"/>
     </row>
     <row r="781" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D781" s="51"/>
-      <c r="E781" s="51"/>
+      <c r="D781" s="50"/>
+      <c r="E781" s="50"/>
     </row>
     <row r="782" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D782" s="51"/>
-      <c r="E782" s="51"/>
+      <c r="D782" s="50"/>
+      <c r="E782" s="50"/>
     </row>
     <row r="783" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D783" s="51"/>
-      <c r="E783" s="51"/>
+      <c r="D783" s="50"/>
+      <c r="E783" s="50"/>
     </row>
     <row r="784" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D784" s="51"/>
-      <c r="E784" s="51"/>
+      <c r="D784" s="50"/>
+      <c r="E784" s="50"/>
     </row>
     <row r="785" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D785" s="51"/>
-      <c r="E785" s="51"/>
+      <c r="D785" s="50"/>
+      <c r="E785" s="50"/>
     </row>
     <row r="786" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D786" s="51"/>
-      <c r="E786" s="51"/>
+      <c r="D786" s="50"/>
+      <c r="E786" s="50"/>
     </row>
     <row r="787" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D787" s="51"/>
-      <c r="E787" s="51"/>
+      <c r="D787" s="50"/>
+      <c r="E787" s="50"/>
     </row>
     <row r="788" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D788" s="51"/>
-      <c r="E788" s="51"/>
+      <c r="D788" s="50"/>
+      <c r="E788" s="50"/>
     </row>
     <row r="789" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D789" s="51"/>
-      <c r="E789" s="51"/>
+      <c r="D789" s="50"/>
+      <c r="E789" s="50"/>
     </row>
     <row r="790" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D790" s="51"/>
-      <c r="E790" s="51"/>
+      <c r="D790" s="50"/>
+      <c r="E790" s="50"/>
     </row>
     <row r="791" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D791" s="51"/>
-      <c r="E791" s="51"/>
+      <c r="D791" s="50"/>
+      <c r="E791" s="50"/>
     </row>
     <row r="792" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D792" s="51"/>
-      <c r="E792" s="51"/>
+      <c r="D792" s="50"/>
+      <c r="E792" s="50"/>
     </row>
     <row r="793" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D793" s="51"/>
-      <c r="E793" s="51"/>
+      <c r="D793" s="50"/>
+      <c r="E793" s="50"/>
     </row>
     <row r="794" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D794" s="51"/>
-      <c r="E794" s="51"/>
+      <c r="D794" s="50"/>
+      <c r="E794" s="50"/>
     </row>
     <row r="795" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D795" s="51"/>
-      <c r="E795" s="51"/>
+      <c r="D795" s="50"/>
+      <c r="E795" s="50"/>
     </row>
     <row r="796" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D796" s="51"/>
-      <c r="E796" s="51"/>
+      <c r="D796" s="50"/>
+      <c r="E796" s="50"/>
     </row>
     <row r="797" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D797" s="51"/>
-      <c r="E797" s="51"/>
+      <c r="D797" s="50"/>
+      <c r="E797" s="50"/>
     </row>
     <row r="798" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D798" s="51"/>
-      <c r="E798" s="51"/>
+      <c r="D798" s="50"/>
+      <c r="E798" s="50"/>
     </row>
     <row r="799" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D799" s="51"/>
-      <c r="E799" s="51"/>
+      <c r="D799" s="50"/>
+      <c r="E799" s="50"/>
     </row>
     <row r="800" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D800" s="51"/>
-      <c r="E800" s="51"/>
+      <c r="D800" s="50"/>
+      <c r="E800" s="50"/>
     </row>
     <row r="801" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D801" s="51"/>
-      <c r="E801" s="51"/>
+      <c r="D801" s="50"/>
+      <c r="E801" s="50"/>
     </row>
     <row r="802" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D802" s="51"/>
-      <c r="E802" s="51"/>
+      <c r="D802" s="50"/>
+      <c r="E802" s="50"/>
     </row>
     <row r="803" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D803" s="51"/>
-      <c r="E803" s="51"/>
+      <c r="D803" s="50"/>
+      <c r="E803" s="50"/>
     </row>
     <row r="804" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D804" s="51"/>
-      <c r="E804" s="51"/>
+      <c r="D804" s="50"/>
+      <c r="E804" s="50"/>
     </row>
     <row r="805" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D805" s="51"/>
-      <c r="E805" s="51"/>
+      <c r="D805" s="50"/>
+      <c r="E805" s="50"/>
     </row>
     <row r="806" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D806" s="51"/>
-      <c r="E806" s="51"/>
+      <c r="D806" s="50"/>
+      <c r="E806" s="50"/>
     </row>
     <row r="807" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D807" s="51"/>
-      <c r="E807" s="51"/>
+      <c r="D807" s="50"/>
+      <c r="E807" s="50"/>
     </row>
     <row r="808" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D808" s="51"/>
-      <c r="E808" s="51"/>
+      <c r="D808" s="50"/>
+      <c r="E808" s="50"/>
     </row>
     <row r="809" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D809" s="51"/>
-      <c r="E809" s="51"/>
+      <c r="D809" s="50"/>
+      <c r="E809" s="50"/>
     </row>
     <row r="810" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D810" s="51"/>
-      <c r="E810" s="51"/>
+      <c r="D810" s="50"/>
+      <c r="E810" s="50"/>
     </row>
     <row r="811" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D811" s="51"/>
-      <c r="E811" s="51"/>
+      <c r="D811" s="50"/>
+      <c r="E811" s="50"/>
     </row>
     <row r="812" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D812" s="51"/>
-      <c r="E812" s="51"/>
+      <c r="D812" s="50"/>
+      <c r="E812" s="50"/>
     </row>
     <row r="813" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D813" s="51"/>
-      <c r="E813" s="51"/>
+      <c r="D813" s="50"/>
+      <c r="E813" s="50"/>
     </row>
     <row r="814" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D814" s="51"/>
-      <c r="E814" s="51"/>
+      <c r="D814" s="50"/>
+      <c r="E814" s="50"/>
     </row>
     <row r="815" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D815" s="51"/>
-      <c r="E815" s="51"/>
+      <c r="D815" s="50"/>
+      <c r="E815" s="50"/>
     </row>
     <row r="816" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D816" s="51"/>
-      <c r="E816" s="51"/>
+      <c r="D816" s="50"/>
+      <c r="E816" s="50"/>
     </row>
     <row r="817" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D817" s="51"/>
-      <c r="E817" s="51"/>
+      <c r="D817" s="50"/>
+      <c r="E817" s="50"/>
     </row>
     <row r="818" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D818" s="51"/>
-      <c r="E818" s="51"/>
+      <c r="D818" s="50"/>
+      <c r="E818" s="50"/>
     </row>
     <row r="819" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D819" s="51"/>
-      <c r="E819" s="51"/>
+      <c r="D819" s="50"/>
+      <c r="E819" s="50"/>
     </row>
     <row r="820" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D820" s="51"/>
-      <c r="E820" s="51"/>
+      <c r="D820" s="50"/>
+      <c r="E820" s="50"/>
     </row>
     <row r="821" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D821" s="51"/>
-      <c r="E821" s="51"/>
+      <c r="D821" s="50"/>
+      <c r="E821" s="50"/>
     </row>
     <row r="822" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D822" s="51"/>
-      <c r="E822" s="51"/>
+      <c r="D822" s="50"/>
+      <c r="E822" s="50"/>
     </row>
     <row r="823" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D823" s="51"/>
-      <c r="E823" s="51"/>
+      <c r="D823" s="50"/>
+      <c r="E823" s="50"/>
     </row>
     <row r="824" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D824" s="51"/>
-      <c r="E824" s="51"/>
+      <c r="D824" s="50"/>
+      <c r="E824" s="50"/>
     </row>
     <row r="825" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D825" s="51"/>
-      <c r="E825" s="51"/>
+      <c r="D825" s="50"/>
+      <c r="E825" s="50"/>
     </row>
     <row r="826" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D826" s="51"/>
-      <c r="E826" s="51"/>
+      <c r="D826" s="50"/>
+      <c r="E826" s="50"/>
     </row>
     <row r="827" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D827" s="51"/>
-      <c r="E827" s="51"/>
+      <c r="D827" s="50"/>
+      <c r="E827" s="50"/>
     </row>
     <row r="828" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D828" s="51"/>
-      <c r="E828" s="51"/>
+      <c r="D828" s="50"/>
+      <c r="E828" s="50"/>
     </row>
     <row r="829" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D829" s="51"/>
-      <c r="E829" s="51"/>
+      <c r="D829" s="50"/>
+      <c r="E829" s="50"/>
     </row>
     <row r="830" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D830" s="51"/>
-      <c r="E830" s="51"/>
+      <c r="D830" s="50"/>
+      <c r="E830" s="50"/>
     </row>
     <row r="831" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D831" s="51"/>
-      <c r="E831" s="51"/>
+      <c r="D831" s="50"/>
+      <c r="E831" s="50"/>
     </row>
     <row r="832" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D832" s="51"/>
-      <c r="E832" s="51"/>
+      <c r="D832" s="50"/>
+      <c r="E832" s="50"/>
     </row>
     <row r="833" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D833" s="51"/>
-      <c r="E833" s="51"/>
+      <c r="D833" s="50"/>
+      <c r="E833" s="50"/>
     </row>
     <row r="834" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D834" s="51"/>
-      <c r="E834" s="51"/>
+      <c r="D834" s="50"/>
+      <c r="E834" s="50"/>
     </row>
     <row r="835" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D835" s="51"/>
-      <c r="E835" s="51"/>
+      <c r="D835" s="50"/>
+      <c r="E835" s="50"/>
     </row>
     <row r="836" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D836" s="51"/>
-      <c r="E836" s="51"/>
+      <c r="D836" s="50"/>
+      <c r="E836" s="50"/>
     </row>
     <row r="837" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D837" s="51"/>
-      <c r="E837" s="51"/>
+      <c r="D837" s="50"/>
+      <c r="E837" s="50"/>
     </row>
     <row r="838" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D838" s="51"/>
-      <c r="E838" s="51"/>
+      <c r="D838" s="50"/>
+      <c r="E838" s="50"/>
     </row>
     <row r="839" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D839" s="51"/>
-      <c r="E839" s="51"/>
+      <c r="D839" s="50"/>
+      <c r="E839" s="50"/>
     </row>
     <row r="840" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D840" s="51"/>
-      <c r="E840" s="51"/>
+      <c r="D840" s="50"/>
+      <c r="E840" s="50"/>
     </row>
     <row r="841" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D841" s="51"/>
-      <c r="E841" s="51"/>
+      <c r="D841" s="50"/>
+      <c r="E841" s="50"/>
     </row>
     <row r="842" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D842" s="51"/>
-      <c r="E842" s="51"/>
+      <c r="D842" s="50"/>
+      <c r="E842" s="50"/>
     </row>
     <row r="843" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D843" s="51"/>
-      <c r="E843" s="51"/>
+      <c r="D843" s="50"/>
+      <c r="E843" s="50"/>
     </row>
     <row r="844" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D844" s="51"/>
-      <c r="E844" s="51"/>
+      <c r="D844" s="50"/>
+      <c r="E844" s="50"/>
     </row>
     <row r="845" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D845" s="51"/>
-      <c r="E845" s="51"/>
+      <c r="D845" s="50"/>
+      <c r="E845" s="50"/>
     </row>
     <row r="846" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D846" s="51"/>
-      <c r="E846" s="51"/>
+      <c r="D846" s="50"/>
+      <c r="E846" s="50"/>
     </row>
     <row r="847" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D847" s="51"/>
-      <c r="E847" s="51"/>
+      <c r="D847" s="50"/>
+      <c r="E847" s="50"/>
     </row>
     <row r="848" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D848" s="51"/>
-      <c r="E848" s="51"/>
+      <c r="D848" s="50"/>
+      <c r="E848" s="50"/>
     </row>
     <row r="849" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D849" s="51"/>
-      <c r="E849" s="51"/>
+      <c r="D849" s="50"/>
+      <c r="E849" s="50"/>
     </row>
     <row r="850" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D850" s="51"/>
-      <c r="E850" s="51"/>
+      <c r="D850" s="50"/>
+      <c r="E850" s="50"/>
     </row>
     <row r="851" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D851" s="51"/>
-      <c r="E851" s="51"/>
+      <c r="D851" s="50"/>
+      <c r="E851" s="50"/>
     </row>
     <row r="852" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D852" s="51"/>
-      <c r="E852" s="51"/>
+      <c r="D852" s="50"/>
+      <c r="E852" s="50"/>
     </row>
     <row r="853" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D853" s="51"/>
-      <c r="E853" s="51"/>
+      <c r="D853" s="50"/>
+      <c r="E853" s="50"/>
     </row>
     <row r="854" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D854" s="51"/>
-      <c r="E854" s="51"/>
+      <c r="D854" s="50"/>
+      <c r="E854" s="50"/>
     </row>
     <row r="855" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D855" s="51"/>
-      <c r="E855" s="51"/>
+      <c r="D855" s="50"/>
+      <c r="E855" s="50"/>
     </row>
     <row r="856" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D856" s="51"/>
-      <c r="E856" s="51"/>
+      <c r="D856" s="50"/>
+      <c r="E856" s="50"/>
     </row>
     <row r="857" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D857" s="51"/>
-      <c r="E857" s="51"/>
+      <c r="D857" s="50"/>
+      <c r="E857" s="50"/>
     </row>
     <row r="858" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D858" s="51"/>
-      <c r="E858" s="51"/>
+      <c r="D858" s="50"/>
+      <c r="E858" s="50"/>
     </row>
     <row r="859" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D859" s="51"/>
-      <c r="E859" s="51"/>
+      <c r="D859" s="50"/>
+      <c r="E859" s="50"/>
     </row>
     <row r="860" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D860" s="51"/>
-      <c r="E860" s="51"/>
+      <c r="D860" s="50"/>
+      <c r="E860" s="50"/>
     </row>
     <row r="861" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D861" s="51"/>
-      <c r="E861" s="51"/>
+      <c r="D861" s="50"/>
+      <c r="E861" s="50"/>
     </row>
     <row r="862" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D862" s="51"/>
-      <c r="E862" s="51"/>
+      <c r="D862" s="50"/>
+      <c r="E862" s="50"/>
     </row>
     <row r="863" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D863" s="51"/>
-      <c r="E863" s="51"/>
+      <c r="D863" s="50"/>
+      <c r="E863" s="50"/>
     </row>
     <row r="864" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D864" s="51"/>
-      <c r="E864" s="51"/>
+      <c r="D864" s="50"/>
+      <c r="E864" s="50"/>
     </row>
     <row r="865" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D865" s="51"/>
-      <c r="E865" s="51"/>
+      <c r="D865" s="50"/>
+      <c r="E865" s="50"/>
     </row>
     <row r="866" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D866" s="51"/>
-      <c r="E866" s="51"/>
+      <c r="D866" s="50"/>
+      <c r="E866" s="50"/>
     </row>
     <row r="867" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D867" s="51"/>
-      <c r="E867" s="51"/>
+      <c r="D867" s="50"/>
+      <c r="E867" s="50"/>
     </row>
     <row r="868" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D868" s="51"/>
-      <c r="E868" s="51"/>
+      <c r="D868" s="50"/>
+      <c r="E868" s="50"/>
     </row>
     <row r="869" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D869" s="51"/>
-      <c r="E869" s="51"/>
+      <c r="D869" s="50"/>
+      <c r="E869" s="50"/>
     </row>
     <row r="870" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D870" s="51"/>
-      <c r="E870" s="51"/>
+      <c r="D870" s="50"/>
+      <c r="E870" s="50"/>
     </row>
     <row r="871" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D871" s="51"/>
-      <c r="E871" s="51"/>
+      <c r="D871" s="50"/>
+      <c r="E871" s="50"/>
     </row>
     <row r="872" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D872" s="51"/>
-      <c r="E872" s="51"/>
+      <c r="D872" s="50"/>
+      <c r="E872" s="50"/>
     </row>
     <row r="873" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D873" s="51"/>
-      <c r="E873" s="51"/>
+      <c r="D873" s="50"/>
+      <c r="E873" s="50"/>
     </row>
     <row r="874" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D874" s="51"/>
-      <c r="E874" s="51"/>
+      <c r="D874" s="50"/>
+      <c r="E874" s="50"/>
     </row>
     <row r="875" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D875" s="51"/>
-      <c r="E875" s="51"/>
+      <c r="D875" s="50"/>
+      <c r="E875" s="50"/>
     </row>
     <row r="876" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D876" s="51"/>
-      <c r="E876" s="51"/>
+      <c r="D876" s="50"/>
+      <c r="E876" s="50"/>
     </row>
     <row r="877" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D877" s="51"/>
-      <c r="E877" s="51"/>
+      <c r="D877" s="50"/>
+      <c r="E877" s="50"/>
     </row>
     <row r="878" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D878" s="51"/>
-      <c r="E878" s="51"/>
+      <c r="D878" s="50"/>
+      <c r="E878" s="50"/>
     </row>
     <row r="879" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D879" s="51"/>
-      <c r="E879" s="51"/>
+      <c r="D879" s="50"/>
+      <c r="E879" s="50"/>
     </row>
     <row r="880" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D880" s="51"/>
-      <c r="E880" s="51"/>
+      <c r="D880" s="50"/>
+      <c r="E880" s="50"/>
     </row>
     <row r="881" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D881" s="51"/>
-      <c r="E881" s="51"/>
+      <c r="D881" s="50"/>
+      <c r="E881" s="50"/>
     </row>
     <row r="882" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D882" s="51"/>
-      <c r="E882" s="51"/>
+      <c r="D882" s="50"/>
+      <c r="E882" s="50"/>
     </row>
     <row r="883" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D883" s="51"/>
-      <c r="E883" s="51"/>
+      <c r="D883" s="50"/>
+      <c r="E883" s="50"/>
     </row>
     <row r="884" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D884" s="51"/>
-      <c r="E884" s="51"/>
+      <c r="D884" s="50"/>
+      <c r="E884" s="50"/>
     </row>
     <row r="885" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D885" s="51"/>
-      <c r="E885" s="51"/>
+      <c r="D885" s="50"/>
+      <c r="E885" s="50"/>
     </row>
     <row r="886" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D886" s="51"/>
-      <c r="E886" s="51"/>
+      <c r="D886" s="50"/>
+      <c r="E886" s="50"/>
     </row>
     <row r="887" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D887" s="51"/>
-      <c r="E887" s="51"/>
+      <c r="D887" s="50"/>
+      <c r="E887" s="50"/>
     </row>
     <row r="888" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D888" s="51"/>
-      <c r="E888" s="51"/>
+      <c r="D888" s="50"/>
+      <c r="E888" s="50"/>
     </row>
     <row r="889" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D889" s="51"/>
-      <c r="E889" s="51"/>
+      <c r="D889" s="50"/>
+      <c r="E889" s="50"/>
     </row>
     <row r="890" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D890" s="51"/>
-      <c r="E890" s="51"/>
+      <c r="D890" s="50"/>
+      <c r="E890" s="50"/>
     </row>
     <row r="891" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D891" s="51"/>
-      <c r="E891" s="51"/>
+      <c r="D891" s="50"/>
+      <c r="E891" s="50"/>
     </row>
     <row r="892" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D892" s="51"/>
-      <c r="E892" s="51"/>
+      <c r="D892" s="50"/>
+      <c r="E892" s="50"/>
     </row>
     <row r="893" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D893" s="51"/>
-      <c r="E893" s="51"/>
+      <c r="D893" s="50"/>
+      <c r="E893" s="50"/>
     </row>
     <row r="894" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D894" s="51"/>
-      <c r="E894" s="51"/>
+      <c r="D894" s="50"/>
+      <c r="E894" s="50"/>
     </row>
     <row r="895" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D895" s="51"/>
-      <c r="E895" s="51"/>
+      <c r="D895" s="50"/>
+      <c r="E895" s="50"/>
     </row>
     <row r="896" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D896" s="51"/>
-      <c r="E896" s="51"/>
+      <c r="D896" s="50"/>
+      <c r="E896" s="50"/>
     </row>
     <row r="897" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D897" s="51"/>
-      <c r="E897" s="51"/>
+      <c r="D897" s="50"/>
+      <c r="E897" s="50"/>
     </row>
     <row r="898" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D898" s="51"/>
-      <c r="E898" s="51"/>
+      <c r="D898" s="50"/>
+      <c r="E898" s="50"/>
     </row>
     <row r="899" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D899" s="51"/>
-      <c r="E899" s="51"/>
+      <c r="D899" s="50"/>
+      <c r="E899" s="50"/>
     </row>
     <row r="900" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D900" s="51"/>
-      <c r="E900" s="51"/>
+      <c r="D900" s="50"/>
+      <c r="E900" s="50"/>
     </row>
     <row r="901" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D901" s="51"/>
-      <c r="E901" s="51"/>
+      <c r="D901" s="50"/>
+      <c r="E901" s="50"/>
     </row>
     <row r="902" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D902" s="51"/>
-      <c r="E902" s="51"/>
+      <c r="D902" s="50"/>
+      <c r="E902" s="50"/>
     </row>
     <row r="903" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D903" s="51"/>
-      <c r="E903" s="51"/>
+      <c r="D903" s="50"/>
+      <c r="E903" s="50"/>
     </row>
     <row r="904" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D904" s="51"/>
-      <c r="E904" s="51"/>
+      <c r="D904" s="50"/>
+      <c r="E904" s="50"/>
     </row>
     <row r="905" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D905" s="51"/>
-      <c r="E905" s="51"/>
+      <c r="D905" s="50"/>
+      <c r="E905" s="50"/>
     </row>
     <row r="906" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D906" s="51"/>
-      <c r="E906" s="51"/>
+      <c r="D906" s="50"/>
+      <c r="E906" s="50"/>
     </row>
     <row r="907" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D907" s="51"/>
-      <c r="E907" s="51"/>
+      <c r="D907" s="50"/>
+      <c r="E907" s="50"/>
     </row>
     <row r="908" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D908" s="51"/>
-      <c r="E908" s="51"/>
+      <c r="D908" s="50"/>
+      <c r="E908" s="50"/>
     </row>
     <row r="909" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D909" s="51"/>
-      <c r="E909" s="51"/>
+      <c r="D909" s="50"/>
+      <c r="E909" s="50"/>
     </row>
     <row r="910" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D910" s="51"/>
-      <c r="E910" s="51"/>
+      <c r="D910" s="50"/>
+      <c r="E910" s="50"/>
     </row>
     <row r="911" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D911" s="51"/>
-      <c r="E911" s="51"/>
+      <c r="D911" s="50"/>
+      <c r="E911" s="50"/>
     </row>
     <row r="912" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D912" s="51"/>
-      <c r="E912" s="51"/>
+      <c r="D912" s="50"/>
+      <c r="E912" s="50"/>
     </row>
     <row r="913" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D913" s="51"/>
-      <c r="E913" s="51"/>
+      <c r="D913" s="50"/>
+      <c r="E913" s="50"/>
     </row>
     <row r="914" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D914" s="51"/>
-      <c r="E914" s="51"/>
+      <c r="D914" s="50"/>
+      <c r="E914" s="50"/>
     </row>
     <row r="915" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D915" s="51"/>
-      <c r="E915" s="51"/>
+      <c r="D915" s="50"/>
+      <c r="E915" s="50"/>
     </row>
     <row r="916" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D916" s="51"/>
-      <c r="E916" s="51"/>
+      <c r="D916" s="50"/>
+      <c r="E916" s="50"/>
     </row>
     <row r="917" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D917" s="51"/>
-      <c r="E917" s="51"/>
+      <c r="D917" s="50"/>
+      <c r="E917" s="50"/>
     </row>
     <row r="918" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D918" s="51"/>
-      <c r="E918" s="51"/>
+      <c r="D918" s="50"/>
+      <c r="E918" s="50"/>
     </row>
     <row r="919" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D919" s="51"/>
-      <c r="E919" s="51"/>
+      <c r="D919" s="50"/>
+      <c r="E919" s="50"/>
     </row>
     <row r="920" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D920" s="51"/>
-      <c r="E920" s="51"/>
+      <c r="D920" s="50"/>
+      <c r="E920" s="50"/>
     </row>
     <row r="921" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D921" s="51"/>
-      <c r="E921" s="51"/>
+      <c r="D921" s="50"/>
+      <c r="E921" s="50"/>
     </row>
     <row r="922" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D922" s="51"/>
-      <c r="E922" s="51"/>
+      <c r="D922" s="50"/>
+      <c r="E922" s="50"/>
     </row>
     <row r="923" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D923" s="51"/>
-      <c r="E923" s="51"/>
+      <c r="D923" s="50"/>
+      <c r="E923" s="50"/>
     </row>
     <row r="924" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D924" s="51"/>
-      <c r="E924" s="51"/>
+      <c r="D924" s="50"/>
+      <c r="E924" s="50"/>
     </row>
     <row r="925" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D925" s="51"/>
-      <c r="E925" s="51"/>
+      <c r="D925" s="50"/>
+      <c r="E925" s="50"/>
     </row>
     <row r="926" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D926" s="51"/>
-      <c r="E926" s="51"/>
+      <c r="D926" s="50"/>
+      <c r="E926" s="50"/>
     </row>
     <row r="927" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D927" s="51"/>
-      <c r="E927" s="51"/>
+      <c r="D927" s="50"/>
+      <c r="E927" s="50"/>
     </row>
     <row r="928" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D928" s="51"/>
-      <c r="E928" s="51"/>
+      <c r="D928" s="50"/>
+      <c r="E928" s="50"/>
     </row>
     <row r="929" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D929" s="51"/>
-      <c r="E929" s="51"/>
+      <c r="D929" s="50"/>
+      <c r="E929" s="50"/>
     </row>
     <row r="930" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D930" s="51"/>
-      <c r="E930" s="51"/>
+      <c r="D930" s="50"/>
+      <c r="E930" s="50"/>
     </row>
     <row r="931" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D931" s="51"/>
-      <c r="E931" s="51"/>
+      <c r="D931" s="50"/>
+      <c r="E931" s="50"/>
     </row>
     <row r="932" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D932" s="51"/>
-      <c r="E932" s="51"/>
+      <c r="D932" s="50"/>
+      <c r="E932" s="50"/>
     </row>
     <row r="933" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D933" s="51"/>
-      <c r="E933" s="51"/>
+      <c r="D933" s="50"/>
+      <c r="E933" s="50"/>
     </row>
     <row r="934" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D934" s="51"/>
-      <c r="E934" s="51"/>
+      <c r="D934" s="50"/>
+      <c r="E934" s="50"/>
     </row>
     <row r="935" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D935" s="51"/>
-      <c r="E935" s="51"/>
+      <c r="D935" s="50"/>
+      <c r="E935" s="50"/>
     </row>
     <row r="936" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D936" s="51"/>
-      <c r="E936" s="51"/>
+      <c r="D936" s="50"/>
+      <c r="E936" s="50"/>
     </row>
     <row r="937" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D937" s="51"/>
-      <c r="E937" s="51"/>
+      <c r="D937" s="50"/>
+      <c r="E937" s="50"/>
     </row>
     <row r="938" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D938" s="51"/>
-      <c r="E938" s="51"/>
+      <c r="D938" s="50"/>
+      <c r="E938" s="50"/>
     </row>
     <row r="939" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D939" s="51"/>
-      <c r="E939" s="51"/>
+      <c r="D939" s="50"/>
+      <c r="E939" s="50"/>
     </row>
     <row r="940" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D940" s="51"/>
-      <c r="E940" s="51"/>
+      <c r="D940" s="50"/>
+      <c r="E940" s="50"/>
     </row>
     <row r="941" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D941" s="51"/>
-      <c r="E941" s="51"/>
+      <c r="D941" s="50"/>
+      <c r="E941" s="50"/>
     </row>
     <row r="942" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D942" s="51"/>
-      <c r="E942" s="51"/>
+      <c r="D942" s="50"/>
+      <c r="E942" s="50"/>
     </row>
     <row r="943" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D943" s="51"/>
-      <c r="E943" s="51"/>
+      <c r="D943" s="50"/>
+      <c r="E943" s="50"/>
     </row>
     <row r="944" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D944" s="51"/>
-      <c r="E944" s="51"/>
+      <c r="D944" s="50"/>
+      <c r="E944" s="50"/>
     </row>
     <row r="945" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D945" s="51"/>
-      <c r="E945" s="51"/>
+      <c r="D945" s="50"/>
+      <c r="E945" s="50"/>
     </row>
     <row r="946" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D946" s="51"/>
-      <c r="E946" s="51"/>
+      <c r="D946" s="50"/>
+      <c r="E946" s="50"/>
     </row>
     <row r="947" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D947" s="51"/>
-      <c r="E947" s="51"/>
+      <c r="D947" s="50"/>
+      <c r="E947" s="50"/>
     </row>
     <row r="948" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D948" s="51"/>
-      <c r="E948" s="51"/>
+      <c r="D948" s="50"/>
+      <c r="E948" s="50"/>
     </row>
     <row r="949" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D949" s="51"/>
-      <c r="E949" s="51"/>
+      <c r="D949" s="50"/>
+      <c r="E949" s="50"/>
     </row>
     <row r="950" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D950" s="51"/>
-      <c r="E950" s="51"/>
+      <c r="D950" s="50"/>
+      <c r="E950" s="50"/>
     </row>
     <row r="951" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D951" s="51"/>
-      <c r="E951" s="51"/>
+      <c r="D951" s="50"/>
+      <c r="E951" s="50"/>
     </row>
     <row r="952" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D952" s="51"/>
-      <c r="E952" s="51"/>
+      <c r="D952" s="50"/>
+      <c r="E952" s="50"/>
     </row>
     <row r="953" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D953" s="51"/>
-      <c r="E953" s="51"/>
+      <c r="D953" s="50"/>
+      <c r="E953" s="50"/>
     </row>
     <row r="954" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D954" s="51"/>
-      <c r="E954" s="51"/>
+      <c r="D954" s="50"/>
+      <c r="E954" s="50"/>
     </row>
     <row r="955" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D955" s="51"/>
-      <c r="E955" s="51"/>
+      <c r="D955" s="50"/>
+      <c r="E955" s="50"/>
     </row>
     <row r="956" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D956" s="51"/>
-      <c r="E956" s="51"/>
+      <c r="D956" s="50"/>
+      <c r="E956" s="50"/>
     </row>
     <row r="957" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D957" s="51"/>
-      <c r="E957" s="51"/>
+      <c r="D957" s="50"/>
+      <c r="E957" s="50"/>
     </row>
     <row r="958" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D958" s="51"/>
-      <c r="E958" s="51"/>
+      <c r="D958" s="50"/>
+      <c r="E958" s="50"/>
     </row>
     <row r="959" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D959" s="51"/>
-      <c r="E959" s="51"/>
+      <c r="D959" s="50"/>
+      <c r="E959" s="50"/>
     </row>
     <row r="960" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D960" s="51"/>
-      <c r="E960" s="51"/>
+      <c r="D960" s="50"/>
+      <c r="E960" s="50"/>
     </row>
     <row r="961" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D961" s="51"/>
-      <c r="E961" s="51"/>
+      <c r="D961" s="50"/>
+      <c r="E961" s="50"/>
     </row>
     <row r="962" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D962" s="51"/>
-      <c r="E962" s="51"/>
+      <c r="D962" s="50"/>
+      <c r="E962" s="50"/>
     </row>
     <row r="963" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D963" s="51"/>
-      <c r="E963" s="51"/>
+      <c r="D963" s="50"/>
+      <c r="E963" s="50"/>
     </row>
     <row r="964" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D964" s="51"/>
-      <c r="E964" s="51"/>
+      <c r="D964" s="50"/>
+      <c r="E964" s="50"/>
     </row>
     <row r="965" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D965" s="51"/>
-      <c r="E965" s="51"/>
+      <c r="D965" s="50"/>
+      <c r="E965" s="50"/>
     </row>
     <row r="966" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D966" s="51"/>
-      <c r="E966" s="51"/>
+      <c r="D966" s="50"/>
+      <c r="E966" s="50"/>
     </row>
     <row r="967" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D967" s="51"/>
-      <c r="E967" s="51"/>
+      <c r="D967" s="50"/>
+      <c r="E967" s="50"/>
     </row>
     <row r="968" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D968" s="51"/>
-      <c r="E968" s="51"/>
+      <c r="D968" s="50"/>
+      <c r="E968" s="50"/>
     </row>
     <row r="969" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D969" s="51"/>
-      <c r="E969" s="51"/>
+      <c r="D969" s="50"/>
+      <c r="E969" s="50"/>
     </row>
     <row r="970" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D970" s="51"/>
-      <c r="E970" s="51"/>
+      <c r="D970" s="50"/>
+      <c r="E970" s="50"/>
     </row>
     <row r="971" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D971" s="51"/>
-      <c r="E971" s="51"/>
+      <c r="D971" s="50"/>
+      <c r="E971" s="50"/>
     </row>
     <row r="972" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D972" s="51"/>
-      <c r="E972" s="51"/>
+      <c r="D972" s="50"/>
+      <c r="E972" s="50"/>
     </row>
     <row r="973" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D973" s="51"/>
-      <c r="E973" s="51"/>
+      <c r="D973" s="50"/>
+      <c r="E973" s="50"/>
     </row>
     <row r="974" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D974" s="51"/>
-      <c r="E974" s="51"/>
+      <c r="D974" s="50"/>
+      <c r="E974" s="50"/>
     </row>
     <row r="975" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D975" s="51"/>
-      <c r="E975" s="51"/>
+      <c r="D975" s="50"/>
+      <c r="E975" s="50"/>
     </row>
     <row r="976" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D976" s="51"/>
-      <c r="E976" s="51"/>
+      <c r="D976" s="50"/>
+      <c r="E976" s="50"/>
     </row>
     <row r="977" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D977" s="51"/>
-      <c r="E977" s="51"/>
+      <c r="D977" s="50"/>
+      <c r="E977" s="50"/>
     </row>
     <row r="978" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D978" s="51"/>
-      <c r="E978" s="51"/>
+      <c r="D978" s="50"/>
+      <c r="E978" s="50"/>
     </row>
     <row r="979" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D979" s="51"/>
-      <c r="E979" s="51"/>
+      <c r="D979" s="50"/>
+      <c r="E979" s="50"/>
     </row>
     <row r="980" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D980" s="51"/>
-      <c r="E980" s="51"/>
+      <c r="D980" s="50"/>
+      <c r="E980" s="50"/>
     </row>
     <row r="981" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D981" s="51"/>
-      <c r="E981" s="51"/>
+      <c r="D981" s="50"/>
+      <c r="E981" s="50"/>
     </row>
     <row r="982" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D982" s="51"/>
-      <c r="E982" s="51"/>
+      <c r="D982" s="50"/>
+      <c r="E982" s="50"/>
     </row>
     <row r="983" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D983" s="51"/>
-      <c r="E983" s="51"/>
+      <c r="D983" s="50"/>
+      <c r="E983" s="50"/>
     </row>
     <row r="984" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D984" s="51"/>
-      <c r="E984" s="51"/>
+      <c r="D984" s="50"/>
+      <c r="E984" s="50"/>
     </row>
     <row r="985" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D985" s="51"/>
-      <c r="E985" s="51"/>
+      <c r="D985" s="50"/>
+      <c r="E985" s="50"/>
     </row>
     <row r="986" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D986" s="51"/>
-      <c r="E986" s="51"/>
+      <c r="D986" s="50"/>
+      <c r="E986" s="50"/>
     </row>
     <row r="987" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D987" s="51"/>
-      <c r="E987" s="51"/>
+      <c r="D987" s="50"/>
+      <c r="E987" s="50"/>
     </row>
     <row r="988" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D988" s="51"/>
-      <c r="E988" s="51"/>
+      <c r="D988" s="50"/>
+      <c r="E988" s="50"/>
     </row>
     <row r="989" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D989" s="51"/>
-      <c r="E989" s="51"/>
+      <c r="D989" s="50"/>
+      <c r="E989" s="50"/>
     </row>
     <row r="990" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D990" s="51"/>
-      <c r="E990" s="51"/>
+      <c r="D990" s="50"/>
+      <c r="E990" s="50"/>
     </row>
     <row r="991" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D991" s="51"/>
-      <c r="E991" s="51"/>
+      <c r="D991" s="50"/>
+      <c r="E991" s="50"/>
     </row>
     <row r="992" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D992" s="51"/>
-      <c r="E992" s="51"/>
+      <c r="D992" s="50"/>
+      <c r="E992" s="50"/>
     </row>
     <row r="993" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D993" s="51"/>
-      <c r="E993" s="51"/>
+      <c r="D993" s="50"/>
+      <c r="E993" s="50"/>
     </row>
     <row r="994" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D994" s="51"/>
-      <c r="E994" s="51"/>
+      <c r="D994" s="50"/>
+      <c r="E994" s="50"/>
     </row>
     <row r="995" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D995" s="51"/>
-      <c r="E995" s="51"/>
+      <c r="D995" s="50"/>
+      <c r="E995" s="50"/>
     </row>
     <row r="996" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D996" s="51"/>
-      <c r="E996" s="51"/>
+      <c r="D996" s="50"/>
+      <c r="E996" s="50"/>
     </row>
     <row r="997" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D997" s="51"/>
-      <c r="E997" s="51"/>
+      <c r="D997" s="50"/>
+      <c r="E997" s="50"/>
     </row>
     <row r="998" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D998" s="51"/>
-      <c r="E998" s="51"/>
+      <c r="D998" s="50"/>
+      <c r="E998" s="50"/>
     </row>
     <row r="999" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D999" s="51"/>
-      <c r="E999" s="51"/>
+      <c r="D999" s="50"/>
+      <c r="E999" s="50"/>
     </row>
     <row r="1000" spans="4:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D1000" s="51"/>
-      <c r="E1000" s="51"/>
+      <c r="D1000" s="50"/>
+      <c r="E1000" s="50"/>
     </row>
     <row r="1047602" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F1047602" s="38"/>
+      <c r="F1047602" s="37"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1047602" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
@@ -63548,468 +63551,468 @@
   <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.109375" style="55" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" style="55" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" style="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="78" t="s">
         <v>494</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="78" t="s">
         <v>583</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="78" t="s">
         <v>588</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="78" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="51" t="s">
         <v>498</v>
       </c>
-      <c r="B2" s="55">
+      <c r="B2" s="53">
         <f>COUNTIF(Fatture!C2:C80,"abbigliamento")</f>
         <v>11</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="51" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="51" t="s">
         <v>499</v>
       </c>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="75" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="51" t="s">
         <v>503</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="51" t="s">
         <v>500</v>
       </c>
-      <c r="D4" s="55">
+      <c r="D4" s="53">
         <f>COUNTIF(Fatture!$B$2:$B$80,C4)</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="51" t="s">
         <v>505</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="53">
         <f>COUNTIF(Fatture!C5:C83,"abbigliamento")</f>
         <v>9</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="51" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="51" t="s">
         <v>507</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="51" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="51" t="s">
         <v>506</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="53">
         <f>COUNTIF(Fatture!$B$2:$B$80,C7)</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="51" t="s">
         <v>511</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="51" t="s">
         <v>508</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="53">
         <f>COUNTIF(Fatture!$B$2:$B$80,C8)</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>514</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="51" t="s">
         <v>500</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="53">
         <f>COUNTIF(Fatture!$B$2:$B$80,C9)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="51" t="s">
         <v>515</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="51" t="s">
         <v>510</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="53">
         <f>COUNTIF(Fatture!$B$2:$B$80,C10)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="51" t="s">
         <v>517</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="51" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="51" t="s">
         <v>520</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="51" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="51" t="s">
         <v>523</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="51" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="51" t="s">
         <v>526</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="51" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="51" t="s">
         <v>529</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="51" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="51" t="s">
         <v>534</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="51" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="51" t="s">
         <v>539</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="51" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="51" t="s">
         <v>542</v>
       </c>
-      <c r="C18" s="52" t="s">
+      <c r="C18" s="51" t="s">
         <v>524</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="53">
         <f>COUNTIF(Fatture!$B$2:$B$80,C18)</f>
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="51" t="s">
         <v>544</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="51" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="51" t="s">
         <v>546</v>
       </c>
-      <c r="B20" s="55">
+      <c r="B20" s="53">
         <f>COUNTIF(Fatture!C20:C98,"abbigliamento")</f>
         <v>8</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="51" t="s">
         <v>527</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="53">
         <f>COUNTIF(Fatture!$B$2:$B$80,C20)</f>
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="52" t="s">
+      <c r="A21" s="51" t="s">
         <v>550</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="51" t="s">
         <v>528</v>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="53">
         <f>COUNTIF(Fatture!$B$2:$B$80,C21)</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="51" t="s">
         <v>555</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="51" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="51" t="s">
         <v>557</v>
       </c>
-      <c r="B23" s="55">
+      <c r="B23" s="53">
         <f>COUNTIF(Fatture!C23:C101,"abbigliamento")</f>
         <v>8</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="51" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="51" t="s">
         <v>561</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="51" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="51" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="51" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="51" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="51" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="51" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="51" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="51" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="51" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="51" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C34" s="52" t="s">
+      <c r="C34" s="51" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C35" s="52" t="s">
+      <c r="C35" s="51" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C36" s="52" t="s">
+      <c r="C36" s="51" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C37" s="52" t="s">
+      <c r="C37" s="51" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C38" s="52" t="s">
+      <c r="C38" s="51" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C39" s="52" t="s">
+      <c r="C39" s="51" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="40" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C40" s="52" t="s">
+      <c r="C40" s="51" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="41" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C41" s="52" t="s">
+      <c r="C41" s="51" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="42" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="51" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="43" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C43" s="52" t="s">
+      <c r="C43" s="51" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="44" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C44" s="52" t="s">
+      <c r="C44" s="51" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C45" s="52" t="s">
+      <c r="C45" s="51" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="46" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C46" s="52" t="s">
+      <c r="C46" s="51" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="47" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="51" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="48" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C48" s="52" t="s">
+      <c r="C48" s="51" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C49" s="52" t="s">
+      <c r="C49" s="51" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C50" s="52" t="s">
+      <c r="C50" s="51" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="51" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C51" s="52" t="s">
+      <c r="C51" s="51" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="52" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C52" s="52" t="s">
+      <c r="C52" s="51" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="53" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C53" s="52" t="s">
+      <c r="C53" s="51" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="54" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C54" s="52" t="s">
+      <c r="C54" s="51" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="55" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C55" s="52" t="s">
+      <c r="C55" s="51" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="56" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C56" s="52" t="s">
+      <c r="C56" s="51" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="57" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C57" s="52" t="s">
+      <c r="C57" s="51" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="58" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C58" s="52" t="s">
+      <c r="C58" s="51" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="59" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C59" s="52" t="s">
+      <c r="C59" s="51" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="60" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C60" s="52" t="s">
+      <c r="C60" s="51" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="61" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C61" s="52" t="s">
+      <c r="C61" s="51" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="62" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C62" s="52" t="s">
+      <c r="C62" s="51" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="63" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C63" s="52" t="s">
+      <c r="C63" s="51" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="64" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C64" s="52" t="s">
+      <c r="C64" s="51" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C65" s="52" t="s">
+      <c r="C65" s="51" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="66" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C66" s="52" t="s">
+      <c r="C66" s="51" t="s">
         <v>567</v>
       </c>
     </row>
@@ -64024,23 +64027,23 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" style="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.77734375" style="40" customWidth="1"/>
+    <col min="1" max="1" width="38.109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" style="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" style="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>582</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="76" t="s">
         <v>577</v>
       </c>
-      <c r="C1" s="79"/>
+      <c r="C1" s="77"/>
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>570</v>
       </c>
       <c r="B2" s="24" t="s">
@@ -64054,13 +64057,13 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="71" t="s">
         <v>571</v>
       </c>
-      <c r="B3" s="69">
+      <c r="B3" s="67">
         <v>0</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="69" t="s">
         <v>581</v>
       </c>
       <c r="D3" s="20"/>
@@ -64068,13 +64071,13 @@
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="71" t="s">
         <v>572</v>
       </c>
-      <c r="B4" s="69">
+      <c r="B4" s="67">
         <v>40</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="69" t="s">
         <v>580</v>
       </c>
       <c r="D4" s="20"/>
@@ -64082,25 +64085,25 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="71" t="s">
         <v>573</v>
       </c>
-      <c r="B5" s="69">
+      <c r="B5" s="67">
         <v>60</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="69" t="s">
         <v>579</v>
       </c>
       <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="72" t="s">
         <v>574</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="68">
         <v>70</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="70" t="s">
         <v>578</v>
       </c>
       <c r="D6" s="20"/>
